--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_令和8年3月課長会議資料との対比" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_記載漏れと追加の方針" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_独自に加えた記載の棚卸し" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_協議用への移行の検討" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_協議用への移行の記録" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_記載する場合の体裁" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_自己点検" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>747</v>
+        <v>721</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>15</v>
@@ -1005,36 +1005,51 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E26" s="14" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="28" ht="66" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>注1）「移す」と判定したものは、削るのではなく打合せ協議用の資料へ移すことを提案するものである。移した後の本文には結論のみを残す。
-注2）「協議」と判定したものは、計画に置くか移すかを打合せでお決めいただくものである。既定値は「素案に残す」とする。
-注3）本表は判定の案であり、素案の記載はまだ動かしていない。お決めいただいた後に一括して反映する。
-注4）判定は確認事項No.170、体裁は確認事項No.171として業務工程管理表に登録している。</t>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>【令和8年9月29日のご指示による移行（済み）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から916段落141表36図となった（表6点の減）。
+「協議」と判定した15件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>注1）「協議」と判定したものは、計画に置くか移すかを打合せでお決めいただくものである。既定値は「素案に残す」とする。
+注2）判定は確認事項No.170、体裁は確認事項No.171として業務工程管理表に登録している。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="F25:J25"/>
+    <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="E15:J15"/>
     <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="F24:J24"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="F26:J26"/>
@@ -1060,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1167,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表147表／実物147表</t>
+          <t>本表141表／実物141表</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
@@ -1177,7 +1192,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表747段落（空段落・目次の行を除く）／実物943段落（すべて）</t>
+          <t>本表721段落（空段落・目次の行を除く）／実物916段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -1202,7 +1217,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>68件</t>
+          <t>61件</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -1802,7 +1817,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>23件（全68件）</t>
+          <t>15件（全61件）</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -1817,17 +1832,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>移し先の案が「移す」と判定した全件にあること</t>
+          <t>移した8件の見出しが計画素案に残っていないこと</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>ISAKI の網羅</t>
+          <t>ISHITA の見出しと素案の【　】の突合</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>8／8件</t>
+          <t>残っていない</t>
         </is>
       </c>
       <c r="E33" s="17" t="inlineStr">
@@ -1838,24 +1853,124 @@
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="10" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>移した内容の要点が計画素案の本文に残っていること</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>本文に残した値の走査</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>全て残っている</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="10" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>移した内容が移し先の成果品にあること</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>移し先4件の走査</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>全てある</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="10" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護の全数把握が実施済み調査 結果報告書にあること</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>181人・13事業所の走査</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="10" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>計画素案の見出しに「受託者」が現れないこと</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>【　】の見出しの走査</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>現れない</t>
+        </is>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>体裁の検討に第9期計画との関係が全件あること</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>TEISAI</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>10件</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2097,13 +2212,13 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>0</v>
@@ -2268,22 +2383,18 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>【　】の見出しが5件あり、記述の単位が多い。</t>
-        </is>
-      </c>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -2351,13 +2462,13 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>3</v>
@@ -2475,10 +2586,10 @@
         <v>13</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0</v>
@@ -2618,13 +2729,13 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>7</v>
@@ -2943,20 +3054,20 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>4</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>【　】の見出しが10件あり、記述の単位が多い。</t>
+          <t>【　】の見出しが8件あり、記述の単位が多い。</t>
         </is>
       </c>
     </row>
@@ -3161,13 +3272,13 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>747</v>
+        <v>721</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F55" s="14" t="n">
         <v>146</v>
@@ -5251,7 +5362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5337,7 +5448,7 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1</v>
@@ -5366,33 +5477,33 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第7節</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>推計の見直しの手順</t>
+          <t>訪問・通所困難地域の考え方</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
+        <v>0</v>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>推計を誰がいつ見直すかという作業の手順であり、計画の読み手に向けた記述ではない。進行管理の実施要領に移す。</t>
+          <t>基本指針別表 一（地勢と交通）に対応する。日常生活圏域の設定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -5409,18 +5520,18 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の考え方</t>
+          <t>通常の事業の実施地域による確認</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
@@ -5430,7 +5541,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 一（地勢と交通）に対応する。日常生活圏域の設定の根拠となる。</t>
+          <t>圏域設定の根拠を指定事業所の実施地域から確かめたもの。必要利用定員総数の圏域別の配分の前提となるため計画に置く。</t>
         </is>
       </c>
     </row>
@@ -5442,23 +5553,23 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第8節</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>通常の事業の実施地域による確認</t>
+          <t>北海道第9期計画の基本目標との対応</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -5468,7 +5579,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>圏域設定の根拠を指定事業所の実施地域から確かめたもの。必要利用定員総数の圏域別の配分の前提となるため計画に置く。</t>
+          <t>都道府県計画との調和は法第117条第9項による。</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5596,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>北海道第9期計画の基本目標との対応</t>
+          <t>「市町村数」を単位とする指標の読替え</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
@@ -5494,9 +5605,9 @@
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -5506,7 +5617,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>都道府県計画との調和は法第117条第9項による。</t>
+          <t>北海道計画の指標が市町村数を単位とするため、広域連合として読み替える必要がある。分量は3行にとどまる。</t>
         </is>
       </c>
     </row>
@@ -5518,23 +5629,23 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>第8節</t>
+          <t>第9節</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>「市町村数」を単位とする指標の読替え</t>
+          <t>2040年を見据えた地域類型の考え方</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -5544,7 +5655,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>北海道計画の指標が市町村数を単位とするため、広域連合として読み替える必要がある。分量は3行にとどまる。</t>
+          <t>令和8年3月課長会議資料により追加した。</t>
         </is>
       </c>
     </row>
@@ -5561,11 +5672,11 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2040年を見据えた地域類型の考え方</t>
+          <t>医療と介護の協議の場の再編成</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>0</v>
@@ -5599,14 +5710,14 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>医療と介護の協議の場の再編成</t>
+          <t>中山間・人口減少地域（特定地域）に係る特例の創設</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
@@ -5620,35 +5731,35 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。</t>
+          <t>令和9年4月施行。第10期の初年度から適用される。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>第1章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>第9節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）に係る特例の創設</t>
+          <t>第10期の人口の基礎</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
@@ -5658,7 +5769,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>令和9年4月施行。第10期の初年度から適用される。</t>
+          <t>推計の基礎を示すもので、見込量の前提として要る。</t>
         </is>
       </c>
     </row>
@@ -5675,28 +5786,28 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>第10期の人口の基礎</t>
+          <t>第9期計画及び社人研推計との関係</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>推計の基礎を示すもので、見込量の前提として要る。</t>
+          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
         </is>
       </c>
     </row>
@@ -5708,33 +5819,33 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>第9期計画及び社人研推計との関係</t>
+          <t>上川管内における位置</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>3</v>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
+          <t>第9期計画にも管内比較がある。</t>
         </is>
       </c>
     </row>
@@ -5751,18 +5862,18 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上川管内における位置</t>
+          <t>訪問介護の利用強度</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
@@ -5772,7 +5883,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも管内比較がある。</t>
+          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -5789,18 +5900,18 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の利用強度</t>
+          <t>町別の要介護認定者数</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
@@ -5810,7 +5921,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
+          <t>実績は町別に掲げる方針による。</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5938,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>町別の要介護認定者数</t>
+          <t>町別の給付費の実績</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
@@ -5860,23 +5971,23 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>町別の給付費の実績</t>
+          <t>事業所数と定員・給付の突合</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
@@ -5886,7 +5997,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>実績は町別に掲げる方針による。</t>
+          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -5903,14 +6014,14 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>事業所数と定員・給付の突合</t>
+          <t>職種別の状況（介護老人福祉施設）</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F20" s="17" t="inlineStr">
         <is>
@@ -5924,7 +6035,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
+          <t>基本指針別表 七（従事者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -5941,28 +6052,28 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>職種別の状況（介護老人福祉施設）</t>
+          <t>リハビリテーション専門職の配置</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>3</v>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（従事者数）に対応する。</t>
+          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
         </is>
       </c>
     </row>
@@ -5979,28 +6090,28 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>リハビリテーション専門職の配置</t>
+          <t>運営法人の状況</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
+          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
         </is>
       </c>
     </row>
@@ -6012,33 +6123,33 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>リハビリテーション関係の加算の算定状況</t>
+          <t>調査の対象者の範囲</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>加算の算定状況は事業所の運営に関する分析であり、計画の記載事項に当たらない。協議用の地域分析資料に移す。</t>
+          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
         </is>
       </c>
     </row>
@@ -6050,23 +6161,23 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>運営法人の状況</t>
+          <t>1　主要指標の状況</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
@@ -6076,7 +6187,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
+          <t>第9期計画にも調査結果の掲載がある。</t>
         </is>
       </c>
     </row>
@@ -6093,28 +6204,28 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>調査の対象者の範囲</t>
+          <t>2　年齢構成の影響と町間の差</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
+          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -6131,18 +6242,18 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>1　主要指標の状況</t>
+          <t>3　同規模の保険者との比較</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
@@ -6152,7 +6263,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも調査結果の掲載がある。</t>
+          <t>基本指針が地域間比較を求めている。</t>
         </is>
       </c>
     </row>
@@ -6169,11 +6280,11 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2　年齢構成の影響と町間の差</t>
+          <t>4　社会参加との関連</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>1</v>
@@ -6183,14 +6294,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
+          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -6207,11 +6318,11 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>3　同規模の保険者との比較</t>
+          <t>5　暮らし向きとの関連</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>1</v>
@@ -6221,14 +6332,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>基本指針が地域間比較を求めている。</t>
+          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6356,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>4　社会参加との関連</t>
+          <t>6　生活実態の主な値</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
@@ -6254,9 +6365,9 @@
       <c r="E29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr">
@@ -6266,7 +6377,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
+          <t>第9期計画の第2章にも生活実態の記載がある。</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6394,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>5　暮らし向きとの関連</t>
+          <t>7　地区別の状況</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
@@ -6304,7 +6415,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
+          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6432,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>6　生活実態の主な値</t>
+          <t>8　前回調査との比較</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
@@ -6342,7 +6453,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の第2章にも生活実態の記載がある。</t>
+          <t>経年比較は計画に置く。</t>
         </is>
       </c>
     </row>
@@ -6354,16 +6465,16 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>7　地区別の状況</t>
+          <t>重度者の在宅・居住系割合の上昇</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>1</v>
@@ -6373,14 +6484,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
+          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -6392,23 +6503,23 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>8　前回調査との比較</t>
+          <t>在宅生活の継続に必要な生活支援</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
@@ -6418,7 +6529,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>経年比較は計画に置く。</t>
+          <t>第5章 基本目標2・3の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -6430,16 +6541,16 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>重度者の在宅・居住系割合の上昇</t>
+          <t>第10期分の介護人材実態調査の結果</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>1</v>
@@ -6456,35 +6567,35 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
+          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>第2章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>在宅生活の継続に必要な生活支援</t>
+          <t>令和6年度の事業費（決算）</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
@@ -6494,35 +6605,35 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2・3の根拠となる。</t>
+          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>第2章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>第10期分の介護人材実態調査の結果</t>
+          <t>令和6年度の通いの場の展開状況</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
@@ -6532,45 +6643,45 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
+          <t>第9期計画にも通いの場の記載がある。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>第2章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>訪問介護事業所の全数把握</t>
+          <t>一般介護予防事業の実施状況（令和6年度）</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>調査の把握率に関する記述であり、調査の実施方法の説明に当たる。調査結果報告書に移す。</t>
+          <t>第9期計画にも実施状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -6582,206 +6693,206 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の事業費（決算）</t>
+          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G38" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>4</v>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
+          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の通いの場の展開状況</t>
+          <t>H07・H08・H12・H16の振替について</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G39" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも通いの場の記載がある。</t>
+          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>一般介護予防事業の実施状況（令和6年度）</t>
+          <t>H13・H14の定義変更について</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>0</v>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも実施状況の記載がある。</t>
+          <t>同上。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>基本目標5</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>第9期における確認内容と第10期への反映</t>
+          <t>介護給付費の適正化（第7期給付適正化計画）</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
+        <v>3</v>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>第9期の確認の経過であり、反映の結果だけを本文に残し、経過は評価の作業記録に移す。</t>
+          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
+          <t>要介護度別の認定者数</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F42" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
+          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>H01のデータ源について</t>
+          <t>認定率の置き方によるちがい</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>1</v>
@@ -6791,35 +6902,35 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>指標のデータ源の選定の経過であり、資料1（代表KPIの定義）に一本化する。</t>
+          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>H07・H08・H12・H16の振替について</t>
+          <t>人口の基礎による推計のちがい</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>1</v>
@@ -6836,69 +6947,69 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
+          <t>同上。案Cを採る理由の説明としては要る。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>H13・H14の定義変更について</t>
+          <t>見込量の算定方法</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G45" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>5</v>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>見込量の前提を示すもので、計画に置く。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第6章</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>基本目標5</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>介護給付費の適正化（第7期給付適正化計画）</t>
+          <t>利用回（日）数</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
@@ -6912,7 +7023,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
+          <t>法第117条第2項第1号が回数・日数を求めている。</t>
         </is>
       </c>
     </row>
@@ -6924,16 +7035,16 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>要介護度別の認定者数</t>
+          <t>介護予防・日常生活支援総合事業の量の見込み</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>1</v>
@@ -6950,7 +7061,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
+          <t>法第117条第2項第2号。</t>
         </is>
       </c>
     </row>
@@ -6962,33 +7073,33 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>認定率の置き方によるちがい</t>
+          <t>地域支援事業費</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G48" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>2</v>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
+          <t>法第117条第3項第2号。</t>
         </is>
       </c>
     </row>
@@ -7000,33 +7111,33 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎による推計のちがい</t>
+          <t>定員と見込量の照合</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G49" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F49" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>同上。案Cを採る理由の説明としては要る。</t>
+          <t>必要利用定員総数の算定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -7038,23 +7149,23 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定方法</t>
+          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>0</v>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
@@ -7064,7 +7175,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>見込量の前提を示すもので、計画に置く。</t>
+          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
         </is>
       </c>
     </row>
@@ -7076,33 +7187,33 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>利用回（日）数</t>
+          <t>供給の担い手の集中</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G51" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号が回数・日数を求めている。</t>
+          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
         </is>
       </c>
     </row>
@@ -7114,12 +7225,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業の量の見込み</t>
+          <t>現況（令和8年度）</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
@@ -7128,9 +7239,9 @@
       <c r="E52" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F52" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
@@ -7140,7 +7251,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号。</t>
+          <t>第9期計画にも現況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -7152,19 +7263,19 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業費</t>
+          <t>第10期における必要利用定員総数</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" s="17" t="inlineStr">
         <is>
@@ -7178,7 +7289,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号。</t>
+          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
         </is>
       </c>
     </row>
@@ -7190,23 +7301,23 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>定員と見込量の照合</t>
+          <t>入所の経路からみた整備の考え方</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>0</v>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
@@ -7216,7 +7327,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数の算定の根拠となる。</t>
+          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -7228,23 +7339,23 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
+          <t>第9期の状況</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
@@ -7254,7 +7365,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
+          <t>第9期計画にも前期の状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -7266,16 +7377,16 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>供給の担い手の集中</t>
+          <t>期別の必要保険料月額と基準額の対比</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>1</v>
@@ -7292,7 +7403,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -7304,16 +7415,16 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>現況（令和8年度）</t>
+          <t>介護給付費準備基金の状況</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" s="6" t="n">
         <v>1</v>
@@ -7330,7 +7441,7 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも現況の記載がある。</t>
+          <t>基金の取崩しは保険料の決定に直結する。</t>
         </is>
       </c>
     </row>
@@ -7342,20 +7453,20 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>第10期における必要利用定員総数</t>
+          <t>保険料収納率と所得段階別被保険者数の実績</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E58" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E58" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F58" s="17" t="inlineStr">
         <is>
           <t>法定</t>
@@ -7368,7 +7479,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
+          <t>保険料算定の基礎。</t>
         </is>
       </c>
     </row>
@@ -7380,33 +7491,33 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>入所の経路からみた整備の考え方</t>
+          <t>保険料と必要保険料月額との関係</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G59" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G59" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
         </is>
       </c>
     </row>
@@ -7423,18 +7534,18 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>第9期の状況</t>
+          <t>暫定算定</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -7444,7 +7555,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも前期の状況の記載がある。</t>
+          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
         </is>
       </c>
     </row>
@@ -7461,11 +7572,11 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
+          <t>給付費の置き方によるちがい</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E61" s="6" t="n">
         <v>1</v>
@@ -7482,7 +7593,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
         </is>
       </c>
     </row>
@@ -7499,28 +7610,28 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>見える化システムによる期別の保険料基準額</t>
+          <t>前提を動かした場合の幅</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>システムの出力の対比であり、当方の算定と重複する。協議用の保険料算定資料に移す。</t>
+          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
         </is>
       </c>
     </row>
@@ -7532,23 +7643,23 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第7節</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の状況</t>
+          <t>第10期に施行される見直し</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G63" s="17" t="inlineStr">
@@ -7558,35 +7669,31 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>基金の取崩しは保険料の決定に直結する。</t>
+          <t>令和8年3月課長会議資料により追加した。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="44" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>第6節</t>
-        </is>
-      </c>
+          <t>資料5</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr"/>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>保険料収納率と所得段階別被保険者数の実績</t>
+          <t>地域包括ケア「見える化」システムの使用データ</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F64" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -7596,28 +7703,24 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>保険料算定の基礎。</t>
+          <t>出典の明示に当たる。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="44" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>第6節</t>
-        </is>
-      </c>
+          <t>資料7</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr"/>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>比較結果の読み方</t>
+          <t>採番と表記の規則</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>0</v>
@@ -7627,277 +7730,19 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G65" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
+      <c r="G65" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>比較の方法の説明であり、計画の記載事項に当たらない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="44" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>第6章</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>第6節</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>保険料と必要保険料月額との関係</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F66" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G66" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="44" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>第6章</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>第6節</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>受託者による暫定算定</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G67" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>見出しに受託者が現れている。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。「暫定算定」として残し、暫定である旨は注記で示す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="44" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>第6章</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>第6節</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>給付費の置き方によるちがい</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E68" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G68" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="44" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>第6章</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>第6節</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>前提を動かした場合の幅</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="E69" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F69" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G69" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="44" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>第6章</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>第7節</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>第10期に施行される見直し</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E70" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G70" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>令和8年3月課長会議資料により追加した。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="44" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>資料5</t>
-        </is>
-      </c>
-      <c r="B71" s="5" t="inlineStr"/>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>地域包括ケア「見える化」システムの使用データ</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G71" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>出典の明示に当たる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="44" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>資料7</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr"/>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>採番と表記の規則</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G72" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
           <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="48" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
+    <row r="67" ht="48" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -7906,8 +7751,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A67:H67"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A74:H74"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7920,554 +7765,389 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>打合せ協議用への移行の検討</t>
+          <t>打合せ協議用への移行の記録と残る協議事項</t>
         </is>
       </c>
     </row>
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>判定が「移す」又は「協議」であるものについて、移す場合の移し先と、本文に残す内容を示す。移す場合も本文から内容が消えるのではなく、結論のみを残す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+          <t>令和8年9月29日のご指示（「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」）により、8件を計画素案から移した。移した内容は本文から消えるのではなく、結論のみを本文に残している。「協議」と判定した15件は素案に残したままとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>【令和8年9月29日に移した8件】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>移す前の【　】の見出し</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>移し先</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>計画素案の本文に残した内容</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>第1章</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>推計の見直しの手順</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>年次評価の実施要領</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>年齢階級別の認定率・認定者数・人口・給付費の4つを計画の前提と対比し、乖離が2年続いた場合は中間年（令和10年度）に推計を見直すこと、見直すのは認定率の前提であることを1段落で残した。確認の方法と見直しの基準の表は移した。</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>移した</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>第2章</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>第3節</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>リハビリテーション関係の加算の算定状況</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>見える化データの受領点検（福祉用具・住宅改修とリハビリテーション）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>11指標のうち6指標が全国の2倍以上であること、生活機能向上連携加算（全国比2.24）と入所前後訪問指導加算（同2.10）が住宅改修・福祉用具の点検につながることを1段落で残した。7指標の一覧表は移した。</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>移した</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>第2章</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護事業所の全数把握</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>実施済み調査 結果報告書</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護員等181人・利用者346人、8事業所（70.7％）が居住系の住まいに併設されていること、採用23人に対し退職28人であることを残した。調査の回答が3事業所にとどまり公表画面で補ったという把握の方法と、回答の有無別の内訳表は移した。</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>移した</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>第3章</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>第2節</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>第9期における確認内容と第10期への反映</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>第9期施策別評価表と暫定評価ルール</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>総合事業・包括的支援事業・任意事業それぞれを第10期において何により評価するかを1段落で残した。第9期における確認内容との対照表は移した。</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>移した</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>第4章</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>第3節</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>H01のデータ源について</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>資料1（代表KPI16項目の定義）</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>本文からは落とした。見える化B5-aを採らない理由（【注目する地域のみ】と【他地域と比較】の2系列があり他地域と比較できない）は資料1の算式・データ源の欄に集約した。</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>移した</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>見える化システムによる期別の保険料基準額</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第3段階（給付費と保険料）</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>第9期は実績が計画を下回り、乖離が標準給付費見込額に集中していること、実績から算定した令和6年度6,063円・令和7年度6,352円の平均6,208円が別の経路の値と0.2％の差で一致することを残した。期別の計画値・実績値の対照表は移した。</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>移した</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>比較結果の読み方</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第3段階（給付費と保険料）</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>箇条書き5件を1段落にまとめて残した（単純平均との差、保険料が受ける影響、給付水準が高い理由、サービス不足により低く見えることへの留意、第10期の要因分解）。</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>本文に残した（体裁のみ改めた）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>受託者による暫定算定</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>移していない（見出しの表現のみ改めた）</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>見出しを「暫定算定」に改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。暫定である旨は本文と注記で示している。</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>見出しを改めた</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
+注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
+注3）この移行により、計画素案は943段落147表から916段落141表36図（表6点の減）となった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>【「協議」と判定した15件（一旦そのまま素案に残す）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>節</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>【　】の見出し</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>移し先の案</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>本文に残す内容</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>本文に置く場合の考え方</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>移す場合の移し先の案</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>決定の主体</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>第1章</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>第6節</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>推計の見直しの手順</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>進行管理の実施要領（新規）</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>本文には「計画期間中に推計の前提が変わった場合は見直す」ことのみ残す。</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>受託者（ご了承を得て）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>第2章</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>第1節</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画及び社人研推計との関係</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>第2章</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>第3節</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>リハビリテーション専門職の配置</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>第2章</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>第3節</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>リハビリテーション関係の加算の算定状況</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>協議用の地域分析資料（既存の「見える化システムによる地域分析」）</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>本文にはリハビリテーション専門職の配置の状況のみ残す。</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>受託者（ご了承を得て）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>第2章</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>第4節</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>2　年齢構成の影響と町間の差</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>第2章</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>第4節</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>5　暮らし向きとの関連</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>第2章</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>第4節</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>7　地区別の状況</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>第2章</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>第6節</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>訪問介護事業所の全数把握</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>実施済み調査 結果報告書（既存）</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>本文には調査の把握率を注記として1行残す。</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>受託者（ご了承を得て）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>第3章</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>第2節</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>第9期における確認内容と第10期への反映</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の評価表（既存）</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>本文には第10期への反映の結果のみ残す。</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>受託者（ご了承を得て）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>第3章</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>第4節</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>第4章</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>第3節</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>H01のデータ源について</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>資料1（代表KPI16項目の定義）</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>資料1のデータ源の欄に集約する。第4章第3節からは落とす。</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>受託者（ご了承を得て）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>第4章</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>第3節</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>H07・H08・H12・H16の振替について</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>第4章</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>第3節</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>H13・H14の定義変更について</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>同上。</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -8477,25 +8157,21 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>認定率の置き方によるちがい</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+          <t>第9期計画及び社人研推計との関係</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
+          <t>資料編</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -8504,35 +8180,31 @@
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎による推計のちがい</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+          <t>リハビリテーション専門職の配置</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>同上。案Cを採る理由の説明としては要る。</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
+          <t>見える化データの受領点検</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -8541,7 +8213,7 @@
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -8551,25 +8223,21 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>供給の担い手の集中</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+          <t>2　年齢構成の影響と町間の差</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
+          <t>調査の集計分析報告書</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -8578,35 +8246,31 @@
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+          <t>5　暮らし向きとの関連</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
+          <t>調査の集計分析報告書</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -8615,109 +8279,97 @@
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>見える化システムによる期別の保険料基準額</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
+          <t>7　地区別の状況</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>協議用の保険料算定資料（新規）</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>本文には当方の算定による期別の対比のみ残す。</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>受託者（ご了承を得て）</t>
+          <t>調査の集計分析報告書</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>発注者</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>比較結果の読み方</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
+          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>協議用の保険料算定資料（新規）</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>本文には比較の結論のみ残す。</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>受託者（ご了承を得て）</t>
+          <t>第9期施策別評価表と暫定評価ルール</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>発注者</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>保険料と必要保険料月額との関係</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+          <t>H07・H08・H12・H16の振替について</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
+          <t>資料1（代表KPI16項目の定義）</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -8726,37 +8378,33 @@
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>受託者による暫定算定</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>移す</t>
+          <t>H13・H14の定義変更について</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>同上。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>移さない（見出しの表現のみ改める）</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>見出しを「暫定算定」に改め、暫定である旨は注記で示す。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>受託者（ご了承を得て）</t>
+          <t>資料1（代表KPI16項目の定義）</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>発注者</t>
         </is>
       </c>
     </row>
@@ -8768,30 +8416,26 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>給付費の置き方によるちがい</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+          <t>認定率の置き方によるちがい</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
+          <t>将来推計 人口と認定者数</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -8800,51 +8444,236 @@
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>第1節</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>人口の基礎による推計のちがい</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>同上。案Cを採る理由の説明としては要る。</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 人口と認定者数</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>第4節</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>供給の担い手の集中</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節に一本化する</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>期別の必要保険料月額と基準額の対比</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>資料編</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>保険料と必要保険料月額との関係</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第3段階（給付費と保険料）</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>給付費の置き方によるちがい</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>採用案の決定により1つに絞る</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>資料7</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>採番と表記の規則</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>（お決めいただく）</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>資料7の冒頭1段落に圧縮する</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>注1）「移す」と判定したものは、移し先の成果品に内容を移したうえで本文には結論のみを残す。移した後に計画素案を再出力する。
-注2）「協議」と判定したものは、既定値を「素案に残す」とする。打合せで「移す」とお決めいただいた場合に移す。
-注3）移す場合は、移した先の成果品名を計画素案の本文に書かない（計画の読み手に向けた記述ではないため）。
-注4）本シートの判定は確認事項No.170として業務工程管理表に登録している。体裁については確認事項No.171による。</t>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>注1）令和8年9月29日のご指示により、15件は一旦そのまま計画素案に残している。「移す場合の移し先の案」は、後日移すこととなった場合の候補である。
+注2）確認事項No.170として業務工程管理表に登録している。体裁（小見出し【　】の階層ほか）は保留となっており、確認事項No.171による。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="29">
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>0</v>
@@ -1027,7 +1027,7 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から916段落141表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から927段落143表36図となった（表6点の減）。
 「協議」と判定した15件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表141表／実物141表</t>
+          <t>本表143表／実物143表</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表721段落（空段落・目次の行を除く）／実物916段落（すべて）</t>
+          <t>本表730段落（空段落・目次の行を除く）／実物927段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>61件</t>
+          <t>63件</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>11／15件</t>
+          <t>13／17件</t>
         </is>
       </c>
       <c r="E29" s="17" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>15件（全61件）</t>
+          <t>15件（全63件）</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>10件</t>
+          <t>11件</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
@@ -2187,16 +2187,16 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
     </row>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>2</v>
@@ -3272,16 +3272,16 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
     </row>
@@ -4832,7 +4832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5230,22 +5230,22 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>高齢者居住安定確保計画との連携（第3項第8号）</t>
+          <t>被保険者の意見を反映させるために必要な措置</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>北海道の高齢者居住安定確保計画との連携に関する記述がない。介護保険の指定を受けない住まいの状況は把握できている。</t>
+          <t>介護保険法第117条は、計画を定め又は変更しようとするときは、あらかじめ被保険者の意見を反映させるために必要な措置を講ずること及び都道府県の意見を聴くことを定めているが、素案に記載がなかった。意見公募手続・認知症の人及びその家族等からの意見の聴取・北海道の意見の聴取・計画の公表の4件を表に掲げた。条文を受領していないため項番号は書いていない［要確認］。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>第1章第8節、第5章 基本目標3</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>未追加。北海道の計画の改定時期の確認を要する</t>
+          <t>第1章第5節（【法令が定める手続】を新設）</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>追加済み（令和8年9月29日）</t>
         </is>
       </c>
     </row>
@@ -5255,27 +5255,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>A 法第117条</t>
+          <t>B 別表／基本指針</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数（第2項第1号）</t>
+          <t>認知症高齢者の状況</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>現定員の据置き案を掲げるにとどまり［要協議］のまま残している。日常生活圏域の設定と一体で決定を要する。</t>
+          <t>基本指針は2040年に向けて認知症高齢者が増えることを主要なテーマとしているが、素案には認知症高齢者の日常生活自立度の状況がなかった。自立度Ⅱ以上は平成24年10月末1,190人から令和6年10月末1,498人へ25.9％増える一方、認定者に占める割合は65.5％から60.3％へ低下している。割合の低下をもって需要が減っているとは読まないことを明記した。</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>第6章第4節4</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>決定待ち（確認事項No.88）</t>
+          <t>第2章第1節3（【認知症高齢者の状況】を新設）</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>追加済み（令和8年9月29日）</t>
         </is>
       </c>
     </row>
@@ -5290,22 +5290,22 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>見込量の確保のための方策（第3項第3号）</t>
+          <t>高齢者居住安定確保計画との連携（第3項第8号）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策が選択肢の提示にとどまる。</t>
+          <t>北海道の高齢者居住安定確保計画との連携に関する記述がない。介護保険の指定を受けない住まいの状況は把握できている。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>第6章第4節1</t>
+          <t>第1章第8節、第5章 基本目標3</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>決定待ち（確認事項No.88・No.84）</t>
+          <t>未追加。北海道の計画の改定時期の確認を要する</t>
         </is>
       </c>
     </row>
@@ -5315,32 +5315,92 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
+          <t>A 法第117条</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>必要利用定員総数（第2項第1号）</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>現定員の据置き案を掲げるにとどまり［要協議］のまま残している。日常生活圏域の設定と一体で決定を要する。</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>第6章第4節4</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>決定待ち（確認事項No.88）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>A 法第117条</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>見込量の確保のための方策（第3項第3号）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>24時間対応サービスの確保方策が選択肢の提示にとどまる。</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>第6章第4節1</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>決定待ち（確認事項No.88・No.84）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
           <t>B 別表</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>点検ツール（8シート）による第9期の点検</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>国が提供する点検ツールを用いた第9期計画の点検結果を第10期計画に反映することが求められているが、ツールが未受領である。</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>第3章第4節</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>未受領。提供され次第、評価に加えるかを協議する</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>注）本シートは記載漏れと追加の対応を記録するものである。追加済みのものは計画素案に反映済みであり、決定待ち・未受領のものは確認事項として管理している。</t>
         </is>
@@ -5349,8 +5409,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5362,7 +5422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5439,23 +5499,23 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>年次の進行管理の手順</t>
+          <t>法令が定める手続</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G5" s="17" t="inlineStr">
@@ -5465,7 +5525,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第9号の進行管理に当たる。第9期計画にPDCAの記述はあるが年次の手順はない。国が第10期計画でPDCAの充実を求めているため計画に置く。</t>
+          <t>介護保険法第117条が定める手続（被保険者の意見の反映・都道府県の意見の聴取・公表）である。令和8年9月29日に新設した。</t>
         </is>
       </c>
     </row>
@@ -5477,23 +5537,23 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の考え方</t>
+          <t>年次の進行管理の手順</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -5503,7 +5563,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 一（地勢と交通）に対応する。日常生活圏域の設定の根拠となる。</t>
+          <t>法第117条第3項第9号の進行管理に当たる。第9期計画にPDCAの記述はあるが年次の手順はない。国が第10期計画でPDCAの充実を求めているため計画に置く。</t>
         </is>
       </c>
     </row>
@@ -5520,18 +5580,18 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>通常の事業の実施地域による確認</t>
+          <t>訪問・通所困難地域の考え方</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>0</v>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G7" s="17" t="inlineStr">
@@ -5541,7 +5601,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>圏域設定の根拠を指定事業所の実施地域から確かめたもの。必要利用定員総数の圏域別の配分の前提となるため計画に置く。</t>
+          <t>基本指針別表 一（地勢と交通）に対応する。日常生活圏域の設定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -5553,23 +5613,23 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>第8節</t>
+          <t>第7節</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>北海道第9期計画の基本目標との対応</t>
+          <t>通常の事業の実施地域による確認</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -5579,7 +5639,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>都道府県計画との調和は法第117条第9項による。</t>
+          <t>圏域設定の根拠を指定事業所の実施地域から確かめたもの。必要利用定員総数の圏域別の配分の前提となるため計画に置く。</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5656,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>「市町村数」を単位とする指標の読替え</t>
+          <t>北海道第9期計画の基本目標との対応</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
@@ -5605,9 +5665,9 @@
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G9" s="17" t="inlineStr">
@@ -5617,7 +5677,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>北海道計画の指標が市町村数を単位とするため、広域連合として読み替える必要がある。分量は3行にとどまる。</t>
+          <t>都道府県計画との調和は法第117条第9項による。</t>
         </is>
       </c>
     </row>
@@ -5629,23 +5689,23 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>第9節</t>
+          <t>第8節</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2040年を見据えた地域類型の考え方</t>
+          <t>「市町村数」を単位とする指標の読替え</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -5655,7 +5715,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。</t>
+          <t>北海道計画の指標が市町村数を単位とするため、広域連合として読み替える必要がある。分量は3行にとどまる。</t>
         </is>
       </c>
     </row>
@@ -5672,11 +5732,11 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>医療と介護の協議の場の再編成</t>
+          <t>2040年を見据えた地域類型の考え方</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>0</v>
@@ -5710,14 +5770,14 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）に係る特例の創設</t>
+          <t>医療と介護の協議の場の再編成</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
@@ -5731,35 +5791,35 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>令和9年4月施行。第10期の初年度から適用される。</t>
+          <t>令和8年3月課長会議資料により追加した。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>第2章</t>
+          <t>第1章</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第9節</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>第10期の人口の基礎</t>
+          <t>中山間・人口減少地域（特定地域）に係る特例の創設</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G13" s="17" t="inlineStr">
@@ -5769,7 +5829,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>推計の基礎を示すもので、見込量の前提として要る。</t>
+          <t>令和9年4月施行。第10期の初年度から適用される。</t>
         </is>
       </c>
     </row>
@@ -5786,28 +5846,28 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>第9期計画及び社人研推計との関係</t>
+          <t>第10期の人口の基礎</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
+          <t>推計の基礎を示すもので、見込量の前提として要る。</t>
         </is>
       </c>
     </row>
@@ -5819,33 +5879,33 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上川管内における位置</t>
+          <t>第9期計画及び社人研推計との関係</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>5</v>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも管内比較がある。</t>
+          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
         </is>
       </c>
     </row>
@@ -5857,23 +5917,23 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の利用強度</t>
+          <t>認知症高齢者の状況</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>2</v>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
@@ -5883,7 +5943,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
+          <t>国の第10期基本指針が主要テーマとする事項である。法第117条第3項第6号（認知症である被保険者の支援）の前提となる。令和8年9月29日に新設した。</t>
         </is>
       </c>
     </row>
@@ -5900,14 +5960,14 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>町別の要介護認定者数</t>
+          <t>上川管内における位置</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
@@ -5921,7 +5981,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>実績は町別に掲げる方針による。</t>
+          <t>第9期計画にも管内比較がある。</t>
         </is>
       </c>
     </row>
@@ -5938,18 +5998,18 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>町別の給付費の実績</t>
+          <t>訪問介護の利用強度</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>3</v>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
@@ -5959,7 +6019,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>実績は町別に掲げる方針による。</t>
+          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -5971,23 +6031,23 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>事業所数と定員・給付の突合</t>
+          <t>町別の要介護認定者数</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
@@ -5997,7 +6057,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
+          <t>実績は町別に掲げる方針による。</t>
         </is>
       </c>
     </row>
@@ -6009,23 +6069,23 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>職種別の状況（介護老人福祉施設）</t>
+          <t>町別の給付費の実績</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
@@ -6035,7 +6095,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（従事者数）に対応する。</t>
+          <t>実績は町別に掲げる方針による。</t>
         </is>
       </c>
     </row>
@@ -6052,28 +6112,28 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>リハビリテーション専門職の配置</t>
+          <t>事業所数と定員・給付の突合</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>4</v>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
+          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -6090,18 +6150,18 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>運営法人の状況</t>
+          <t>職種別の状況（介護老人福祉施設）</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
@@ -6111,7 +6171,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
+          <t>基本指針別表 七（従事者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -6123,33 +6183,33 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>調査の対象者の範囲</t>
+          <t>リハビリテーション専門職の配置</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
+          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
         </is>
       </c>
     </row>
@@ -6161,23 +6221,23 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>1　主要指標の状況</t>
+          <t>運営法人の状況</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>3</v>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
@@ -6187,7 +6247,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも調査結果の掲載がある。</t>
+          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
         </is>
       </c>
     </row>
@@ -6204,28 +6264,28 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2　年齢構成の影響と町間の差</t>
+          <t>調査の対象者の範囲</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
+          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
         </is>
       </c>
     </row>
@@ -6242,18 +6302,18 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>3　同規模の保険者との比較</t>
+          <t>1　主要指標の状況</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
@@ -6263,7 +6323,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>基本指針が地域間比較を求めている。</t>
+          <t>第9期計画にも調査結果の掲載がある。</t>
         </is>
       </c>
     </row>
@@ -6280,11 +6340,11 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>4　社会参加との関連</t>
+          <t>2　年齢構成の影響と町間の差</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>1</v>
@@ -6294,14 +6354,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
+          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -6318,11 +6378,11 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>5　暮らし向きとの関連</t>
+          <t>3　同規模の保険者との比較</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>1</v>
@@ -6332,14 +6392,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
+          <t>基本指針が地域間比較を求めている。</t>
         </is>
       </c>
     </row>
@@ -6356,7 +6416,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>6　生活実態の主な値</t>
+          <t>4　社会参加との関連</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
@@ -6365,9 +6425,9 @@
       <c r="E29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G29" s="17" t="inlineStr">
@@ -6377,7 +6437,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の第2章にも生活実態の記載がある。</t>
+          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6454,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>7　地区別の状況</t>
+          <t>5　暮らし向きとの関連</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
@@ -6415,7 +6475,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
+          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6492,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>8　前回調査との比較</t>
+          <t>6　生活実態の主な値</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
@@ -6453,7 +6513,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>経年比較は計画に置く。</t>
+          <t>第9期計画の第2章にも生活実態の記載がある。</t>
         </is>
       </c>
     </row>
@@ -6465,16 +6525,16 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>重度者の在宅・居住系割合の上昇</t>
+          <t>7　地区別の状況</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>1</v>
@@ -6484,14 +6544,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
+          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
         </is>
       </c>
     </row>
@@ -6503,23 +6563,23 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>在宅生活の継続に必要な生活支援</t>
+          <t>8　前回調査との比較</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr">
@@ -6529,7 +6589,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2・3の根拠となる。</t>
+          <t>経年比較は計画に置く。</t>
         </is>
       </c>
     </row>
@@ -6541,16 +6601,16 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>第10期分の介護人材実態調査の結果</t>
+          <t>重度者の在宅・居住系割合の上昇</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>1</v>
@@ -6567,35 +6627,35 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
+          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の事業費（決算）</t>
+          <t>在宅生活の継続に必要な生活支援</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
@@ -6605,35 +6665,35 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
+          <t>第5章 基本目標2・3の根拠となる。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の通いの場の展開状況</t>
+          <t>第10期分の介護人材実態調査の結果</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
@@ -6643,7 +6703,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも通いの場の記載がある。</t>
+          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6720,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>一般介護予防事業の実施状況（令和6年度）</t>
+          <t>令和6年度の事業費（決算）</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
@@ -6669,9 +6729,9 @@
       <c r="E37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
@@ -6681,7 +6741,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも実施状況の記載がある。</t>
+          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
         </is>
       </c>
     </row>
@@ -6693,50 +6753,50 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
+          <t>令和6年度の通いの場の展開状況</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F38" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
+          <t>第9期計画にも通いの場の記載がある。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>H07・H08・H12・H16の振替について</t>
+          <t>一般介護予防事業の実施状況（令和6年度）</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
@@ -6745,43 +6805,43 @@
       <c r="E39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G39" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
+          <t>第9期計画にも実施状況の記載がある。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>H13・H14の定義変更について</t>
+          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
@@ -6795,121 +6855,121 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>基本目標5</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>介護給付費の適正化（第7期給付適正化計画）</t>
+          <t>H07・H08・H12・H16の振替について</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G41" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>1</v>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
+          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>要介護度別の認定者数</t>
+          <t>H13・H14の定義変更について</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>0</v>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
+          <t>同上。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>基本目標5</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>認定率の置き方によるちがい</t>
+          <t>介護給付費の適正化（第7期給付適正化計画）</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E43" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G43" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
+          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
         </is>
       </c>
     </row>
@@ -6926,28 +6986,28 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎による推計のちがい</t>
+          <t>要介護度別の認定者数</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G44" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G44" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>同上。案Cを採る理由の説明としては要る。</t>
+          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
         </is>
       </c>
     </row>
@@ -6959,33 +7019,33 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定方法</t>
+          <t>認定率の置き方によるちがい</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>1</v>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>見込量の前提を示すもので、計画に置く。</t>
+          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
         </is>
       </c>
     </row>
@@ -6997,33 +7057,33 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>利用回（日）数</t>
+          <t>人口の基礎による推計のちがい</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G46" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号が回数・日数を求めている。</t>
+          <t>同上。案Cを採る理由の説明としては要る。</t>
         </is>
       </c>
     </row>
@@ -7035,19 +7095,19 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業の量の見込み</t>
+          <t>見込量の算定方法</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
@@ -7061,7 +7121,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号。</t>
+          <t>見込量の前提を示すもので、計画に置く。</t>
         </is>
       </c>
     </row>
@@ -7073,19 +7133,19 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業費</t>
+          <t>利用回（日）数</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" s="17" t="inlineStr">
         <is>
@@ -7099,7 +7159,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号。</t>
+          <t>法第117条第2項第1号が回数・日数を求めている。</t>
         </is>
       </c>
     </row>
@@ -7111,16 +7171,16 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>定員と見込量の照合</t>
+          <t>介護予防・日常生活支援総合事業の量の見込み</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>1</v>
@@ -7137,7 +7197,7 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数の算定の根拠となる。</t>
+          <t>法第117条第2項第2号。</t>
         </is>
       </c>
     </row>
@@ -7149,23 +7209,23 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
+          <t>地域支援事業費</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>2</v>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
@@ -7175,7 +7235,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
+          <t>法第117条第3項第2号。</t>
         </is>
       </c>
     </row>
@@ -7192,28 +7252,28 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>供給の担い手の集中</t>
+          <t>定員と見込量の照合</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G51" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G51" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
+          <t>必要利用定員総数の算定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -7230,18 +7290,18 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>現況（令和8年度）</t>
+          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F52" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
@@ -7251,7 +7311,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも現況の記載がある。</t>
+          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
         </is>
       </c>
     </row>
@@ -7268,28 +7328,28 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>第10期における必要利用定員総数</t>
+          <t>供給の担い手の集中</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G53" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G53" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
+          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
         </is>
       </c>
     </row>
@@ -7301,23 +7361,23 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>入所の経路からみた整備の考え方</t>
+          <t>現況（令和8年度）</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
@@ -7327,7 +7387,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
+          <t>第9期計画にも現況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7399,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>第9期の状況</t>
+          <t>第10期における必要利用定員総数</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
@@ -7353,9 +7413,9 @@
       <c r="E55" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
@@ -7365,7 +7425,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも前期の状況の記載がある。</t>
+          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
         </is>
       </c>
     </row>
@@ -7377,33 +7437,33 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
+          <t>入所の経路からみた整備の考え方</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G56" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -7420,11 +7480,11 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の状況</t>
+          <t>第9期の状況</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E57" s="6" t="n">
         <v>1</v>
@@ -7441,7 +7501,7 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>基金の取崩しは保険料の決定に直結する。</t>
+          <t>第9期計画にも前期の状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -7458,28 +7518,28 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>保険料収納率と所得段階別被保険者数の実績</t>
+          <t>期別の必要保険料月額と基準額の対比</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>1</v>
+      </c>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G58" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>保険料算定の基礎。</t>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -7496,28 +7556,28 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>保険料と必要保険料月額との関係</t>
+          <t>介護給付費準備基金の状況</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E59" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F59" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G59" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
+          <t>基金の取崩しは保険料の決定に直結する。</t>
         </is>
       </c>
     </row>
@@ -7534,18 +7594,18 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>暫定算定</t>
+          <t>保険料収納率と所得段階別被保険者数の実績</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>2</v>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -7555,7 +7615,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
+          <t>保険料算定の基礎。</t>
         </is>
       </c>
     </row>
@@ -7572,14 +7632,14 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>給付費の置き方によるちがい</t>
+          <t>保険料と必要保険料月額との関係</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
@@ -7593,7 +7653,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
         </is>
       </c>
     </row>
@@ -7610,14 +7670,14 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>前提を動かした場合の幅</t>
+          <t>暫定算定</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
@@ -7631,7 +7691,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
         </is>
       </c>
     </row>
@@ -7643,53 +7703,57 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>第10期に施行される見直し</t>
+          <t>給付費の置き方によるちがい</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E63" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G63" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G63" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。</t>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="44" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>資料5</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの使用データ</t>
+          <t>前提を動かした場合の幅</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
@@ -7703,46 +7767,118 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>出典の明示に当たる。</t>
+          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="44" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>第7節</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>第10期に施行される見直し</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>令和8年3月課長会議資料により追加した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="44" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>資料5</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr"/>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>地域包括ケア「見える化」システムの使用データ</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>出典の明示に当たる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="44" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
           <t>資料7</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr"/>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr"/>
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>採番と表記の規則</t>
         </is>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D67" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E67" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F65" s="20" t="inlineStr">
+      <c r="F67" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G65" s="20" t="inlineStr">
+      <c r="G67" s="20" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="48" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
+    <row r="69" ht="48" customHeight="1">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -7751,8 +7887,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A67:H67"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8100,7 +8236,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から916段落141表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から927段落143表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>
@@ -8685,7 +8821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8967,27 +9103,52 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
+          <t>資料編の構成</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>第9期計画には、意見公募手続の実施状況、策定委員会の委嘱期間・組織・委員名簿・開催の状況、用語解説、区域内の事業所一覧を資料編に掲げる例がある。</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>現在の素案の資料編は資料1〜7であり、代表KPIの定義・構成3町との役割分担・年次評価スコアカード・施策の採否基準・主な参照資料・基本指針の別表への対応・図表番号一覧からなる。上記4件はいずれもない。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>意見公募手続の実施状況は手続を行った後でなければ書けないため、計画として確定する段階で加える。用語解説と事業所一覧を加えるかはご判断による。委員名簿は氏名を掲げるため、個人情報を収録しない方針との関係を確認したうえでお決めいただく［要協議］。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>他団体の固有名称</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>協議用の資料には掲げてよいが、計画素案には掲げない。</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>計画素案に他の団体の名が現れないことは自己点検で確かめている。掲げてよいこととなった場合は、協議用の様式をそのまま計画に流用できるよう表の作りをそろえている。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>注）第9期計画の図表レイアウト・フォント・表の体裁を維持することは発注者の指示による。第9期計画にない体裁を用いる場合は、その必要があることを示したうえでお決めいただく。</t>
         </is>
@@ -8995,8 +9156,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -16,7 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_独自に加えた記載の棚卸し" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_協議用への移行の記録" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_記載する場合の体裁" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_自己点検" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_他計画との対比と視認性" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_レッドチームによる点検" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_協議用素案と公表版の切り分け" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_自己点検" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -690,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -1027,7 +1030,7 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から927段落143表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から928段落143表36図となった（表6点の減）。
 「協議」と判定した15件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -1075,7 +1078,1243 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>他の計画を比較材料とした視認性・図表レイアウト・記載内容の点検</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>他の広域行政組合が策定した介護保険事業計画（第9期）を比較材料としてのみ読み、当方の計画素案に不足している点を洗い出した。記載の借用は行わず、気づいた点はいずれも原典（介護保険法・国の基本指針・第9期計画の体裁）で確かめてから扱う。団体名は掲げない。作業の終了後に当該資料は消去する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>当方に不足していた点・気づいた点</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>行ったこと</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>視認性</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>表が紙面をまたぐとき、見出し行が次のページで繰り返されていなかった。12ページに及ぶ表もあり、何の列か分からないまま読むことになる。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>表の見出し行に繰返しの設定を加え、行の途中で改ページしないようにした。</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>計画素案・公表版の全表</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>是正した</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>視認性</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>表の見出し行に地色がなく、本文の表と見分けがつきにくい。比較材料の計画は表頭に淡い色を敷いている。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>表頭に淡い青の地色を敷き、中央寄せの太字とした。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>計画素案・公表版の全表</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>是正した</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>視認性</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>本文の行間が詰まっており、1ページの文字数が多い。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>本文の行間を1.12とし、小見出しの前に余白を置いた。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>計画素案・公表版の本文</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>是正した</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>視認性</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>節の冒頭にいきなり箇条書きが置かれ、何の一覧か分からない箇所があった（第1章第9節）。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>箇条書きの前に、何を掲げたものかを述べる1段落を置いた。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第9節</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>是正した</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>図表レイアウト</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>章の見出しに装飾がなく、章の変わり目が紙面で分かりにくい。比較材料の計画は章の見出しを帯で示している。</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>公表版の章の見出しに上下の罫線と淡い地色を付け、中央寄せとした。協議用素案は第9期計画の体裁を維持するため変更していない。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>公表版の全章</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>公表版のみ是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>図表レイアウト</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>サービス見込量を1つの大きな表にまとめており、サービスごとの推移が読み取りにくい。比較材料の計画はサービスごとに、内容の説明・実績と見込みの表・給付費と人数を重ねたグラフを1組にして並べている。</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>サービスの内容の説明を公表版に加えた。サービスごとのグラフは、採用する見込量が確定した後に作成する。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>公表版 参考・第6章第2節</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>記載内容</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>介護サービスの内容（どのようなサービスかの説明）がない。読み手が見込量の表だけを見ても内容が分からない。</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>公表版の巻末に29区分のサービスの内容を加えた。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>公表版 参考</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>是正した</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>記載内容</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>用語の解説がない。要介護認定・地域支援事業・補足給付・調整交付金など、読み手になじみのない語が本文に多い。</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>公表版の巻末に用語の解説を加えた。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>公表版 用語の解説</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>是正した</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>記載内容</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>被保険者の意見を反映させるために必要な措置の記載がなかった。</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法第117条により確かめたうえで、意見公募手続・認知症の人及びその家族等からの意見の聴取・北海道の意見の聴取・公表の4件を表に掲げた。</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第5節</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>是正した</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>記載内容</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>認知症高齢者の日常生活自立度の状況がなかった。</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>自立度Ⅱ以上の人数と認定者に占める割合の推移を加えた。割合の低下をもって需要が減っているとは読まないことを明記した。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第1節3</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>是正した</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>記載内容</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>計画の本文に受託者を主語とする語が残っていた（小見出し・年次評価の実施主体・推計の案）。計画は広域連合が定めるものである。</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>小見出しを改め、実施主体から受託者を外し、「受託者の案とします」を「案を示しています」に改めた。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第2節・第6章第6節・資料3</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>是正した</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>記載内容</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>本文に「本素案」「修正指示書」という語が残っていた。いずれも計画そのものの語ではない。</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>「本計画」に改め、内部の作業物の名を落とした。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第9節・資料7</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>是正した</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>記載内容</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>意見公募手続の実施状況・策定委員会の委嘱期間と委員名簿・用語解説・区域内の事業所一覧が資料編にない。比較材料の計画はいずれも資料編に掲げている。</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>用語の解説は公表版に加えた。他の3件は確認事項No.171によりお決めいただく。委員名簿は氏名を掲げるため個人情報の取扱いの確認を要する。</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>資料編</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>一部対応・協議</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>体裁の裏づけ</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>小見出しに【　】を用いることは第9期計画にない体裁であると整理していたが、第9期計画は【　】を図表のキャプションとして用いている（資料7）。比較材料の計画も【　】を図表のキャプション及び「今後の方向性」等の定型の小見出しに用いており、この様式の計画では一般的である。</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.171の判断材料として記録する。【　】そのものが第9期計画にない体裁なのではなく、分析のまとまりの小見出しとして用いることが新しい。</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 全体</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>記録した</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>図表レイアウト</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>図表に通し番号を付けている。第9期計画及び比較材料の計画は図表に番号を付けていない。</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>第10期では本文・別冊の図表集で同じ番号を用いるため付している（資料7）。変更しない。</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 資料7</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>変更しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>注1）比較材料とした計画は成果品に用いず、記載の借用も行わない。団体名は掲げない。作業の終了後に消去する（発注者指示）。
+注2）気づいた点は、いずれも原典（介護保険法・国の基本指針・第9期計画の体裁）で確かめてから扱っている。比較材料は「当方に何がないか」に気づくために用い、「どう書くか」は原典から決める。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>レッドチームによる点検</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>作成した版を、あら探しの側から読み直した結果である。見つかったものはいずれも是正し、同じ誤りが再び出ないよう自己点検に置いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>見た観点</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>見つかったこと・危ないこと</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>手立て</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>点検の置き場所</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>文字化け</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>公表版に加えたサービスの内容の説明に、日本語でない文字が2か所混じっていた（英単語1件・他の言語の文字1件）。書き下ろした文章は機械で読み合わせないと気づかない。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>該当の2か所を直し、日本語以外の文字が混じっていないことを自己点検に置いた。</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>公表版の自己点検17.5</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>節の消失</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>公表版を作る際、本文の末尾の分析のまとまりを落としたところ、本文の終わりに置かれている節の区切りまで一緒に落ちてしまい、ヘッダー・フッター・ページ番号が失われた。見た目では気づきにくい。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>落とす範囲を段落と表に限り、節の区切りで必ず止めるようにした。節の数が協議用素案と一致することを自己点検に置いた。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>公表版の自己点検0</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>内部の語</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>計画の本文に「受託者」「本素案」「修正指示書」が残っていた。計画は広域連合が定めるものであり、受託者を主語とする語や内部の作業物の名を置かない。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>3語を落とし、公表版の自己点検で走査する語に加えた。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>公表版の自己点検13</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>表の可読性</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>12ページに及ぶ表が見出し行の繰返しなしで分割されていた。何の列か分からないまま読むことになる。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>見出し行の繰返しと行の分割禁止を加え、設定されている表の数を自己点検に置いた。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>公表版の自己点検17</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>版の取違え</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>公表版と協議用素案で内容が食い違うと、どちらが正しいか分からなくなる。</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>公表版は協議用素案（docx）を読んで組み替える形とし、本文・数値を別に持たないようにした。協議用素案を改めれば公表版も追随する。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>公表版の作り</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>設計で防いだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>未確定のまま公表</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所（［要協議］等）が残ったまま公表版が公表できる版に見えると誤解を生む。</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所が1つでも残る間は表紙に「体裁確認用」と記し、0になったときだけ外れるようにした。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>公表版の表紙・自己点検12</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>設計で防いだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>落とし過ぎ</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>公表版から分析を落とす際、落としてはならない法定記載事項まで落とすと計画が成り立たない。</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>落とすのは判定が「協議」であるものに限り、落とした件数が判定の件数と一致すること、落としていない小見出しが残っていることを自己点検に置いた。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>公表版の自己点検3・4・5</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>設計で防いだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>目次のずれ</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>公表版は分析を落とし巻末を加えるため、協議用素案の目次のページ番号がそのままでは合わない。</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>公表版の目次を作り直し、組版結果からページ番号を求める形にした（ページ番号が変わらなくなるまで繰り返す）。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>公表版の目次・自己点検10</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>是正</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>個人情報</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>公表版は広く配る版であるため、個人情報が残っていないことを確かめる必要がある。</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>電話番号とメールアドレスの形（正規表現）で走査し、0件であることを自己点検に置いた。</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>公表版の自己点検16</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>設計で防いだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>他団体名</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>比較材料とした計画の団体名が紛れ込むと発注者指示に反する。</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>団体名を語で走査し、0件であることを自己点検に置いた。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>公表版の自己点検15</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>設計で防いだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>注）1と2は実際に起きた誤りであり、自己点検が不適合になる形にして再発を止めている。3と4は読み直して見つけたものである。5から10は、起こると重いものについてあらかじめ点検を置いたものである。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>協議用素案と公表版の切り分け</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>令和8年9月29日のご指示により、協議用素案と併せて公表に用いる版を作成した。内容の正本は協議用素案であり、公表版は協議用素案を読んで組み替えたものである。本文・数値を別に持たないため、協議用素案を改めれば公表版も追随する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>協議用素案</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>公表版</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>読み手</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>打合せでご判断いただく方（発注者・構成3町）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>計画をお読みになる方（住民・策定委員会の委員）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>表題</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>第10期介護保険事業計画／協議用素案（令和8年9月時点）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>第10期介護保険事業計画（案）／公表版（未確定箇所が残る間は「公表版（体裁確認用）」）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所が0になった時点で表紙の記載が変わる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>当方の分析</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>複数の置き方の対比・感度・推計の前提を残す</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>落とす（判定が「協議」である15件）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>落とすのは分析のまとまりであり、結論は本文に残っている</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>未確定箇所</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>［要協議］［要確認］［要内訳］を本文に残す</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>同左（公表できる版ではないことを表紙で示す）</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>決定後にすべて解消する</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>サービスの内容</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>掲げない</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>29区分のサービスの内容を巻末に掲げる</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法及び国が定める基準による</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>用語の解説</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>掲げない</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>巻末に掲げる</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>章の見出し</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>第9期計画の体裁を維持する</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>上下の罫線と淡い地色の帯を付ける</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>体裁は確認事項No.171</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>表の体裁</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>表頭に淡い地色。見出し行を各ページで繰り返す。行を分割しない</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>同左</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>視認性の是正（09シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>目次</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>章・節を同じ階層で並べる</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>節を字下げして階層を分ける</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>図表番号</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>図Nの通し番号を付す</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>同左</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>資料7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>注1）公表版は協議用素案から組み替えたものであり、数値・本文を別に持たない。2つの版に別の答えが並ぶことはない。
+注2）公表版から落とした15件は、協議用素案には残っている（ご指示により一旦そのまま）。計画に置くか協議用の資料へ移すかは確認事項No.170による。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1192,7 +2431,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表730段落（空段落・目次の行を除く）／実物927段落（すべて）</t>
+          <t>本表731段落（空段落・目次の行を除く）／実物928段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -1971,6 +3210,206 @@
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>公表版が生成されていること</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>ファイルの有無</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>公表版から「協議」と判定した分析が落ちていること</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>残っているもの</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>残っていない</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>公表版に「協議用素案」「受託者」「本素案」が現れないこと</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>走査</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>現れない</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>公表版にサービスの内容と用語の解説があること</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>走査</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>サービスの内容 あり／用語の解説 あり</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>公表版の節（ヘッダー・フッター）が協議用素案と同じ数であること</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>節の数</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>協議用2／公表版2</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>公表版の表の見出し行が各ページで繰り返される設定であること</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>設定のある表の数</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>133／133表</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>計画素案の本文に受託者を主語とする語がないこと</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>走査</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>現れない</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>計画素案の表の見出し行が各ページで繰り返される設定であること</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>設定のある表の数</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>143／143表</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2287,7 +3726,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>5</v>
@@ -3272,7 +4711,7 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>143</v>
@@ -4126,7 +5565,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>地域包括支援センターの相談体制（F15～F25）及び多様なサービス・活動の数（F28～F40）は再出力を依頼中</t>
+          <t>地域包括支援センターの相談体制（F15～F25）及び多様なサービス・活動の数（F28～F40）はデータの登録を進める</t>
         </is>
       </c>
     </row>
@@ -4153,7 +5592,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>介護報酬側のO1～O3・O6～O13は再出力を依頼中。診療報酬側のL20～L26はデータ登録がない。上川中部圏域の医療機関への照会で補う</t>
+          <t>介護報酬側のO1～O3・O6～O13はデータの登録を進める。診療報酬側のL20～L26はデータ登録がない。上川中部圏域の医療機関への照会で補う</t>
         </is>
       </c>
     </row>
@@ -8236,7 +9675,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から927段落143表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から928段落143表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>台帳171件</t>
+          <t>台帳173件</t>
         </is>
       </c>
       <c r="E27" s="17" t="inlineStr">

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>17</v>
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -1008,16 +1008,16 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -1030,8 +1030,8 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から928段落143表36図となった（表6点の減）。
-「協議」と判定した15件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から942段落145表36図となった（表6点の減）。
+「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表143表／実物143表</t>
+          <t>本表145表／実物145表</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表731段落（空段落・目次の行を除く）／実物928段落（すべて）</t>
+          <t>本表742段落（空段落・目次の行を除く）／実物942段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>63件</t>
+          <t>65件</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>15件（全63件）</t>
+          <t>16件（全65件）</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>133／133表</t>
+          <t>134／134表</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>143／143表</t>
+          <t>145／145表</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
@@ -4439,20 +4439,20 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D43" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E43" s="6" t="n">
-        <v>5</v>
-      </c>
       <c r="F43" s="9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>未確定箇所が集中している。【　】の見出しが5件あり、記述の単位が多い。</t>
+          <t>未確定箇所が集中している。【　】の見出しが6件あり、記述の単位が多い。</t>
         </is>
       </c>
     </row>
@@ -4493,20 +4493,20 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>【　】の見出しが8件あり、記述の単位が多い。</t>
+          <t>【　】の見出しが9件あり、記述の単位が多い。</t>
         </is>
       </c>
     </row>
@@ -4711,16 +4711,16 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
     </row>
@@ -6861,7 +6861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8876,23 +8876,23 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>入所の経路からみた整備の考え方</t>
+          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
+          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -8914,23 +8914,23 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>第9期の状況</t>
+          <t>入所の経路からみた整備の考え方</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも前期の状況の記載がある。</t>
+          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
+          <t>第9期の状況</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
@@ -8966,19 +8966,19 @@
       <c r="E58" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G58" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F58" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+          <t>第9期計画にも前期の状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -8995,28 +8995,28 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の状況</t>
+          <t>期別の必要保険料月額と基準額の対比</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G59" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>基金の取崩しは保険料の決定に直結する。</t>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -9033,18 +9033,18 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>保険料収納率と所得段階別被保険者数の実績</t>
+          <t>介護給付費準備基金の状況</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E60" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>保険料算定の基礎。</t>
+          <t>基金の取崩しは保険料の決定に直結する。</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>保険料と必要保険料月額との関係</t>
+          <t>保険料収納率と所得段階別被保険者数の実績</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
@@ -9080,19 +9080,19 @@
       <c r="E61" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G61" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G61" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
+          <t>保険料算定の基礎。</t>
         </is>
       </c>
     </row>
@@ -9109,28 +9109,28 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>暫定算定</t>
+          <t>保険料と必要保険料月額との関係</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G62" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
         </is>
       </c>
     </row>
@@ -9147,11 +9147,11 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>給付費の置き方によるちがい</t>
+          <t>暫定算定</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E63" s="6" t="n">
         <v>1</v>
@@ -9161,14 +9161,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G63" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
+          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
         </is>
       </c>
     </row>
@@ -9185,28 +9185,28 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>前提を動かした場合の幅</t>
+          <t>給付費の置き方によるちがい</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G64" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G64" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
         </is>
       </c>
     </row>
@@ -9218,53 +9218,57 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>第10期に施行される見直し</t>
+          <t>サービス別の趨勢を反映した場合</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G65" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F65" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G65" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。</t>
+          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="44" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>資料5</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの使用データ</t>
+          <t>前提を動かした場合の幅</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
@@ -9278,46 +9282,118 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>出典の明示に当たる。</t>
+          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="44" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>第7節</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>第10期に施行される見直し</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>令和8年3月課長会議資料により追加した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="44" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>資料5</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr"/>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>地域包括ケア「見える化」システムの使用データ</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G68" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>出典の明示に当たる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="44" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>資料7</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr"/>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr"/>
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>採番と表記の規則</t>
         </is>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D69" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E69" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="20" t="inlineStr">
+      <c r="F69" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G67" s="20" t="inlineStr">
+      <c r="G69" s="20" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="48" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
+    <row r="71" ht="48" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -9326,8 +9402,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9340,7 +9416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9675,7 +9751,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から928段落143表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から942段落145表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>
@@ -10184,23 +10260,27 @@
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>資料7</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>採番と表記の規則</t>
+          <t>サービス別の趨勢を反映した場合</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
+          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>資料7の冒頭1段落に圧縮する</t>
+          <t>確認事項No.106のご判断により落とす</t>
         </is>
       </c>
       <c r="F32" s="8" t="n"/>
@@ -10210,8 +10290,37 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>資料7</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>採番と表記の規則</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>資料7の冒頭1段落に圧縮する</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>注1）令和8年9月29日のご指示により、15件は一旦そのまま計画素案に残している。「移す場合の移し先の案」は、後日移すこととなった場合の候補である。
 注2）確認事項No.170として業務工程管理表に登録している。体裁（小見出し【　】の階層ほか）は保留となっており、確認事項No.171による。</t>
@@ -10219,10 +10328,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E8:F8"/>
@@ -10230,7 +10341,6 @@
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="A34:G34"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="E9:F9"/>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から942段落145表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から949段落146表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表145表／実物145表</t>
+          <t>本表146表／実物146表</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表742段落（空段落・目次の行を除く）／実物942段落（すべて）</t>
+          <t>本表748段落（空段落・目次の行を除く）／実物949段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>65件</t>
+          <t>66件</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>16件（全65件）</t>
+          <t>16件（全66件）</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>134／134表</t>
+          <t>135／135表</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>145／145表</t>
+          <t>146／146表</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
@@ -4414,16 +4414,16 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
     </row>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>13</v>
@@ -4502,7 +4502,7 @@
         <v>9</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -4711,16 +4711,16 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
     </row>
@@ -6861,7 +6861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8657,10 +8657,10 @@
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
@@ -8686,20 +8686,20 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>定員と見込量の照合</t>
+          <t>認知症総合支援事業の実施状況</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E51" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
           <t>法定</t>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数の算定の根拠となる。</t>
+          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -8729,18 +8729,18 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
+          <t>定員と見込量の照合</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
+          <t>必要利用定員総数の算定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -8767,28 +8767,28 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>供給の担い手の集中</t>
+          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G53" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G53" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
+          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
         </is>
       </c>
     </row>
@@ -8805,28 +8805,28 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>現況（令和8年度）</t>
+          <t>供給の担い手の集中</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも現況の記載がある。</t>
+          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
         </is>
       </c>
     </row>
@@ -8843,18 +8843,18 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>第10期における必要利用定員総数</t>
+          <t>現況（令和8年度）</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
+          <t>第9期計画にも現況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -8881,11 +8881,11 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
+          <t>第10期における必要利用定員総数</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>1</v>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
+          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
         </is>
       </c>
     </row>
@@ -8914,23 +8914,23 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>入所の経路からみた整備の考え方</t>
+          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
+          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -8952,23 +8952,23 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>第9期の状況</t>
+          <t>入所の経路からみた整備の考え方</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも前期の状況の記載がある。</t>
+          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
+          <t>第9期の状況</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
@@ -9004,19 +9004,19 @@
       <c r="E59" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G59" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G59" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+          <t>第9期計画にも前期の状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -9033,28 +9033,28 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の状況</t>
+          <t>期別の必要保険料月額と基準額の対比</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G60" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G60" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>基金の取崩しは保険料の決定に直結する。</t>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -9071,18 +9071,18 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>保険料収納率と所得段階別被保険者数の実績</t>
+          <t>介護給付費準備基金の状況</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F61" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F61" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>保険料算定の基礎。</t>
+          <t>基金の取崩しは保険料の決定に直結する。</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>保険料と必要保険料月額との関係</t>
+          <t>保険料収納率と所得段階別被保険者数の実績</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
@@ -9118,19 +9118,19 @@
       <c r="E62" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G62" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G62" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
+          <t>保険料算定の基礎。</t>
         </is>
       </c>
     </row>
@@ -9147,28 +9147,28 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>暫定算定</t>
+          <t>保険料と必要保険料月額との関係</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G63" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G63" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
         </is>
       </c>
     </row>
@@ -9185,11 +9185,11 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>給付費の置き方によるちがい</t>
+          <t>暫定算定</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>1</v>
@@ -9199,14 +9199,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G64" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G64" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
+          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
         </is>
       </c>
     </row>
@@ -9223,11 +9223,11 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映した場合</t>
+          <t>給付費の置き方によるちがい</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>1</v>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
         </is>
       </c>
     </row>
@@ -9261,28 +9261,28 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>前提を動かした場合の幅</t>
+          <t>サービス別の趨勢を反映した場合</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G66" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9294,23 +9294,23 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>第10期に施行される見直し</t>
+          <t>前提を動かした場合の幅</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E67" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G67" s="17" t="inlineStr">
@@ -9320,31 +9320,35 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。</t>
+          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="44" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>資料5</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>第7節</t>
+        </is>
+      </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの使用データ</t>
+          <t>第10期に施行される見直し</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E68" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F68" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
@@ -9354,46 +9358,80 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>出典の明示に当たる。</t>
+          <t>令和8年3月課長会議資料により追加した。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="44" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>資料7</t>
+          <t>資料5</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr"/>
       <c r="C69" s="5" t="inlineStr">
         <is>
+          <t>地域包括ケア「見える化」システムの使用データ</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>出典の明示に当たる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="44" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>資料7</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr"/>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
           <t>採番と表記の規則</t>
         </is>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D70" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E70" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F69" s="20" t="inlineStr">
+      <c r="F70" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G69" s="20" t="inlineStr">
+      <c r="G70" s="20" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H70" s="5" t="inlineStr">
         <is>
           <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="48" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
+    <row r="72" ht="48" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -9402,8 +9440,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A72:H72"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9751,7 +9789,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から942段落145表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から949段落146表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から949段落146表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から951段落146表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表748段落（空段落・目次の行を除く）／実物949段落（すべて）</t>
+          <t>本表750段落（空段落・目次の行を除く）／実物951段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>7</v>
@@ -4323,7 +4323,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>13</v>
@@ -4502,7 +4502,7 @@
         <v>9</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>146</v>
@@ -4720,7 +4720,7 @@
         <v>66</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
     </row>
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>1</v>
@@ -9789,7 +9789,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から949段落146表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から951段落146表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -629,7 +629,7 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>基準日 令和8年9月29日。計画素案の章節構成を実物から洗い出し、介護保険法第117条・国の第10期基本指針（案）別表・令和8年3月の全国課長会議資料の3つの原典と対比する。他団体が策定した計画は対比の軸に用いない。あわせて、第9期計画になく当方が独自に加えた記載を棚卸しし、計画に置くか協議用の資料へ移すかを判定する。</t>
+          <t>基準日 令和8年9月29日。計画素案の章節構成を洗い出し、介護保険法第117条・国の第10期基本指針（案）別表・令和8年3月の全国課長会議資料の3つの原典と対比する。他団体が策定した計画は対比の軸に用いない。あわせて、第9期計画になく当方が独自に加えた記載を棚卸しし、計画に置くか協議用の資料へ移すかを判定する。</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>本表の数値と判定が、計画素案の実物及び業務工程管理表と合っていることを機械で確かめた結果。1件でも不適合があると終了コード1で終わる。</t>
+          <t>本表の数値と判定が、計画素案の実物及び業務工程管理表と合っていることを機械で確かめた結果。1件でも不適合があると作成を止める。</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>素案の章節を実物から読めていること</t>
+          <t>素案の章節を読めていること</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>資料6の表を実物から読めていること</t>
+          <t>資料6の表を読めていること</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案の実物から章・節ごとの段落・表・【　】の見出し・未確定箇所を数えたもの。記述量の偏りと未確定の集中を見るためのものである。</t>
+          <t>計画素案から章・節ごとの段落・表・【　】の見出し・未確定箇所を数えたもの。記述量の偏りと未確定の集中を見るためのものである。</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5295,7 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案 資料6の対応表を実物から読み込んだもの。資料6は計画の一部として発注者へお示しするものであり、本シートはその対応状況を一覧で確かめるためのものである。</t>
+          <t>計画素案 資料6の対応表によるもの。資料6は計画の一部として発注者へお示しするものであり、本シートはその対応状況を一覧で確かめるためのものである。</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案の本文にある【　】の小見出しを実物から拾い、第9期計画及び法定記載事項との関係により区分したもの。見出しごとの段落数・表数は、次の見出し又は節までの数である。</t>
+          <t>計画素案の本文にある【　】の小見出しを拾い、第9期計画及び法定記載事項との関係により区分したもの。見出しごとの段落数・表数は、次の見出し又は節までの数である。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>750</v>
+        <v>768</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から951段落146表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から973段落148表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表146表／実物146表</t>
+          <t>本表148表／実物148表</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表750段落（空段落・目次の行を除く）／実物951段落（すべて）</t>
+          <t>本表768段落（空段落・目次の行を除く）／実物973段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>66件</t>
+          <t>70件</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>第1章第9節、第6章第3節</t>
+          <t>第1章第9節、第4章第3節、第6章第3節</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>16件（全66件）</t>
+          <t>16件（全70件）</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>135／135表</t>
+          <t>137／137表</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>146／146表</t>
+          <t>148／148表</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
@@ -3772,16 +3772,16 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>2</v>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
     </row>
@@ -3831,7 +3831,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
     </row>
@@ -4168,16 +4168,16 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
     </row>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>7</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>7</v>
@@ -4448,7 +4448,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -4493,20 +4493,20 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>13</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>【　】の見出しが9件あり、記述の単位が多い。</t>
+          <t>未確定箇所が集中している。【　】の見出しが10件あり、記述の単位が多い。</t>
         </is>
       </c>
     </row>
@@ -4711,16 +4711,16 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>750</v>
+        <v>768</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
     </row>
@@ -6861,7 +6861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="17" t="inlineStr">
         <is>
@@ -7394,23 +7394,23 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>上川管内における位置</t>
+          <t>認定に要する期間</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>2</v>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G17" s="17" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも管内比較がある。</t>
+          <t>介護保険法第27条第11項が申請から30日以内の処分を定めており、認定事務の状況は第5章 基本目標5の要介護認定の適正化の前提となる（確認事項No.43）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -7437,18 +7437,18 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の利用強度</t>
+          <t>上川管内における位置</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
+          <t>第9期計画にも管内比較がある。</t>
         </is>
       </c>
     </row>
@@ -7475,18 +7475,18 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>町別の要介護認定者数</t>
+          <t>訪問介護の利用強度</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>3</v>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>実績は町別に掲げる方針による。</t>
+          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>町別の給付費の実績</t>
+          <t>町別の要介護認定者数</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
@@ -7546,23 +7546,23 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>事業所数と定員・給付の突合</t>
+          <t>町別の給付費の実績</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
+          <t>実績は町別に掲げる方針による。</t>
         </is>
       </c>
     </row>
@@ -7589,14 +7589,14 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>職種別の状況（介護老人福祉施設）</t>
+          <t>事業所数と定員・給付の突合</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（従事者数）に対応する。</t>
+          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -7627,28 +7627,28 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>リハビリテーション専門職の配置</t>
+          <t>職種別の状況（介護老人福祉施設）</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
+          <t>基本指針別表 七（従事者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -7665,11 +7665,11 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>運営法人の状況</t>
+          <t>リハビリテーション専門職の配置</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>3</v>
@@ -7679,14 +7679,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
+          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
         </is>
       </c>
     </row>
@@ -7698,20 +7698,20 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>調査の対象者の範囲</t>
+          <t>運営法人の状況</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
           <t>独自</t>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
+          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
         </is>
       </c>
     </row>
@@ -7741,18 +7741,18 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>1　主要指標の状況</t>
+          <t>調査の対象者の範囲</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも調査結果の掲載がある。</t>
+          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
         </is>
       </c>
     </row>
@@ -7779,28 +7779,28 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2　年齢構成の影響と町間の差</t>
+          <t>1　主要指標の状況</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
+          <t>第9期計画にも調査結果の掲載がある。</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>3　同規模の保険者との比較</t>
+          <t>2　年齢構成の影響と町間の差</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
@@ -7831,14 +7831,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>基本指針が地域間比較を求めている。</t>
+          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -7855,11 +7855,11 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>4　社会参加との関連</t>
+          <t>3　同規模の保険者との比較</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>1</v>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
+          <t>基本指針が地域間比較を求めている。</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>5　暮らし向きとの関連</t>
+          <t>4　社会参加との関連</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
@@ -7907,14 +7907,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G30" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
+          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>6　生活実態の主な値</t>
+          <t>5　暮らし向きとの関連</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
@@ -7940,19 +7940,19 @@
       <c r="E31" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の第2章にも生活実態の記載がある。</t>
+          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>7　地区別の状況</t>
+          <t>6　生活実態の主な値</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
@@ -7978,19 +7978,19 @@
       <c r="E32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
+          <t>第9期計画の第2章にも生活実態の記載がある。</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>8　前回調査との比較</t>
+          <t>7　地区別の状況</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
@@ -8016,19 +8016,19 @@
       <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>経年比較は計画に置く。</t>
+          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
         </is>
       </c>
     </row>
@@ -8040,23 +8040,23 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>重度者の在宅・居住系割合の上昇</t>
+          <t>8　前回調査との比較</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
+          <t>経年比較は計画に置く。</t>
         </is>
       </c>
     </row>
@@ -8083,11 +8083,11 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>在宅生活の継続に必要な生活支援</t>
+          <t>重度者の在宅・居住系割合の上昇</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>1</v>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2・3の根拠となる。</t>
+          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -8116,16 +8116,16 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>第10期分の介護人材実態調査の結果</t>
+          <t>在宅生活の継続に必要な生活支援</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>1</v>
@@ -8142,35 +8142,35 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
+          <t>第5章 基本目標2・3の根拠となる。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の事業費（決算）</t>
+          <t>第10期分の介護人材実態調査の結果</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G37" s="17" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
+          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
         </is>
       </c>
     </row>
@@ -8197,18 +8197,18 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の通いの場の展開状況</t>
+          <t>令和6年度の事業費（決算）</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも通いの場の記載がある。</t>
+          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
         </is>
       </c>
     </row>
@@ -8235,11 +8235,11 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>一般介護予防事業の実施状況（令和6年度）</t>
+          <t>令和6年度の通いの場の展開状況</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>1</v>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも実施状況の記載がある。</t>
+          <t>第9期計画にも通いの場の記載がある。</t>
         </is>
       </c>
     </row>
@@ -8268,57 +8268,57 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
+          <t>一般介護予防事業の実施状況（令和6年度）</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G40" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
+          <t>第9期計画にも実施状況の記載がある。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>H07・H08・H12・H16の振替について</t>
+          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
+          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
         </is>
       </c>
     </row>
@@ -8349,180 +8349,180 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>H13・H14の定義変更について</t>
+          <t>第9期の目標指標との接続</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G42" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>基本目標5</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>介護給付費の適正化（第7期給付適正化計画）</t>
+          <t>H07・H08・H12・H16の振替について</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F43" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>1</v>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G43" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
+          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>要介護度別の認定者数</t>
+          <t>H13・H14の定義変更について</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>0</v>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
+          <t>同上。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>認定率の置き方によるちがい</t>
+          <t>H15の分母について</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G45" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
+          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>基本目標5</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎による推計のちがい</t>
+          <t>介護給付費の適正化（第7期給付適正化計画）</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G46" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>3</v>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G46" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>同上。案Cを採る理由の説明としては要る。</t>
+          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
         </is>
       </c>
     </row>
@@ -8534,19 +8534,19 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定方法</t>
+          <t>要介護度別の認定者数</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>見込量の前提を示すもので、計画に置く。</t>
+          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
         </is>
       </c>
     </row>
@@ -8572,33 +8572,33 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>利用回（日）数</t>
+          <t>認定率の置き方によるちがい</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号が回数・日数を求めている。</t>
+          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
         </is>
       </c>
     </row>
@@ -8610,33 +8610,33 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業の量の見込み</t>
+          <t>人口の基礎による推計のちがい</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号。</t>
+          <t>同上。案Cを採る理由の説明としては要る。</t>
         </is>
       </c>
     </row>
@@ -8648,19 +8648,19 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業費</t>
+          <t>見込量の算定方法</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F50" s="17" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号。</t>
+          <t>見込量の前提を示すもので、計画に置く。</t>
         </is>
       </c>
     </row>
@@ -8686,19 +8686,19 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実施状況</t>
+          <t>利用回（日）数</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
+          <t>法第117条第2項第1号が回数・日数を求めている。</t>
         </is>
       </c>
     </row>
@@ -8724,16 +8724,16 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>定員と見込量の照合</t>
+          <t>介護予防・日常生活支援総合事業の量の見込み</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>1</v>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数の算定の根拠となる。</t>
+          <t>法第117条第2項第2号。</t>
         </is>
       </c>
     </row>
@@ -8762,23 +8762,23 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
+          <t>地域支援事業費</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G53" s="17" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
+          <t>法第117条第3項第2号。</t>
         </is>
       </c>
     </row>
@@ -8800,33 +8800,33 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>供給の担い手の集中</t>
+          <t>認知症総合支援事業の実施状況</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G54" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>2</v>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
+          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -8843,18 +8843,18 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>現況（令和8年度）</t>
+          <t>定員と見込量の照合</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G55" s="17" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも現況の記載がある。</t>
+          <t>必要利用定員総数の算定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -8881,18 +8881,18 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>第10期における必要利用定員総数</t>
+          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>0</v>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
+          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
+          <t>供給の担い手の集中</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
@@ -8928,19 +8928,19 @@
       <c r="E57" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G57" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G57" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
+          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
         </is>
       </c>
     </row>
@@ -8952,23 +8952,23 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>入所の経路からみた整備の考え方</t>
+          <t>現況（令和8年度）</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F58" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
+          <t>第9期計画にも現況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -8990,12 +8990,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>第9期の状況</t>
+          <t>第10期における必要利用定員総数</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
@@ -9004,9 +9004,9 @@
       <c r="E59" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも前期の状況の記載がある。</t>
+          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
         </is>
       </c>
     </row>
@@ -9028,33 +9028,33 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
+          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G60" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G60" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9066,23 +9066,23 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の状況</t>
+          <t>入所の経路からみた整備の考え方</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>基金の取崩しは保険料の決定に直結する。</t>
+          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -9109,18 +9109,18 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>保険料収納率と所得段階別被保険者数の実績</t>
+          <t>第9期の状況</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F62" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>保険料算定の基礎。</t>
+          <t>第9期計画にも前期の状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -9147,14 +9147,14 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>保険料と必要保険料月額との関係</t>
+          <t>期別の必要保険料月額と基準額の対比</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -9185,18 +9185,18 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>暫定算定</t>
+          <t>介護給付費準備基金の状況</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F64" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
+          <t>基金の取崩しは保険料の決定に直結する。</t>
         </is>
       </c>
     </row>
@@ -9223,28 +9223,28 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>給付費の置き方によるちがい</t>
+          <t>保険料収納率と所得段階別被保険者数の実績</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G65" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
+          <t>保険料算定の基礎。</t>
         </is>
       </c>
     </row>
@@ -9261,28 +9261,28 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映した場合</t>
+          <t>所得段階と乗率の置き方</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G66" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
+          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9299,28 +9299,28 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>前提を動かした場合の幅</t>
+          <t>保険料と必要保険料月額との関係</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G67" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G67" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
         </is>
       </c>
     </row>
@@ -9332,23 +9332,23 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>第10期に施行される見直し</t>
+          <t>暫定算定</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E68" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F68" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
@@ -9358,24 +9358,28 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。</t>
+          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="44" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>資料5</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの使用データ</t>
+          <t>給付費の置き方によるちがい</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69" s="6" t="n">
         <v>1</v>
@@ -9385,53 +9389,201 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G69" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>出典の明示に当たる。</t>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="44" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>サービス別の趨勢を反映した場合</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G70" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="44" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>前提を動かした場合の幅</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G71" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="44" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>第7節</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>第10期に施行される見直し</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G72" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>令和8年3月課長会議資料により追加した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="44" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>資料5</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr"/>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>地域包括ケア「見える化」システムの使用データ</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>出典の明示に当たる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="44" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
           <t>資料7</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr"/>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr"/>
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>採番と表記の規則</t>
         </is>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D74" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E74" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F70" s="20" t="inlineStr">
+      <c r="F74" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G70" s="20" t="inlineStr">
+      <c r="G74" s="20" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="48" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
+    <row r="76" ht="48" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -9440,8 +9592,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A76:H76"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A72:H72"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9789,7 +9941,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から951段落146表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から973段落148表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>台帳173件</t>
+          <t>台帳174件</t>
         </is>
       </c>
       <c r="E27" s="17" t="inlineStr">

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から973段落148表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1000段落151表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表148表／実物148表</t>
+          <t>本表151表／実物151表</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表768段落（空段落・目次の行を除く）／実物973段落（すべて）</t>
+          <t>本表793段落（空段落・目次の行を除く）／実物1000段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>70件</t>
+          <t>72件</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>第1章第9節、第6章第7節</t>
+          <t>第1章第9節、第6章第6節、第6章第7節</t>
         </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>台帳174件</t>
+          <t>台帳177件</t>
         </is>
       </c>
       <c r="E27" s="17" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第1章第9節に項が4つあること（制度改正の項を新設した）</t>
+          <t>第1章第9節に項が5つあること（制度改正の項を新設した）</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>1〜4</t>
+          <t>1〜5</t>
         </is>
       </c>
       <c r="E30" s="17" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>第6章第7節に第10期に施行される見直しの表があること</t>
+          <t>第6章第7節に低所得者に係る負担軽減の見直しの表があること</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>16件（全70件）</t>
+          <t>16件（全72件）</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>137／137表</t>
+          <t>140／140表</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>148／148表</t>
+          <t>151／151表</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
@@ -3726,18 +3726,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所が集中している。</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -4214,7 +4218,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>3</v>
@@ -4264,7 +4268,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>3</v>
@@ -4273,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
     </row>
@@ -4289,7 +4293,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>3</v>
@@ -4298,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
     </row>
@@ -4314,7 +4318,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>7</v>
@@ -4398,7 +4402,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
     </row>
@@ -4493,20 +4497,20 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D45" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="E45" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>10</v>
-      </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>未確定箇所が集中している。【　】の見出しが10件あり、記述の単位が多い。</t>
+          <t>未確定箇所が集中している。【　】の見出しが11件あり、記述の単位が多い。</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4526,7 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>2</v>
@@ -4531,7 +4535,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
     </row>
@@ -4711,16 +4715,16 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
     </row>
@@ -6861,7 +6865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7251,10 +7255,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
@@ -7275,28 +7279,28 @@
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>第2章</t>
+          <t>第1章</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第9節</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>第10期の人口の基礎</t>
+          <t>引き続き検討することとされた事項</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
@@ -7306,7 +7310,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>推計の基礎を示すもので、見込量の前提として要る。</t>
+          <t>令和8年9月18日社会保障審議会介護保険部会の資料により追加した。給付と負担の在り方として引き続き検討することとされた7事項を、本計画への影響が及び得る箇所と対にして掲げる。いずれも算定には織り込んでいない。令和8年10月7日に新設した。</t>
         </is>
       </c>
     </row>
@@ -7323,28 +7327,28 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>第9期計画及び社人研推計との関係</t>
+          <t>第10期の人口の基礎</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
+          <t>推計の基礎を示すもので、見込量の前提として要る。</t>
         </is>
       </c>
     </row>
@@ -7361,28 +7365,28 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>認知症高齢者の状況</t>
+          <t>第9期計画及び社人研推計との関係</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E16" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>国の第10期基本指針が主要テーマとする事項である。法第117条第3項第6号（認知症である被保険者の支援）の前提となる。令和8年9月29日に新設した。</t>
+          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
         </is>
       </c>
     </row>
@@ -7399,14 +7403,14 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>認定に要する期間</t>
+          <t>認知症高齢者の状況</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
@@ -7420,7 +7424,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第27条第11項が申請から30日以内の処分を定めており、認定事務の状況は第5章 基本目標5の要介護認定の適正化の前提となる（確認事項No.43）。令和8年10月5日に新設した。</t>
+          <t>国の第10期基本指針が主要テーマとする事項である。法第117条第3項第6号（認知症である被保険者の支援）の前提となる。令和8年9月29日に新設した。</t>
         </is>
       </c>
     </row>
@@ -7432,23 +7436,23 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上川管内における位置</t>
+          <t>認定に要する期間</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>2</v>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
@@ -7458,7 +7462,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも管内比較がある。</t>
+          <t>介護保険法第27条第11項が申請から30日以内の処分を定めており、認定事務の状況は第5章 基本目標5の要介護認定の適正化の前提となる（確認事項No.43）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -7475,18 +7479,18 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の利用強度</t>
+          <t>上川管内における位置</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G19" s="17" t="inlineStr">
@@ -7496,7 +7500,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
+          <t>第9期計画にも管内比較がある。</t>
         </is>
       </c>
     </row>
@@ -7513,18 +7517,18 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>町別の要介護認定者数</t>
+          <t>訪問介護の利用強度</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>3</v>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
@@ -7534,7 +7538,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>実績は町別に掲げる方針による。</t>
+          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7555,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>町別の給付費の実績</t>
+          <t>町別の要介護認定者数</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
@@ -7584,23 +7588,23 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>事業所数と定員・給付の突合</t>
+          <t>町別の給付費の実績</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
@@ -7610,7 +7614,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
+          <t>実績は町別に掲げる方針による。</t>
         </is>
       </c>
     </row>
@@ -7627,14 +7631,14 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>職種別の状況（介護老人福祉施設）</t>
+          <t>事業所数と定員・給付の突合</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
@@ -7648,7 +7652,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（従事者数）に対応する。</t>
+          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -7665,28 +7669,28 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>リハビリテーション専門職の配置</t>
+          <t>職種別の状況（介護老人福祉施設）</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
+          <t>基本指針別表 七（従事者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -7703,11 +7707,11 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>運営法人の状況</t>
+          <t>リハビリテーション専門職の配置</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>3</v>
@@ -7717,14 +7721,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
+          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
         </is>
       </c>
     </row>
@@ -7736,20 +7740,20 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>調査の対象者の範囲</t>
+          <t>運営法人の状況</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
           <t>独自</t>
@@ -7762,7 +7766,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
+          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
         </is>
       </c>
     </row>
@@ -7779,18 +7783,18 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>1　主要指標の状況</t>
+          <t>調査の対象者の範囲</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G27" s="17" t="inlineStr">
@@ -7800,7 +7804,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも調査結果の掲載がある。</t>
+          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
         </is>
       </c>
     </row>
@@ -7817,28 +7821,28 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>2　年齢構成の影響と町間の差</t>
+          <t>1　主要指標の状況</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
+          <t>第9期計画にも調査結果の掲載がある。</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7859,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>3　同規模の保険者との比較</t>
+          <t>2　年齢構成の影響と町間の差</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
@@ -7869,14 +7873,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>基本指針が地域間比較を求めている。</t>
+          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -7893,11 +7897,11 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>4　社会参加との関連</t>
+          <t>3　同規模の保険者との比較</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>1</v>
@@ -7914,7 +7918,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
+          <t>基本指針が地域間比較を求めている。</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7935,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>5　暮らし向きとの関連</t>
+          <t>4　社会参加との関連</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
@@ -7945,14 +7949,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G31" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
+          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7973,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>6　生活実態の主な値</t>
+          <t>5　暮らし向きとの関連</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
@@ -7978,19 +7982,19 @@
       <c r="E32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の第2章にも生活実態の記載がある。</t>
+          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8011,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>7　地区別の状況</t>
+          <t>6　生活実態の主な値</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
@@ -8016,19 +8020,19 @@
       <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G33" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
+          <t>第9期計画の第2章にも生活実態の記載がある。</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8049,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>8　前回調査との比較</t>
+          <t>7　地区別の状況</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
@@ -8054,19 +8058,19 @@
       <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F34" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>経年比較は計画に置く。</t>
+          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
         </is>
       </c>
     </row>
@@ -8078,23 +8082,23 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>重度者の在宅・居住系割合の上昇</t>
+          <t>8　前回調査との比較</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G35" s="17" t="inlineStr">
@@ -8104,7 +8108,7 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
+          <t>経年比較は計画に置く。</t>
         </is>
       </c>
     </row>
@@ -8121,11 +8125,11 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>在宅生活の継続に必要な生活支援</t>
+          <t>重度者の在宅・居住系割合の上昇</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>1</v>
@@ -8142,7 +8146,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2・3の根拠となる。</t>
+          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -8154,16 +8158,16 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>第10期分の介護人材実態調査の結果</t>
+          <t>在宅生活の継続に必要な生活支援</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>1</v>
@@ -8180,35 +8184,35 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
+          <t>第5章 基本目標2・3の根拠となる。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の事業費（決算）</t>
+          <t>第10期分の介護人材実態調査の結果</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
@@ -8218,7 +8222,7 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
+          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
         </is>
       </c>
     </row>
@@ -8235,18 +8239,18 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の通いの場の展開状況</t>
+          <t>令和6年度の事業費（決算）</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G39" s="17" t="inlineStr">
@@ -8256,7 +8260,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも通いの場の記載がある。</t>
+          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
         </is>
       </c>
     </row>
@@ -8273,11 +8277,11 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>一般介護予防事業の実施状況（令和6年度）</t>
+          <t>令和6年度の通いの場の展開状況</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>1</v>
@@ -8294,7 +8298,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも実施状況の記載がある。</t>
+          <t>第9期計画にも通いの場の記載がある。</t>
         </is>
       </c>
     </row>
@@ -8306,71 +8310,71 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
+          <t>一般介護予防事業の実施状況（令和6年度）</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G41" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
+          <t>第9期計画にも実施状況の記載がある。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>第9期の目標指標との接続</t>
+          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G42" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>4</v>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
+          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
         </is>
       </c>
     </row>
@@ -8387,28 +8391,28 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>H07・H08・H12・H16の振替について</t>
+          <t>第9期の目標指標との接続</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G43" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>0</v>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
+          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -8425,14 +8429,14 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>H13・H14の定義変更について</t>
+          <t>H07・H08・H12・H16の振替について</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
@@ -8446,7 +8450,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
         </is>
       </c>
     </row>
@@ -8463,52 +8467,52 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>H15の分母について</t>
+          <t>H13・H14の定義変更について</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>0</v>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G45" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
+          <t>同上。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>基本目標5</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>介護給付費の適正化（第7期給付適正化計画）</t>
+          <t>H15の分母について</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" s="17" t="inlineStr">
         <is>
@@ -8522,31 +8526,31 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
+          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>基本目標5</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>要介護度別の認定者数</t>
+          <t>介護給付費の適正化（第7期給付適正化計画）</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" s="17" t="inlineStr">
         <is>
@@ -8560,7 +8564,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
+          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
         </is>
       </c>
     </row>
@@ -8577,28 +8581,28 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>認定率の置き方によるちがい</t>
+          <t>要介護度別の認定者数</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G48" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F48" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
+          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
         </is>
       </c>
     </row>
@@ -8615,11 +8619,11 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎による推計のちがい</t>
+          <t>認定率の置き方によるちがい</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>1</v>
@@ -8636,7 +8640,7 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>同上。案Cを採る理由の説明としては要る。</t>
+          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
         </is>
       </c>
     </row>
@@ -8648,33 +8652,33 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定方法</t>
+          <t>人口の基礎による推計のちがい</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F50" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G50" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>1</v>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>見込量の前提を示すもので、計画に置く。</t>
+          <t>同上。案Cを採る理由の説明としては要る。</t>
         </is>
       </c>
     </row>
@@ -8691,15 +8695,15 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>利用回（日）数</t>
+          <t>見込量の算定方法</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E51" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E51" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
           <t>法定</t>
@@ -8712,7 +8716,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号が回数・日数を求めている。</t>
+          <t>見込量の前提を示すもので、計画に置く。</t>
         </is>
       </c>
     </row>
@@ -8724,16 +8728,16 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業の量の見込み</t>
+          <t>利用回（日）数</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>1</v>
@@ -8750,7 +8754,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号。</t>
+          <t>法第117条第2項第1号が回数・日数を求めている。</t>
         </is>
       </c>
     </row>
@@ -8767,11 +8771,11 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業費</t>
+          <t>介護予防・日常生活支援総合事業の量の見込み</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>1</v>
@@ -8788,7 +8792,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号。</t>
+          <t>法第117条第2項第2号。</t>
         </is>
       </c>
     </row>
@@ -8805,14 +8809,14 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実施状況</t>
+          <t>地域支援事業費</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" s="17" t="inlineStr">
         <is>
@@ -8826,7 +8830,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
+          <t>法第117条第3項第2号。</t>
         </is>
       </c>
     </row>
@@ -8838,20 +8842,20 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>定員と見込量の照合</t>
+          <t>認知症総合支援事業の実施状況</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E55" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F55" s="17" t="inlineStr">
         <is>
           <t>法定</t>
@@ -8864,7 +8868,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数の算定の根拠となる。</t>
+          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -8881,18 +8885,18 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
+          <t>定員と見込量の照合</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
@@ -8902,7 +8906,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
+          <t>必要利用定員総数の算定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -8919,28 +8923,28 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>供給の担い手の集中</t>
+          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G57" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G57" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
+          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
         </is>
       </c>
     </row>
@@ -8957,28 +8961,28 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>現況（令和8年度）</t>
+          <t>供給の担い手の集中</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G58" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも現況の記載がある。</t>
+          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
         </is>
       </c>
     </row>
@@ -8995,18 +8999,18 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>第10期における必要利用定員総数</t>
+          <t>現況（令和8年度）</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G59" s="17" t="inlineStr">
@@ -9016,7 +9020,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
+          <t>第9期計画にも現況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -9033,11 +9037,11 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
+          <t>第10期における必要利用定員総数</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>1</v>
@@ -9054,7 +9058,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
+          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
         </is>
       </c>
     </row>
@@ -9066,23 +9070,23 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>入所の経路からみた整備の考え方</t>
+          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G61" s="17" t="inlineStr">
@@ -9092,7 +9096,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
+          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9104,23 +9108,23 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>第9期の状況</t>
+          <t>入所の経路からみた整備の考え方</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
@@ -9130,7 +9134,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも前期の状況の記載がある。</t>
+          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9151,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
+          <t>第9期の状況</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
@@ -9156,19 +9160,19 @@
       <c r="E63" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G63" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F63" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G63" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+          <t>第9期計画にも前期の状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -9185,28 +9189,28 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の状況</t>
+          <t>期別の必要保険料月額と基準額の対比</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="21" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G64" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G64" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>基金の取崩しは保険料の決定に直結する。</t>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -9223,18 +9227,18 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>保険料収納率と所得段階別被保険者数の実績</t>
+          <t>介護給付費準備基金の状況</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F65" s="21" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G65" s="17" t="inlineStr">
@@ -9244,7 +9248,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>保険料算定の基礎。</t>
+          <t>基金の取崩しは保険料の決定に直結する。</t>
         </is>
       </c>
     </row>
@@ -9261,11 +9265,11 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>所得段階と乗率の置き方</t>
+          <t>保険料収納率と所得段階別被保険者数の実績</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>1</v>
@@ -9282,7 +9286,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
+          <t>保険料算定の基礎。</t>
         </is>
       </c>
     </row>
@@ -9299,28 +9303,28 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>保険料と必要保険料月額との関係</t>
+          <t>所得段階と乗率の置き方</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F67" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G67" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G67" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
+          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9337,28 +9341,28 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>暫定算定</t>
+          <t>保険料と必要保険料月額との関係</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G68" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
         </is>
       </c>
     </row>
@@ -9375,11 +9379,11 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>給付費の置き方によるちがい</t>
+          <t>暫定算定</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E69" s="6" t="n">
         <v>1</v>
@@ -9389,14 +9393,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G69" s="20" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G69" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
+          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
         </is>
       </c>
     </row>
@@ -9413,11 +9417,11 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映した場合</t>
+          <t>給付費の置き方によるちがい</t>
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E70" s="6" t="n">
         <v>1</v>
@@ -9434,7 +9438,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
         </is>
       </c>
     </row>
@@ -9451,28 +9455,28 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>前提を動かした場合の幅</t>
+          <t>サービス別の趨勢を反映した場合</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E71" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G71" s="17" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G71" s="20" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9484,23 +9488,23 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>第10期に施行される見直し</t>
+          <t>前提を動かした場合の幅</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E72" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E72" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="17" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
@@ -9510,31 +9514,35 @@
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。</t>
+          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="44" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>資料5</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの使用データ</t>
+          <t>所得段階の置き方による保険料の違い</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F73" s="20" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G73" s="17" t="inlineStr">
@@ -9544,46 +9552,118 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>出典の明示に当たる。</t>
+          <t>国は第10期において高所得者の標準乗率の見直し及び課税化に伴う上昇の緩和を含めた標準段階の見直しを検討課題として挙げている（令和8年9月18日社会保障審議会介護保険部会）。段階の置き方により基準額が動くため、3案の比較を掲げる（確認事項No.33）。令和8年10月7日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="44" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>資料7</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>第7節</t>
+        </is>
+      </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>採番と表記の規則</t>
+          <t>低所得者に係る負担軽減の見直し</t>
         </is>
       </c>
       <c r="D74" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E74" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>令和8年3月課長会議資料により追加した。令和8年10月7日に、見出しを「第10期に施行される見直し」から改めた。一定以上所得基準は結論を得る段階であり施行が決まっていないため、見出しで施行を断定しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="44" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>資料5</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr"/>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>地域包括ケア「見える化」システムの使用データ</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G75" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>出典の明示に当たる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="44" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>資料7</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr"/>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>採番と表記の規則</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E76" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F74" s="20" t="inlineStr">
+      <c r="F76" s="20" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G74" s="20" t="inlineStr">
+      <c r="G76" s="20" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="48" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
+    <row r="78" ht="48" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -9592,7 +9672,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A78:H78"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -9941,7 +10021,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から973段落148表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1000段落151表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1000段落151表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1001段落151表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表793段落（空段落・目次の行を除く）／実物1000段落（すべて）</t>
+          <t>本表794段落（空段落・目次の行を除く）／実物1001段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -3835,7 +3835,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
     </row>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>3</v>
@@ -4180,10 +4180,14 @@
       <c r="E32" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G32" s="5" t="inlineStr"/>
+      <c r="F32" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所が集中している。</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
@@ -4715,7 +4719,7 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>151</v>
@@ -4724,7 +4728,7 @@
         <v>72</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
     </row>
@@ -4932,7 +4936,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>代表KPI16項目の定義は1か所にまとめ、第5章第3節・各基本目標の達成目標・資料1が同じ定義を掲げる。</t>
+          <t>代表KPI16項目の定義は1か所にまとめ、第4章第3節・各基本目標の達成目標・資料1が同じ定義を掲げる。</t>
         </is>
       </c>
     </row>
@@ -10021,7 +10025,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1000段落151表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1001段落151表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1001段落151表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1006段落151表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表794段落（空段落・目次の行を除く）／実物1001段落（すべて）</t>
+          <t>本表799段落（空段落・目次の行を除く）／実物1006段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -3735,7 +3735,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>9</v>
@@ -3810,7 +3810,7 @@
         <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
     </row>
@@ -3889,7 +3889,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
     </row>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>3</v>
@@ -4035,7 +4035,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
     </row>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>6</v>
@@ -4085,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
     </row>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>4</v>
@@ -4381,7 +4381,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
     </row>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>14</v>
@@ -4510,7 +4510,7 @@
         <v>11</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>151</v>
@@ -4728,7 +4728,7 @@
         <v>72</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
     </row>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>1</v>
@@ -8361,7 +8361,7 @@
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>4</v>
@@ -8589,7 +8589,7 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>1</v>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>1</v>
@@ -10025,7 +10025,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1001段落151表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1006段落151表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         </is>
       </c>
       <c r="B26" s="14" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C26" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D26" s="14" t="n">
         <v>0</v>
@@ -1030,7 +1030,7 @@
     <row r="29" ht="56" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1006段落151表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1019段落152表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表151表／実物151表</t>
+          <t>本表152表／実物152表</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表799段落（空段落・目次の行を除く）／実物1006段落（すべて）</t>
+          <t>本表811段落（空段落・目次の行を除く）／実物1019段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>72件</t>
+          <t>73件</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>16件（全72件）</t>
+          <t>16件（全73件）</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>140／140表</t>
+          <t>141／141表</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>151／151表</t>
+          <t>152／152表</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2</v>
@@ -3660,7 +3660,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
     </row>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>7</v>
@@ -3735,7 +3735,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>9</v>
@@ -3785,7 +3785,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
     </row>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>13</v>
@@ -3835,7 +3835,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
     </row>
@@ -3860,7 +3860,7 @@
         <v>9</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>4</v>
@@ -4010,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
     </row>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>3</v>
@@ -4035,7 +4035,7 @@
         <v>3</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
     </row>
@@ -4085,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
     </row>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>3</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G34" s="5" t="inlineStr"/>
     </row>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>3</v>
@@ -4255,10 +4255,14 @@
       <c r="E35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G35" s="5" t="inlineStr"/>
+      <c r="F35" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所が集中している。</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -4372,7 +4376,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>4</v>
@@ -4381,7 +4385,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
     </row>
@@ -4406,7 +4410,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
     </row>
@@ -4501,7 +4505,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>14</v>
@@ -4510,7 +4514,7 @@
         <v>11</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -4698,16 +4702,16 @@
       </c>
       <c r="B54" s="5" t="inlineStr"/>
       <c r="C54" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
     </row>
@@ -4719,16 +4723,16 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
     </row>
@@ -6869,7 +6873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6993,7 +6997,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1</v>
@@ -7221,7 +7225,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -7373,7 +7377,7 @@
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>5</v>
@@ -7715,7 +7719,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" s="6" t="n">
         <v>3</v>
@@ -8247,7 +8251,7 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>1</v>
@@ -8589,7 +8593,7 @@
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>1</v>
@@ -9501,7 +9505,7 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>3</v>
@@ -9666,8 +9670,42 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="48" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>資料7</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr"/>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所の表示</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G77" s="17" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>［要協議］等の記号の意味を示すものであり、本文を読むために必要な凡例に当たる。記号が0になった時点で落とす。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -9676,7 +9714,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A79:H79"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -10025,7 +10063,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1006段落151表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1019段落152表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -816,17 +816,17 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>A　介護保険法第117条第2項・第3項</t>
+          <t>A　介護保険法第117条（記載事項・作成の基準・策定の手続）</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -842,21 +842,21 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>B　基本指針（案）別表 確認すべき指標・状況</t>
+          <t>A'　介護保険法以外の関係法令</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>3</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="F15" s="7" t="n"/>
@@ -868,21 +868,21 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>C　令和8年3月 全国課長会議資料</t>
+          <t>B　基本指針（案）別表 確認すべき指標・状況</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="F16" s="7" t="n"/>
@@ -891,89 +891,96 @@
       <c r="I16" s="7" t="n"/>
       <c r="J16" s="8" t="n"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>C　令和8年3月 全国課長会議資料</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="8" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>【今回の対比により素案へ加えたもの】</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>令和8年3月の全国課長会議資料（原典）により確認した事項のうち、素案にまったく記載がなかった11件を加えた。加えた箇所は第1章第9節4（新設）・第6章第6節4の注・第6章第7節である。第1章第9節1には2040年を見据えた地域類型の考え方と医療と介護の協議の場の再編成を加えた。新たな章又は節は起こしていない（節の中の項として加えた）。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>【独自に加えた記載の判定】</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>移す</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr"/>
-      <c r="I22" s="4" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>法令・基本指針が求める事項の説明</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>第9期計画にも同種の記載がある事項</t>
+          <t>法令・基本指針が求める事項の説明</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>0</v>
@@ -985,58 +992,77 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>第9期計画になく法令も直接には求めていない分析</t>
+          <t>第9期計画にも同種の記載がある事項</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>第9期計画になく法令も直接には求めていない分析</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B27" s="14" t="n">
         <v>73</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C27" s="14" t="n">
         <v>57</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D27" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E27" s="14" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>【令和8年9月29日のご指示による移行（済み）】</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1019段落152表36図となった（表6点の減）。
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1024段落152表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>注1）「協議」と判定したものは、計画に置くか移すかを打合せでお決めいただくものである。既定値は「素案に残す」とする。
 注2）判定は確認事項No.170、体裁は確認事項No.171として業務工程管理表に登録している。</t>
@@ -1044,27 +1070,28 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A22:J22"/>
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="F25:J25"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A20:J20"/>
     <mergeCell ref="E15:J15"/>
     <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A31:J31"/>
     <mergeCell ref="F24:J24"/>
     <mergeCell ref="C10:J10"/>
+    <mergeCell ref="A30:J30"/>
     <mergeCell ref="F26:J26"/>
     <mergeCell ref="C9:J9"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="E16:J16"/>
-    <mergeCell ref="F23:J23"/>
     <mergeCell ref="C8:J8"/>
+    <mergeCell ref="F27:J27"/>
     <mergeCell ref="C7:J7"/>
     <mergeCell ref="E14:J14"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="E17:J17"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
@@ -2314,7 +2341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2431,7 +2458,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表811段落（空段落・目次の行を除く）／実物1019段落（すべて）</t>
+          <t>本表816段落（空段落・目次の行を除く）／実物1024段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -2556,7 +2583,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>5件</t>
+          <t>6件</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
@@ -2931,7 +2958,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>台帳177件</t>
+          <t>台帳181件</t>
         </is>
       </c>
       <c r="E27" s="17" t="inlineStr">
@@ -3410,6 +3437,306 @@
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>法定記載事項の対比が記載事項の号にとどまっていないこと</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>他計画との関係、任意記載事項、作成の基準、基本的記載事項、策定の手続、計画の性格</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>中長期の見通しと、見通しを踏まえた確保の施策を別の要件としていること</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>第2項（改正後）の行</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>2件</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>反映先として挙げた章節が計画素案に現にあること</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>素案にない章節</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>関係法令の対比に市町村を名宛人とする法令が含まれていること</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>名宛人が市町村のもの</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>4件</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>関係法令の条文を受領していないことを全件に明記していること</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>「未受領」の記載</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>9／9件</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="10" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>「老人福祉法第20条の8」が計画素案にあること</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>現れる章節</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>第1章第2節、第1章第8節</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="10" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>「成年後見制度の利用の促進に関する法律」が計画素案にあること</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>現れる章節</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>第1章第2節</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="10" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>「高齢者虐待の防止」が計画素案にあること</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>現れる章節</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>第1章第2節</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="10" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>「避難確保計画」が計画素案にあること</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>現れる章節</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>第1章第8節、第5章基本目標5</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="10" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>「要配慮者利用施設」が計画素案にあること</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>現れる章節</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>第5章基本目標5</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="10" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>「北海道知事への提出」が計画素案にあること</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>現れる章節</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>第1章第5節</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="10" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>「医療計画との整合性」が計画素案にあること</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>現れる章節</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>第1章第8節</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3551,7 +3878,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
@@ -3560,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
     </row>
@@ -3701,7 +4028,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>2</v>
@@ -3710,7 +4037,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
     </row>
@@ -4326,7 +4653,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>7</v>
@@ -4335,7 +4662,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
@@ -4480,7 +4807,7 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>1</v>
@@ -4489,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
     </row>
@@ -4723,7 +5050,7 @@
       </c>
       <c r="B55" s="15" t="inlineStr"/>
       <c r="C55" s="14" t="n">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>152</v>
@@ -4732,7 +5059,7 @@
         <v>73</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="G55" s="15" t="inlineStr"/>
     </row>
@@ -4759,7 +5086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4819,22 +5146,22 @@
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>第2項第1号</t>
+          <t>第1項</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>基本的記載事項</t>
+          <t>計画の性格</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>各年度における介護給付等対象サービスの種類ごとの量の見込み。認知症対応型共同生活介護、地域密着型特定施設入居者生活介護、地域密着型介護老人福祉施設入所者生活介護に係る必要利用定員総数、その他の介護給付等対象サービスの種類ごとの量の見込みを定める。</t>
+          <t>市町村は、基本指針に即して、三年を一期とする介護保険事業に係る保険給付の円滑な実施に関する計画（市町村介護保険事業計画）を定めるものとする。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>第6章第2節（量の見込み・利用回（日）数）、第6章第4節4（必要利用定員総数）</t>
+          <t>第1章第2節（計画の位置付け）、第1章第4節（計画期間）</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -4844,14 +5171,14 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数は現定員の据置き案を掲げるにとどめ［要協議］のまま。日常生活圏域の設定と一体で決定を要する（確認事項No.88）。</t>
+          <t>計画期間を令和9年度から令和11年度までの3年間と定めている。国の第10期基本指針は案の段階であり、確定後に照合を要する（確認事項No.23）。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>第2項第2号</t>
+          <t>第2項第1号</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -4861,29 +5188,29 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>各年度における地域支援事業の量の見込み。</t>
+          <t>各年度における介護給付等対象サービスの種類ごとの量の見込み。認知症対応型共同生活介護、地域密着型特定施設入居者生活介護、地域密着型介護老人福祉施設入所者生活介護に係る必要利用定員総数、その他の介護給付等対象サービスの種類ごとの量の見込みを定める。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>第6章第3節2（総合事業・一般介護予防事業の量の見込み）</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>対応済</t>
+          <t>第6章第2節（量の見込み・利用回（日）数）、第6章第4節4（必要利用定員総数）</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月16日に量の見込みを加えた。包括的支援事業のうち認知症総合支援事業は量が立たない（確認事項No.150）。</t>
+          <t>必要利用定員総数は現定員の据置き案を掲げるにとどめ［要協議］のまま。日常生活圏域の設定と一体で決定を要する（確認事項No.88）。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>第2項第3号</t>
+          <t>第2項第2号</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -4893,12 +5220,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>被保険者の地域における自立した日常生活の支援、要介護状態等となることの予防又は要介護状態等の軽減若しくは悪化の防止及び介護給付等に要する費用の適正化に関し、市町村が取り組むべき施策に関する事項。</t>
+          <t>各年度における地域支援事業の量の見込み。</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2（介護予防）、基本目標5（3）介護給付費の適正化（第7期給付適正化計画）</t>
+          <t>第6章第3節2（総合事業・一般介護予防事業の量の見込み）</t>
         </is>
       </c>
       <c r="E7" s="17" t="inlineStr">
@@ -4908,14 +5235,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>給付適正化計画は施策として位置づけ、主要3事業の毎年度の定量目標を掲げた。</t>
+          <t>令和8年9月16日に量の見込みを加えた。包括的支援事業のうち認知症総合支援事業は量が立たない（確認事項No.150）。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>第2項第4号</t>
+          <t>第2項第3号</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -4925,12 +5252,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>前号に掲げる事項の目標に関する事項。</t>
+          <t>被保険者の地域における自立した日常生活の支援、要介護状態等となることの予防又は要介護状態等の軽減若しくは悪化の防止及び介護給付等に要する費用の適正化に関し、市町村が取り組むべき施策に関する事項。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>第5章 各基本目標の達成目標、資料1（代表KPI）</t>
+          <t>第5章 基本目標2（介護予防）、基本目標5（3）介護給付費の適正化（第7期給付適正化計画）</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
@@ -4940,14 +5267,14 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>代表KPI16項目の定義は1か所にまとめ、第4章第3節・各基本目標の達成目標・資料1が同じ定義を掲げる。</t>
+          <t>給付適正化計画は施策として位置づけ、主要3事業の毎年度の定量目標を掲げた。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>第2項（改正後）</t>
+          <t>第2項第4号</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -4957,12 +5284,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>中長期的なサービス見通し（令和22年度を含む）を定めること。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。</t>
+          <t>前号に掲げる事項の目標に関する事項。</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>第6章第1節（認定者数）、第6章第3節3（総給付費 令和17・22年度）</t>
+          <t>第5章 各基本目標の達成目標、資料1（代表KPI）</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
@@ -4972,29 +5299,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月16日に見込量・給付費まで広げた。見える化システムが求める令和12・27・32年度は算定の側に置いている。</t>
+          <t>代表KPI16項目の定義は1か所にまとめ、第4章第3節・各基本目標の達成目標・資料1が同じ定義を掲げる。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>第3項第1号</t>
+          <t>第2項（改正後）①</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>任意記載事項</t>
+          <t>基本的記載事項</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>地域包括ケアシステムの構築のため必要な事項。</t>
+          <t>中長期的なサービスの見通し（令和22年度を含む）を定めること。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>第4章（基本理念・基本目標）、第5章 全基本目標</t>
+          <t>第6章第1節（認定者数）、第6章第2節（見込量）、第6章第3節3（総給付費 令和17・22年度）</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
@@ -5004,46 +5331,46 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>令和8年9月16日に見込量・給付費まで広げた。見える化システムが求める令和12・27・32年度は算定の側に置いている。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>第3項第2号</t>
+          <t>第2項（改正後）②</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>任意記載事項</t>
+          <t>基本的記載事項</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>各年度における地域支援事業に要する費用の額及びその見込量の確保のための方策。</t>
+          <t>中長期的なサービスの見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めること。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>第6章第3節2（地域支援事業費）、第5章 基本目標2</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>対応済</t>
+          <t>第6章第5節（整備に係る基本方針）、第6章第4節1（確保方策）、第5章 基本目標3</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>①の推計の表を加えたことでは充足しない要件である。令和22年度の水準を踏まえた整備の考え方は、日常生活圏域ごとの必要利用定員総数の決定と併せて定める［要協議］。条文を受領していないため定めるべき事項の範囲は［要確認］（確認事項No.181）。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>第3項第3号</t>
+          <t>第3項第1号</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -5053,29 +5380,29 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>介護給付等対象サービスの種類ごとの見込量の確保のための方策。</t>
+          <t>地域包括ケアシステムの構築のため必要な事項。</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>第6章第4節（施設の見込み）、第6章第5節（整備に係る基本方針）、第5章 基本目標3</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>一部対応</t>
+          <t>第4章（基本理念・基本目標）、第5章 全基本目標</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策は選択肢の提示にとどまる（第6章第4節1）。</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>第3項第4号</t>
+          <t>第3項第2号</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -5085,12 +5412,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>地域相互間の連携の確保に関する事業その他の被保険者が地域において自立した日常生活を営むために必要な事業に関する事項。</t>
+          <t>各年度における地域支援事業に要する費用の額及びその見込量の確保のための方策。</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>資料2（構成3町との役割分担）、第5章 基本目標3</t>
+          <t>第6章第3節2（地域支援事業費）、第5章 基本目標2</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr">
@@ -5107,7 +5434,7 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>第3項第5号</t>
+          <t>第3項第3号</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -5117,29 +5444,29 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>介護給付等対象サービスの円滑な提供を図るための事業所又は施設相互間の連携の確保その他の事業の円滑な実施を確保するために必要な事項。</t>
+          <t>介護給付等対象サービスの種類ごとの見込量の確保のための方策。</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標3（医療・介護連携）、第2章第3節（運営法人の状況）</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>対応済</t>
+          <t>第6章第4節（施設の見込み）、第6章第5節（整備に係る基本方針）、第5章 基本目標3</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>24時間対応サービスの確保方策は選択肢の提示にとどまる（第6章第4節1）。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>第3項第6号</t>
+          <t>第3項第4号</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -5149,12 +5476,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>認知症である被保険者の地域における自立した日常生活の支援に関する事項。</t>
+          <t>地域相互間の連携の確保に関する事業その他の被保険者が地域において自立した日常生活を営むために必要な事業に関する事項。</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>第1章第2節、第5章 基本目標2（3）</t>
+          <t>資料2（構成3町との役割分担）、第5章 基本目標3</t>
         </is>
       </c>
       <c r="E15" s="17" t="inlineStr">
@@ -5164,14 +5491,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画は構成3町が策定し、本計画は介護保険法第117条第3項による事項として掲げる（案B）。</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>第3項第7号</t>
+          <t>第3項第5号</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -5181,12 +5508,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>医療との連携に関する事項。</t>
+          <t>介護給付等対象サービスの円滑な提供を図るための事業所又は施設相互間の連携の確保その他の事業の円滑な実施を確保するために必要な事項。</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>第1章第8節、第5章 基本目標3</t>
+          <t>第5章 基本目標3（医療・介護連携）、第2章第3節（運営法人の状況）</t>
         </is>
       </c>
       <c r="E16" s="17" t="inlineStr">
@@ -5196,14 +5523,14 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新たな地域医療構想との接続は北海道の第10期支援計画が未策定。</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>第3項第8号</t>
+          <t>第3項第6号</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -5213,69 +5540,704 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>高齢者居住安定確保計画その他の住民の居住に係る施策との連携に関する事項。</t>
+          <t>認知症である被保険者の地域における自立した日常生活の支援に関する事項。</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>第2章第3節（高齢者向け住まい）、第5章 基本目標3</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>一部対応</t>
+          <t>第1章第2節、第5章 基本目標2（3）</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>介護保険の指定を受けない住まい339人・戸を把握しているが、北海道の高齢者居住安定確保計画との連携の記述がない。</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画は構成3町が策定し、本計画は介護保険法第117条第3項による事項として掲げる（案B）。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>第3項第7号</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>任意記載事項</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>医療との連携に関する事項。</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>第1章第8節、第5章 基本目標3</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>新たな地域医療構想との接続は北海道の第10期支援計画が未策定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>第3項第8号</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>任意記載事項</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>高齢者居住安定確保計画その他の住民の居住に係る施策との連携に関する事項。</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節（高齢者向け住まい）、第5章 基本目標3</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>介護保険の指定を受けない住まい339人・戸を把握しているが、北海道の高齢者居住安定確保計画との連携の記述がない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>第3項［号 要確認］</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>任意記載事項</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>介護給付等対象サービスに従事する者の確保及び資質の向上並びにその業務の効率化及び質の向上に資する事業に関する事項。</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>第2章第6節（介護人材の状況）、第5章 基本目標4（介護人材）</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>介護人材の確保・定着、生産性向上、外国人職員の受入れを掲げている。第3項の号の番号は条文の受領前のものであり、本号の位置は［要確認］（確認事項No.181）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
           <t>第3項第9号</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>任意記載事項</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>その他介護給付等対象サービス及び地域支援事業の円滑な提供を図るために市町村が必要と認める事項。</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>第1章第6節（進行管理）、第5章 基本目標5（保険運営）</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="14" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>注）介護保険法は第215条までであり、広域連合の根拠は地方自治法第284条である。保険給付・保険料・施策は保険者（広域連合）を単位として定める。</t>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>第117条［項 要確認］</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>作成の基準</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>市町村介護保険事業計画は、日常生活圏域ごとの人口、要介護者等の人数等を勘案して作成されなければならない。</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>第1章第7節（日常生活圏域の設定）、第6章第4節4（必要利用定員総数）</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>第9期の6圏域をそのまま掲げている。基盤整備の単位としての圏域（3町3圏域の案）は［要協議］のまま（確認事項No.88）。圏域ごとの人口は第9期計画による令和5年10月1日現在の値である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>第117条［項 要確認］</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>他計画との関係</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>市町村介護保険事業計画は、医療計画との整合性の確保が図られたものでなければならない。</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>第1章第8節（関係計画等との関係）</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月14日に、法が整合性の確保を定めていること及び整合を図る箇所（在宅医療・介護連携、協力医療機関、施設の整備）を加えた。北海道の第10期支援計画は未策定（確認事項No.111）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>第117条［項 要確認］</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>他計画との関係</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>市町村介護保険事業計画は、市町村老人福祉計画と一体のものとして作成されなければならない（老人福祉法第20条の8と対をなす規定）。</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>第1章第2節（計画の位置付け）、第1章第8節</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月14日に、構成3町の高齢者福祉計画が市町村老人福祉計画に当たること及び一体作成の定めを加えた。広域連合は老人福祉法上の市町村ではないため同計画は3町が策定する（市町村認知症施策推進計画と同じ構造）。一体のものとして作成する方法は［要協議］（確認事項No.178）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>第117条［項 要確認］</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>策定の手続</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>計画を定め、又は変更しようとするときは、あらかじめ被保険者の意見を反映させるために必要な措置を講ずる。</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>第1章第5節【法令が定める手続】</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>意見公募手続を令和9年1月にウェブサイトにより2週間行い、概要版を併せて示すこととしている。方法及び時期は［要協議］。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>第117条［項 要確認］</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>策定の手続</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>計画を定め、又は変更しようとするときは、あらかじめ都道府県の意見を聴く。</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>第1章第5節【法令が定める手続】</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>第117条［項 要確認］</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>策定の手続</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>計画を定め、又は変更したときは、遅滞なくこれを都道府県知事に提出する。</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>第1章第5節【法令が定める手続】</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月14日に加えた。従前は素案に記載がなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>注1）介護保険法は第215条までであり、広域連合の根拠は地方自治法第284条である。保険給付・保険料・施策は保険者（広域連合）を単位として定める。
+注2）条文を受領していないため、第1項・第2項・第3項以外の項は「第117条［項 要確認］」と記し項番号を書いていない（確認事項No.181）。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行っている。
+注3）第3項の号の番号は条文の受領前のものである。介護人材に係る事項は号の位置を確かめられないため「第3項［号 要確認］」と記している。
+注4）第117条は記載事項（第2項・第3項）のほかに、計画の性格、作成の基準、他計画との関係及び策定の手続を定めている。記載事項の号の対比だけでは、医療計画との整合性の確保、市町村老人福祉計画と一体のものとして作成すること、都道府県知事への提出が点検の外に出る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>【介護保険法以外の関係法令との対比】</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>計画の記載事項は介護保険法第117条に限られない。市町村を名宛人とする法令については、本広域連合が地方自治法第284条により設けられ介護保険法上の保険者としての事務を共同処理するものであることから、市町村認知症施策推進計画と同じ整理により構成3町が定めるものと本計画に定めるものを分ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>法令</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>名宛人</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>定めの内容</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>計画素案の反映先</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>対応</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>原典の受領と残る課題</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>老人福祉法第20条の8</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>市町村</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>市町村老人福祉計画を定めるものとされ、老人福祉事業の量の目標を定める。同計画は市町村介護保険事業計画と一体のものとして作成する。</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>第1章第2節、第1章第8節</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>未受領。令和8年10月14日に法令名及び一体作成の定めを加えた。構成3町の高齢者福祉計画が同計画に当たることの確認、一体作成の方法及び老人福祉事業の量の目標との関係は［要協議］（確認事項No.178）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>成年後見制度の利用の促進に関する法律第14条</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>市町村</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>国の基本計画を勘案して、成年後見制度の利用の促進に関する施策についての基本的な計画を定めるよう努めるものとされる。</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>第1章第2節、第5章 基本目標1（権利擁護・中核機関）</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>未受領。令和8年10月14日に第1章第2節へ位置づけを加えた。構成3町における策定の状況及び中核機関の整備の状況は［要確認］（確認事項No.179）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="52" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>高齢者虐待の防止、高齢者の養護者に対する支援等に関する法律</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>市町村</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>通報の受理、高齢者の安全の確認、措置及び養護者の支援を市町村の事務とする。計画の記載を直接義務づけるものではない。</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>第1章第2節、第5章 基本目標1（3）（4）（5）</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>未受領。施策・主な事業・達成目標（虐待通報への48時間以内の安全確認率100％）を定めている。令和8年10月14日に第1章第2節へ法令名を加えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="52" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>共生社会の実現を推進するための認知症基本法第3条</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>―（基本理念）</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>認知症施策の基本理念を定める。</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>第1章第2節、第4章（基本理念）、第5章 基本目標2（3）</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>未受領。令和8年10月14日に基本理念に沿って施策を定める旨を加えた。各号の内容は［要確認］（確認事項No.149・No.181）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="52" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>同法第13条</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>市町村</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>市町村認知症施策推進計画を定めるよう努めるものとされる。</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>第1章第2節、第1章第8節、第5章 基本目標2（3）、資料2</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>未受領。構成3町がそれぞれ策定し、本計画は介護保険法第117条第3項による事項として認知症施策を掲げる（案B。令和8年9月16日 ご了承）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="52" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>水防法／土砂災害警戒区域等における土砂災害防止対策の推進に関する法律</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>要配慮者利用施設の所有者又は管理者</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>市町村地域防災計画に定められた要配慮者利用施設について、避難確保計画の作成及び避難訓練の実施を求める。</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>第1章第8節、第5章 基本目標5（3）（4）</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>未受領。令和8年10月14日に施策及び主な事業へ加えた。対象施設及び作成の状況は構成3町の地域防災計画によるため［要確認］（確認事項No.180）。達成目標には数値を掲げていない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="52" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法第78条の4</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>広域連合（条例）</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービスの人員・設備・運営の基準を市町村（広域連合）の条例で定める。省令はその条例を定めるに当たっての基準である。</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節1、第6章第4節</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>未受領。当該条例を受領していないため、令和6年改正後の省令に対応しているかを確認できない（確認事項No.95）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="52" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>―（改正法）</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法第117条の記載事項の追加（中長期的なサービスの見通し及びこれを踏まえた提供体制の確保等のための施策）、令和9年4月新設の3区分、特定地域の特例等。</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節2、第6章第1節〜第3節、第6章第5節</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>未受領。7件を整理済み（第1章第9節2）。改正後の条文の構成を確認できていないため、記載事項の点検は条文の番号ではなく内容を単位として行っている（確認事項No.89・No.181）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="52" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>地方自治法第284条</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>―（広域連合の根拠）</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>広域連合は特別地方公共団体として設けられ、介護保険法上の保険者としての事務を共同処理する。</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>第1章第2節</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>未受領。介護保険法は第215条までであり第284条は存在しない。広域連合の根拠は地方自治法である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>注）本表の法令はいずれも条文を受領していない。「対応」は計画素案に当該の記述があるかの判定であり、条文との逐語の照合ではない。条文のご提供を確認事項No.181によりお願いしている。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A20:F20"/>
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8555,7 +9517,7 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>3</v>
@@ -10063,7 +11025,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1019段落152表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1024段落152表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -98,12 +98,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DEEBF7"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -182,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -206,10 +206,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,10 +227,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -236,7 +242,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -604,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -693,7 +699,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -715,7 +721,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -759,7 +765,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -917,89 +923,96 @@
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="8" t="n"/>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>C'　介護給付費分科会（第256〜270回）の論点</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="8" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>【今回の対比により素案へ加えたもの】</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>令和8年3月の全国課長会議資料（原典）により確認した事項のうち、素案にまったく記載がなかった11件を加えた。加えた箇所は第1章第9節4（新設）・第6章第6節4の注・第6章第7節である。第1章第9節1には2040年を見据えた地域類型の考え方と医療と介護の協議の場の再編成を加えた。新たな章又は節は起こしていない（節の中の項として加えた）。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>【独自に加えた記載の判定】</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>移す</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>法令・基本指針が求める事項の説明</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B25" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C25" s="6" t="n">
         <v>27</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>第9期計画にも同種の記載がある事項</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>12</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -1009,60 +1022,79 @@
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>第9期計画になく法令も直接には求めていない分析</t>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>第9期計画にも同種の記載がある事項</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="13" t="inlineStr">
         <is>
+          <t>第9期計画になく法令も直接には求めていない分析</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B28" s="15" t="n">
         <v>73</v>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C28" s="15" t="n">
         <v>57</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D28" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E28" s="15" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>【令和8年9月29日のご指示による移行（済み）】</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="56" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1024段落152表36図となった（表6点の減）。
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1027段落153表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>注1）「協議」と判定したものは、計画に置くか移すかを打合せでお決めいただくものである。既定値は「素案に残す」とする。
 注2）判定は確認事項No.170、体裁は確認事項No.171として業務工程管理表に登録している。</t>
@@ -1070,30 +1102,31 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A22:J22"/>
+  <mergeCells count="24">
+    <mergeCell ref="A23:J23"/>
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="F25:J25"/>
-    <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="E15:J15"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="C10:J10"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="F26:J26"/>
     <mergeCell ref="C9:J9"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="E16:J16"/>
+    <mergeCell ref="E18:J18"/>
+    <mergeCell ref="F28:J28"/>
     <mergeCell ref="C8:J8"/>
     <mergeCell ref="F27:J27"/>
     <mergeCell ref="C7:J7"/>
     <mergeCell ref="E14:J14"/>
     <mergeCell ref="E17:J17"/>
+    <mergeCell ref="A21:J21"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1186,7 +1219,7 @@
           <t>計画素案・公表版の全表</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>是正した</t>
         </is>
@@ -1216,7 +1249,7 @@
           <t>計画素案・公表版の全表</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>是正した</t>
         </is>
@@ -1246,7 +1279,7 @@
           <t>計画素案・公表版の本文</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>是正した</t>
         </is>
@@ -1276,7 +1309,7 @@
           <t>計画素案 第1章第9節</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>是正した</t>
         </is>
@@ -1306,7 +1339,7 @@
           <t>公表版の全章</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>公表版のみ是正</t>
         </is>
@@ -1336,7 +1369,7 @@
           <t>公表版 参考・第6章第2節</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -1366,7 +1399,7 @@
           <t>公表版 参考</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>是正した</t>
         </is>
@@ -1396,7 +1429,7 @@
           <t>公表版 用語の解説</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>是正した</t>
         </is>
@@ -1426,7 +1459,7 @@
           <t>計画素案 第1章第5節</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>是正した</t>
         </is>
@@ -1456,7 +1489,7 @@
           <t>計画素案 第2章第1節3</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>是正した</t>
         </is>
@@ -1486,7 +1519,7 @@
           <t>計画素案 第1章第2節・第6章第6節・資料3</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>是正した</t>
         </is>
@@ -1516,7 +1549,7 @@
           <t>計画素案 第1章第9節・資料7</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>是正した</t>
         </is>
@@ -1546,7 +1579,7 @@
           <t>資料編</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>一部対応・協議</t>
         </is>
@@ -1576,7 +1609,7 @@
           <t>計画素案 全体</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>記録した</t>
         </is>
@@ -1606,14 +1639,14 @@
           <t>計画素案 資料7</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>変更しない</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>注1）比較材料とした計画は成果品に用いず、記載の借用も行わない。団体名は掲げない。作業の終了後に消去する（発注者指示）。
 注2）気づいた点は、いずれも原典（介護保険法・国の基本指針・第9期計画の体裁）で確かめてから扱っている。比較材料は「当方に何がないか」に気づくために用い、「どう書くか」は原典から決める。</t>
@@ -1717,7 +1750,7 @@
           <t>公表版の自己点検17.5</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>是正</t>
         </is>
@@ -1747,7 +1780,7 @@
           <t>公表版の自己点検0</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>是正</t>
         </is>
@@ -1777,7 +1810,7 @@
           <t>公表版の自己点検13</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>是正</t>
         </is>
@@ -1807,7 +1840,7 @@
           <t>公表版の自己点検17</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>是正</t>
         </is>
@@ -1837,7 +1870,7 @@
           <t>公表版の作り</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>設計で防いだ</t>
         </is>
@@ -1867,7 +1900,7 @@
           <t>公表版の表紙・自己点検12</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>設計で防いだ</t>
         </is>
@@ -1897,7 +1930,7 @@
           <t>公表版の自己点検3・4・5</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>設計で防いだ</t>
         </is>
@@ -1927,7 +1960,7 @@
           <t>公表版の目次・自己点検10</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>是正</t>
         </is>
@@ -1957,7 +1990,7 @@
           <t>公表版の自己点検16</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>設計で防いだ</t>
         </is>
@@ -1987,14 +2020,14 @@
           <t>公表版の自己点検15</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>設計で防いだ</t>
         </is>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>注）1と2は実際に起きた誤りであり、自己点検が不適合になる形にして再発を止めている。3と4は読み直して見つけたものである。5から10は、起こると重いものについてあらかじめ点検を置いたものである。</t>
         </is>
@@ -2071,7 +2104,7 @@
       <c r="A5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>読み手</t>
         </is>
@@ -2096,7 +2129,7 @@
       <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>表題</t>
         </is>
@@ -2121,7 +2154,7 @@
       <c r="A7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>当方の分析</t>
         </is>
@@ -2146,7 +2179,7 @@
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>未確定箇所</t>
         </is>
@@ -2171,7 +2204,7 @@
       <c r="A9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>サービスの内容</t>
         </is>
@@ -2196,7 +2229,7 @@
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>用語の解説</t>
         </is>
@@ -2221,7 +2254,7 @@
       <c r="A11" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>章の見出し</t>
         </is>
@@ -2246,7 +2279,7 @@
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>表の体裁</t>
         </is>
@@ -2271,7 +2304,7 @@
       <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>目次</t>
         </is>
@@ -2296,7 +2329,7 @@
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>図表番号</t>
         </is>
@@ -2318,7 +2351,7 @@
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>注1）公表版は協議用素案から組み替えたものであり、数値・本文を別に持たない。2つの版に別の答えが並ぶことはない。
 注2）公表版から落とした15件は、協議用素案には残っている（ご指示により一旦そのまま）。計画に置くか協議用の資料へ移すかは確認事項No.170による。</t>
@@ -2341,7 +2374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2411,7 +2444,7 @@
           <t>50節</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2433,10 +2466,10 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表152表／実物152表</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
+          <t>本表153表／実物153表</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2458,10 +2491,10 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表816段落（空段落・目次の行を除く）／実物1024段落（すべて）</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
+          <t>本表819段落（空段落・目次の行を除く）／実物1027段落（すべて）</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2486,7 +2519,7 @@
           <t>73件</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2511,7 +2544,7 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2536,7 +2569,7 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2561,7 +2594,7 @@
           <t>11事項</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2586,7 +2619,7 @@
           <t>6件</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2611,7 +2644,7 @@
           <t>16／17件</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2636,7 +2669,7 @@
           <t>第1章第9節、第6章第7節</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2661,7 +2694,7 @@
           <t>第1章第9節、第6章第6節</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2686,7 +2719,7 @@
           <t>第1章第9節、第6章第6節</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2711,7 +2744,7 @@
           <t>第1章第9節、第6章第7節</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2736,7 +2769,7 @@
           <t>第1章第9節</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2761,7 +2794,7 @@
           <t>第1章第9節</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2786,7 +2819,7 @@
           <t>第1章第9節、第4章第3節、第6章第3節</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2811,7 +2844,7 @@
           <t>第1章第9節、第6章第6節、第6章第7節</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2836,7 +2869,7 @@
           <t>第1章第9節</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2861,7 +2894,7 @@
           <t>第1章第9節、第6章第4節</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2886,7 +2919,7 @@
           <t>現れない</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2911,7 +2944,7 @@
           <t>現れない</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2936,7 +2969,7 @@
           <t>現れない</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2958,10 +2991,10 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>台帳181件</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
+          <t>台帳184件</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -2986,7 +3019,7 @@
           <t>No.170 あり／No.171 あり</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3011,7 +3044,7 @@
           <t>13／17件</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3036,7 +3069,7 @@
           <t>1〜5</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3061,7 +3094,7 @@
           <t>あり</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3086,7 +3119,7 @@
           <t>16件（全73件）</t>
         </is>
       </c>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3111,7 +3144,7 @@
           <t>残っていない</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3136,7 +3169,7 @@
           <t>全て残っている</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3161,7 +3194,7 @@
           <t>全てある</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E35" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3186,7 +3219,7 @@
           <t>あり</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E36" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3211,7 +3244,7 @@
           <t>現れない</t>
         </is>
       </c>
-      <c r="E37" s="17" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3236,7 +3269,7 @@
           <t>11件</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E38" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3261,7 +3294,7 @@
           <t>あり</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr">
+      <c r="E39" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3286,7 +3319,7 @@
           <t>残っていない</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
+      <c r="E40" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3311,7 +3344,7 @@
           <t>現れない</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3336,7 +3369,7 @@
           <t>サービスの内容 あり／用語の解説 あり</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E42" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3361,7 +3394,7 @@
           <t>協議用2／公表版2</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E43" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3383,10 +3416,10 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>141／141表</t>
-        </is>
-      </c>
-      <c r="E44" s="17" t="inlineStr">
+          <t>142／142表</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3411,7 +3444,7 @@
           <t>現れない</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3433,10 +3466,10 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>152／152表</t>
-        </is>
-      </c>
-      <c r="E46" s="17" t="inlineStr">
+          <t>153／153表</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3461,7 +3494,7 @@
           <t>他計画との関係、任意記載事項、作成の基準、基本的記載事項、策定の手続、計画の性格</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
+      <c r="E47" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3486,7 +3519,7 @@
           <t>2件</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E48" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3511,7 +3544,7 @@
           <t>なし</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="E49" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3536,7 +3569,7 @@
           <t>4件</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E50" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3561,7 +3594,7 @@
           <t>9／9件</t>
         </is>
       </c>
-      <c r="E51" s="17" t="inlineStr">
+      <c r="E51" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3586,7 +3619,7 @@
           <t>第1章第2節、第1章第8節</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="E52" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3611,7 +3644,7 @@
           <t>第1章第2節</t>
         </is>
       </c>
-      <c r="E53" s="17" t="inlineStr">
+      <c r="E53" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3636,7 +3669,7 @@
           <t>第1章第2節</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr">
+      <c r="E54" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3661,7 +3694,7 @@
           <t>第1章第8節、第5章基本目標5</t>
         </is>
       </c>
-      <c r="E55" s="17" t="inlineStr">
+      <c r="E55" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3686,7 +3719,7 @@
           <t>第5章基本目標5</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr">
+      <c r="E56" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3711,7 +3744,7 @@
           <t>第1章第5節</t>
         </is>
       </c>
-      <c r="E57" s="17" t="inlineStr">
+      <c r="E57" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3736,7 +3769,132 @@
           <t>第1章第8節</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr">
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>介護給付費分科会の論点を31件読めていること</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>len(KB.RONTEN)</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>31件</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>論点の全件に当方の反映先の判定があること</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>BUNKA_TOUHOU</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>31／31件</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>当区域に直結する論点が計画素案で扱われていること</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>語による判定</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>未対応 0件</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第9節に介護給付費分科会の項があること</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>in_draft</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>記載あり</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>計画素案に単位数の値を書いていないこと</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>数値を伴う「○○単位」の走査</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>現れない</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4053,16 +4211,16 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -4737,7 +4895,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
     </row>
@@ -4841,7 +4999,7 @@
         <v>11</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -5043,28 +5201,28 @@
       <c r="G54" s="5" t="inlineStr"/>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr"/>
-      <c r="C55" s="14" t="n">
-        <v>816</v>
-      </c>
-      <c r="D55" s="14" t="n">
-        <v>152</v>
-      </c>
-      <c r="E55" s="14" t="n">
+      <c r="B55" s="16" t="inlineStr"/>
+      <c r="C55" s="15" t="n">
+        <v>819</v>
+      </c>
+      <c r="D55" s="15" t="n">
+        <v>153</v>
+      </c>
+      <c r="E55" s="15" t="n">
         <v>73</v>
       </c>
-      <c r="F55" s="14" t="n">
-        <v>228</v>
-      </c>
-      <c r="G55" s="15" t="inlineStr"/>
+      <c r="F55" s="15" t="n">
+        <v>233</v>
+      </c>
+      <c r="G55" s="16" t="inlineStr"/>
     </row>
     <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>注）「段落」は空でない段落を数えたもので、目次の行は含まない。「表」は本文の表の数、「【　】」は本文中の小見出しの数である。未確定箇所は［要協議］［要確認］［要内訳］の出現回数で、本文と表の中の両方を数える。</t>
         </is>
@@ -5164,7 +5322,7 @@
           <t>第1章第2節（計画の位置付け）、第1章第4節（計画期間）</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -5196,7 +5354,7 @@
           <t>第6章第2節（量の見込み・利用回（日）数）、第6章第4節4（必要利用定員総数）</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -5228,7 +5386,7 @@
           <t>第6章第3節2（総合事業・一般介護予防事業の量の見込み）</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5260,7 +5418,7 @@
           <t>第5章 基本目標2（介護予防）、基本目標5（3）介護給付費の適正化（第7期給付適正化計画）</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5292,7 +5450,7 @@
           <t>第5章 各基本目標の達成目標、資料1（代表KPI）</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5324,7 +5482,7 @@
           <t>第6章第1節（認定者数）、第6章第2節（見込量）、第6章第3節3（総給付費 令和17・22年度）</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5356,7 +5514,7 @@
           <t>第6章第5節（整備に係る基本方針）、第6章第4節1（確保方策）、第5章 基本目標3</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -5388,7 +5546,7 @@
           <t>第4章（基本理念・基本目標）、第5章 全基本目標</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5420,7 +5578,7 @@
           <t>第6章第3節2（地域支援事業費）、第5章 基本目標2</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5452,7 +5610,7 @@
           <t>第6章第4節（施設の見込み）、第6章第5節（整備に係る基本方針）、第5章 基本目標3</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -5484,7 +5642,7 @@
           <t>資料2（構成3町との役割分担）、第5章 基本目標3</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5516,7 +5674,7 @@
           <t>第5章 基本目標3（医療・介護連携）、第2章第3節（運営法人の状況）</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5548,7 +5706,7 @@
           <t>第1章第2節、第5章 基本目標2（3）</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5580,7 +5738,7 @@
           <t>第1章第8節、第5章 基本目標3</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5612,7 +5770,7 @@
           <t>第2章第3節（高齢者向け住まい）、第5章 基本目標3</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -5644,7 +5802,7 @@
           <t>第2章第6節（介護人材の状況）、第5章 基本目標4（介護人材）</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5676,7 +5834,7 @@
           <t>第1章第6節（進行管理）、第5章 基本目標5（保険運営）</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5708,7 +5866,7 @@
           <t>第1章第7節（日常生活圏域の設定）、第6章第4節4（必要利用定員総数）</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -5740,7 +5898,7 @@
           <t>第1章第8節（関係計画等との関係）</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5772,7 +5930,7 @@
           <t>第1章第2節（計画の位置付け）、第1章第8節</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -5804,7 +5962,7 @@
           <t>第1章第5節【法令が定める手続】</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5836,7 +5994,7 @@
           <t>第1章第5節【法令が定める手続】</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5868,7 +6026,7 @@
           <t>第1章第5節【法令が定める手続】</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -5880,7 +6038,7 @@
       </c>
     </row>
     <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>注1）介護保険法は第215条までであり、広域連合の根拠は地方自治法第284条である。保険給付・保険料・施策は保険者（広域連合）を単位として定める。
 注2）条文を受領していないため、第1項・第2項・第3項以外の項は「第117条［項 要確認］」と記し項番号を書いていない（確認事項No.181）。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行っている。
@@ -5897,7 +6055,7 @@
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>計画の記載事項は介護保険法第117条に限られない。市町村を名宛人とする法令については、本広域連合が地方自治法第284条により設けられ介護保険法上の保険者としての事務を共同処理するものであることから、市町村認知症施策推進計画と同じ整理により構成3町が定めるものと本計画に定めるものを分ける。</t>
         </is>
@@ -5956,7 +6114,7 @@
           <t>第1章第2節、第1章第8節</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -5988,7 +6146,7 @@
           <t>第1章第2節、第5章 基本目標1（権利擁護・中核機関）</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -6020,7 +6178,7 @@
           <t>第1章第2節、第5章 基本目標1（3）（4）（5）</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E36" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -6052,7 +6210,7 @@
           <t>第1章第2節、第4章（基本理念）、第5章 基本目標2（3）</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -6084,7 +6242,7 @@
           <t>第1章第2節、第1章第8節、第5章 基本目標2（3）、資料2</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E38" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -6116,7 +6274,7 @@
           <t>第1章第8節、第5章 基本目標5（3）（4）</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -6148,7 +6306,7 @@
           <t>第1章第9節1、第6章第4節</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -6180,7 +6338,7 @@
           <t>第1章第9節2、第6章第1節〜第3節、第6章第5節</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -6212,7 +6370,7 @@
           <t>第1章第2節</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E42" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -6224,7 +6382,7 @@
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>注）本表の法令はいずれも条文を受領していない。「対応」は計画素案に当該の記述があるかの判定であり、条文との逐語の照合ではない。条文のご提供を確認事項No.181によりお願いしている。</t>
         </is>
@@ -6311,7 +6469,7 @@
           <t>地勢と交通（地域特性、交通機関、地理的状況、生活圏。特に訪問・通所困難地域のアクセスと社会資源）</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>未対応</t>
         </is>
@@ -6338,7 +6496,7 @@
           <t>人口構造（年齢三区分人口、高齢化率、世帯数）</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -6365,7 +6523,7 @@
           <t>人口動態（出生数、死亡数、健康寿命。死亡場所別の死亡数）</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>未対応</t>
         </is>
@@ -6392,7 +6550,7 @@
           <t>認定者数の状況（要介護度別認定者数、年齢調整後の認定率、計画と実績の乖離）</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -6419,7 +6577,7 @@
           <t>介護サービス等の利用状況（受給者数、受給率、自市町村内の事業所によるサービス提供割合、1人当たり費用額・算定回数、介護SCR）</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
@@ -6446,7 +6604,7 @@
           <t>介護サービス見込量（見込量、地域支援事業見込量、家族の就業の状況・意向）</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>課題あり</t>
         </is>
@@ -6473,7 +6631,7 @@
           <t>介護保険施設・事業所の状況（施設・事業所数、利用者数、入所率、稼働率、従事者数）</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -6500,7 +6658,7 @@
           <t>高齢者向け住まいの状況（有料老人ホーム等の施設数・戸数、入居者数、定員、要介護者等である入居者の状況）</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>未対応</t>
         </is>
@@ -6527,7 +6685,7 @@
           <t>地域支援事業の状況（多様なサービス・活動の数・参加者数、通いの場の数・参加者数、地域包括支援センターにおける相談体制、インセンティブ交付金における評価）</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -6554,7 +6712,7 @@
           <t>医療介護連携の状況（医療介護連携に関する加算の算定状況）</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -6581,7 +6739,7 @@
           <t>認知症の人の数及び関連施策の状況（認知症の人の数・推計値、認知症疾患医療センター、認知症サポート医、ピアサポート活動や就労等の社会参加の機会・場の数・利用者数）</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>未対応</t>
         </is>
@@ -6598,7 +6756,7 @@
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>注）本シートの内容は計画素案 資料6の表そのものである。資料6を更新すれば本シートも追随する。</t>
         </is>
@@ -6620,7 +6778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6698,7 +6856,7 @@
           <t>第1章第9節4</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -6730,7 +6888,7 @@
           <t>第1章第9節4、第6章第6節4の注</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -6762,7 +6920,7 @@
           <t>第1章第9節4、第6章第7節</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -6794,7 +6952,7 @@
           <t>第1章第9節4、第6章第7節</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -6826,7 +6984,7 @@
           <t>第1章第9節1</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -6858,7 +7016,7 @@
           <t>第1章第9節1</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -6890,7 +7048,7 @@
           <t>第3章（第9期計画の実施状況と評価）、第1章第6節</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -6922,7 +7080,7 @@
           <t>第2章第4節・第5節・第6節</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -6954,7 +7112,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>ない</t>
         </is>
@@ -6986,7 +7144,7 @@
           <t>資料6（一・五）、第2章第2節</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -7018,7 +7176,7 @@
           <t>第1章第9節4</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -7050,7 +7208,7 @@
           <t>第1章第9節4、第6章第6節2</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -7082,7 +7240,7 @@
           <t>第1章第9節4、第6章第7節</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -7114,7 +7272,7 @@
           <t>第3章第4節</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -7146,7 +7304,7 @@
           <t>第1章第9節4</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -7178,7 +7336,7 @@
           <t>第1章第9節4</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -7210,7 +7368,7 @@
           <t>第5章 基本目標5</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>ある</t>
         </is>
@@ -7222,18 +7380,618 @@
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>注1）「素案に語があるか」が「ない」であるものは、国から資料が示されていないため記載できないもの（点検ツール）である。
 注2）令和8年度介護報酬改定は、令和9年度改定を待たずに行われるものである。見込量・給付費の基準年度である令和7年度の単価には反映されていないため、改定率が示された時点で令和9年度改定とあわせて反映する。</t>
         </is>
       </c>
     </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>【介護給付費分科会（第256回〜第270回）の論点との対比】</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>介護給付費分科会は介護報酬（単位数・算定の要件・運営の基準）を扱う別の審議の場である。課長会議資料及び介護保険部会の対比ではこの場の論点を軸に持っていなかった。本表は当区域に直結するものに絞って掲げる（全31件の対比は別冊「介護給付費分科会の論点整理の受領点検」による）。**資料の原本を確認できていないため、計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない**（確認事項No.182）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>論点</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>検討されている内容</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>計画素案の反映先</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>素案に語があるか</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>本計画における取扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>I01</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>基本的な視点と確定時期</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>第268回は、物価・賃金と処遇、人口減少と需要変化、地域包括ケア、職場環境・生産性、制度の持続性の5つの視点を提示。</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節、第6章第6節2</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>改定率を据え置き（区分C）とし、1％あたり月額の感度を掲げている。諮問・答申（令和9年1月頃）は当方の第2次概算より後である</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>I04</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>需要推計と供給力の地域差</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>人口構造と需要の変化に応じ、2040年等の見通しを踏まえた提供体制を検討。</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>第1章第7節、第6章第1節〜第4節</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>日常生活圏域の設定（No.88）と中長期の見通し（令和17・22年度）を掲げている。圏域別の受入能力・移動時間は把握していない（No.116）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>I05</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>中山間・人口減少地域の維持</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>第261回は特定地域における配置の弾力化、訪問系の包括的な評価、現行加算を検討。第267回では過疎・離島の移動・待機負担等の意見。</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節1、第6章第4節1（案D）</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>ある</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>特定地域の判定（基準②の試算）と24時間対応の確保方策の選択肢を掲げている。配置の弾力化・訪問系の包括的な評価は反映していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>I06</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護・訪問入浴の供給確保</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護では立地・規模・形態による経営差と人材確保、訪問入浴では利用者の状態や提供体制等を踏まえた対応が論点。</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節、第6章第2節</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護の1人1月あたり利用回数が全国の1.87倍であることを把握している。移動負担・依頼辞退は調査していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>I07</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>定期巡回・夜間対応の移行</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>第269回では夜間対応型訪問介護の定期巡回への移行を見据え、24時間通報・相談と日中支援を踏まえた評価、事業開始時の配置等を検討。</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節（2）</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>ある</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護の区分を立てている（実績なし）。定期巡回への移行（移行猶予 令和11年3月）は反映していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>I10</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>認知症グループホームの地域拠点機能</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>第257回は医療ニーズへの対応、職員配置・連携、地域での役割等を提示。第269回資料4本文は確認未了。</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節、第6章第2節（2）、第6章第4節4</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護の定員（99人＋［要確認］）と令和11年度 月85.2人を掲げている</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>I11</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>通所介護・認知症対応型通所</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>第270回は、資源不足地域での入浴目的の短時間利用、入浴評価、送迎キャンセル・共同送迎、延長加算、中重度者対応、認知症対応型通所の評価を具体化。</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節（1）（2）、第6章第4節</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>通所介護・地域密着型通所介護・認知症対応型通所介護の見込量を立てている。認知症対応型通所は区域内に事業所がないが給付がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>I14</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>短期入所生活介護の多様な利用</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>31日以上連続利用への評価の見直しと、積雪期・猛暑期・農繁期等の季節利用に係る例外、送迎加算・共同送迎の見直し案を提示。</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節 注1-1、第6章第4節</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>ある</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>短期入所生活介護の見込量を立てている。**積雪期の季節利用に係る例外は当区域に直接関わる**</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="52" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>I15</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>短期入所療養介護の在宅療養支援</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>総合医学管理加算を区分支給限度基準額の適用外とする案と、利用日数の精査を踏まえた長期利用減算等の検討案を提示。</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節、第6章第3節</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>短期入所療養介護（老健・病院等・介護医療院）の見込量を立てている。総合医学管理加算の限度額外扱いは反映していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="52" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>I19</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホームの重度者対応</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>医療ニーズのある重度者への対応と安定供給、特別な基本報酬類型、各種加算の在り方が論点。</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>第6章第4節2、第6章第5節</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>ある</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>介護老人福祉施設（定員160人）・地域密着型（62人）の定員と見込量の照合を掲げている。実稼働床・休床は把握していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="52" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>I20</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>老健・介護医療院の機能分担</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>老健は在宅復帰・在宅療養支援、医療・看取り・リハ等。介護医療院は長期療養と生活の両機能が論点。</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>第6章第5節、第1章第8節</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>ある</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設3施設240人・介護医療院の見込量と、入所の経路（新規入所の57.0％が病院・診療所）を掲げている</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="52" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>I21</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>高齢者向け住まいとサービスの適正化</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>第262回の住まい向けサービスの適正化に加え、第270回は通所介護等の同一建物減算に代わる、移動コスト・提供実態に応じた報酬区分の見直し案を提示。</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節6、第6章第2節、第6章第4節4</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>ある</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>介護保険の指定を受けない住まい339人・戸を把握している。**同一建物減算に代わる報酬区分の見直しは単価に及ぶ**</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="52" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>I23</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>協力医療機関・感染症・看取り</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>協力医療機関との連携、感染症対応、ACP・看取りの体制や評価を検討。施設類型により現行の義務・努力義務が異なる。</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節1、第6章第4節</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>ある</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>協力医療機関の要件強化の対象10事業所を掲げている</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="52" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>I28</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>地域区分・多床室の室料負担</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>地域区分は国家公務員の地域手当に準拠する原則等、多床室は施設機能・利用実態と負担の公平性等が論点。</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>第6章第6節2、第6章第7節</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>ある</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>地域区分による単価は算定の基礎に含まれる。多床室の室料負担は利用者負担であり給付費とは別に扱う</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="52" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>I29</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>第10期基本指針案への対応</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>構成案では2040年等を見据えた供給体制、都道府県と市町村の連携、人材・生産性・経営支援、高齢者向け住まいの実態等を重視。</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節1、第1章第8節、第6章第1節〜第3節</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>国の第10期基本指針（案）別表11事項への対応を資料6で整理し、北海道の第10期支援計画が未策定であることを掲げている</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="52" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>I30</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>介護情報基盤とケアプラン連携</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>第136回介護保険部会は令和10年4月1日の本格運用を目指す工程、ケアプランデータ連携システムとの統合等を報告。</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節5、第5章 基本目標1（4）</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>ある</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>介護情報基盤の工程（令和10年4月1日 本格運用）を掲げている（No.175）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="52" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>I31</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>給付適正化・保険料算定</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>第136回は第1号保険料や2割負担の範囲等を検討。給付適正化は主要3事業、小規模保険者支援、住まい単位の点検等を提示。</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>第5章 基本目標5、第6章第6節、第6章第7節</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>ある</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>第7期給付適正化計画と保険料の算定を掲げている。2割負担の範囲は反映していない（No.33）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>注）「素案に語があるか」は、当該の論点を素案で扱っていることを示す語が現れるかを機械的に確かめた結果である（「―」は語による判定を置いていないもの）。国の公表の予定は、改定の考え方及び運営基準に関する整理が令和8年12月頃、諮問及び答申が令和9年1月頃とされており、いずれも本計画の第2次概算（令和8年10月30日）より後である。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7326,7 +8084,7 @@
           <t>第1章第9節4（新設）、第6章第6節4の注</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7356,7 +8114,7 @@
           <t>第1章第9節4、第6章第7節</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7386,7 +8144,7 @@
           <t>第1章第9節4、第6章第7節</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7416,7 +8174,7 @@
           <t>第1章第9節4、第6章第6節2</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7446,7 +8204,7 @@
           <t>第1章第9節4、第6章第7節</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7476,7 +8234,7 @@
           <t>第1章第9節4</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7506,7 +8264,7 @@
           <t>第1章第9節4</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7536,7 +8294,7 @@
           <t>第1章第9節4</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7566,7 +8324,7 @@
           <t>第1章第9節4</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7596,7 +8354,7 @@
           <t>第1章第9節1</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7626,7 +8384,7 @@
           <t>第1章第9節1</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7656,7 +8414,7 @@
           <t>第1章第5節（【法令が定める手続】を新設）</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7686,7 +8444,7 @@
           <t>第2章第1節3（【認知症高齢者の状況】を新設）</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>追加済み（令和8年9月29日）</t>
         </is>
@@ -7716,7 +8474,7 @@
           <t>第1章第8節、第5章 基本目標3</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>未追加。北海道の計画の改定時期の確認を要する</t>
         </is>
@@ -7746,7 +8504,7 @@
           <t>第6章第4節4</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>決定待ち（確認事項No.88）</t>
         </is>
@@ -7776,7 +8534,7 @@
           <t>第6章第4節1</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>決定待ち（確認事項No.88・No.84）</t>
         </is>
@@ -7806,14 +8564,14 @@
           <t>第3章第4節</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>未受領。提供され次第、評価に加えるかを協議する</t>
         </is>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>注）本シートは記載漏れと追加の対応を記録するものである。追加済みのものは計画素案に反映済みであり、決定待ち・未受領のものは確認事項として管理している。</t>
         </is>
@@ -7926,12 +8684,12 @@
       <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -7964,12 +8722,12 @@
       <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8002,12 +8760,12 @@
       <c r="E7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8040,12 +8798,12 @@
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8078,12 +8836,12 @@
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8116,12 +8874,12 @@
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8154,12 +8912,12 @@
       <c r="E11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8192,12 +8950,12 @@
       <c r="E12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8230,12 +8988,12 @@
       <c r="E13" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8263,17 +9021,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8306,12 +9064,12 @@
       <c r="E15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8344,12 +9102,12 @@
       <c r="E16" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -8382,12 +9140,12 @@
       <c r="E17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8420,12 +9178,12 @@
       <c r="E18" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8458,12 +9216,12 @@
       <c r="E19" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G19" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8496,12 +9254,12 @@
       <c r="E20" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8534,12 +9292,12 @@
       <c r="E21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G21" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8572,12 +9330,12 @@
       <c r="E22" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8610,12 +9368,12 @@
       <c r="E23" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G23" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8648,12 +9406,12 @@
       <c r="E24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8686,12 +9444,12 @@
       <c r="E25" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -8724,12 +9482,12 @@
       <c r="E26" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G26" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8762,12 +9520,12 @@
       <c r="E27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8800,12 +9558,12 @@
       <c r="E28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8838,12 +9596,12 @@
       <c r="E29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G29" s="20" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -8876,12 +9634,12 @@
       <c r="E30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G30" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8914,12 +9672,12 @@
       <c r="E31" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -8952,12 +9710,12 @@
       <c r="E32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -8990,12 +9748,12 @@
       <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="G33" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9028,12 +9786,12 @@
       <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
+      <c r="G34" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9066,12 +9824,12 @@
       <c r="E35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="G35" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9104,12 +9862,12 @@
       <c r="E36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="G36" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9142,12 +9900,12 @@
       <c r="E37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9180,12 +9938,12 @@
       <c r="E38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="20" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9218,12 +9976,12 @@
       <c r="E39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="17" t="inlineStr">
+      <c r="F39" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G39" s="17" t="inlineStr">
+      <c r="G39" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9256,12 +10014,12 @@
       <c r="E40" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="21" t="inlineStr">
+      <c r="F40" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr">
+      <c r="G40" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9294,12 +10052,12 @@
       <c r="E41" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="21" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9332,12 +10090,12 @@
       <c r="E42" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="20" t="inlineStr">
+      <c r="F42" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G42" s="20" t="inlineStr">
+      <c r="G42" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9370,12 +10128,12 @@
       <c r="E43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="17" t="inlineStr">
+      <c r="F43" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
+      <c r="G43" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9408,12 +10166,12 @@
       <c r="E44" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="20" t="inlineStr">
+      <c r="F44" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G44" s="20" t="inlineStr">
+      <c r="G44" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9446,12 +10204,12 @@
       <c r="E45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="F45" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G45" s="20" t="inlineStr">
+      <c r="G45" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9484,12 +10242,12 @@
       <c r="E46" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="F46" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G46" s="17" t="inlineStr">
+      <c r="G46" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9522,12 +10280,12 @@
       <c r="E47" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="F47" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G47" s="17" t="inlineStr">
+      <c r="G47" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9560,12 +10318,12 @@
       <c r="E48" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="F48" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G48" s="17" t="inlineStr">
+      <c r="G48" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9598,12 +10356,12 @@
       <c r="E49" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="20" t="inlineStr">
+      <c r="F49" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G49" s="20" t="inlineStr">
+      <c r="G49" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9636,12 +10394,12 @@
       <c r="E50" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="20" t="inlineStr">
+      <c r="F50" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G50" s="20" t="inlineStr">
+      <c r="G50" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9674,12 +10432,12 @@
       <c r="E51" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F51" s="17" t="inlineStr">
+      <c r="F51" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G51" s="17" t="inlineStr">
+      <c r="G51" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9712,12 +10470,12 @@
       <c r="E52" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="17" t="inlineStr">
+      <c r="F52" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G52" s="17" t="inlineStr">
+      <c r="G52" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9750,12 +10508,12 @@
       <c r="E53" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="17" t="inlineStr">
+      <c r="F53" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G53" s="17" t="inlineStr">
+      <c r="G53" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9788,12 +10546,12 @@
       <c r="E54" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="17" t="inlineStr">
+      <c r="F54" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G54" s="17" t="inlineStr">
+      <c r="G54" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9826,12 +10584,12 @@
       <c r="E55" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F55" s="17" t="inlineStr">
+      <c r="F55" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G55" s="17" t="inlineStr">
+      <c r="G55" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9864,12 +10622,12 @@
       <c r="E56" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="17" t="inlineStr">
+      <c r="F56" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
+      <c r="G56" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9902,12 +10660,12 @@
       <c r="E57" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F57" s="20" t="inlineStr">
+      <c r="F57" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G57" s="17" t="inlineStr">
+      <c r="G57" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -9940,12 +10698,12 @@
       <c r="E58" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="20" t="inlineStr">
+      <c r="F58" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G58" s="20" t="inlineStr">
+      <c r="G58" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9978,12 +10736,12 @@
       <c r="E59" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="21" t="inlineStr">
+      <c r="F59" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G59" s="17" t="inlineStr">
+      <c r="G59" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10016,12 +10774,12 @@
       <c r="E60" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="17" t="inlineStr">
+      <c r="F60" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G60" s="17" t="inlineStr">
+      <c r="G60" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10054,12 +10812,12 @@
       <c r="E61" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F61" s="17" t="inlineStr">
+      <c r="F61" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G61" s="17" t="inlineStr">
+      <c r="G61" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10092,12 +10850,12 @@
       <c r="E62" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F62" s="20" t="inlineStr">
+      <c r="F62" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G62" s="17" t="inlineStr">
+      <c r="G62" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10130,12 +10888,12 @@
       <c r="E63" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="21" t="inlineStr">
+      <c r="F63" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G63" s="17" t="inlineStr">
+      <c r="G63" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10168,12 +10926,12 @@
       <c r="E64" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="20" t="inlineStr">
+      <c r="F64" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G64" s="20" t="inlineStr">
+      <c r="G64" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10206,12 +10964,12 @@
       <c r="E65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="21" t="inlineStr">
+      <c r="F65" s="23" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
       </c>
-      <c r="G65" s="17" t="inlineStr">
+      <c r="G65" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10244,12 +11002,12 @@
       <c r="E66" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="17" t="inlineStr">
+      <c r="F66" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G66" s="17" t="inlineStr">
+      <c r="G66" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10282,12 +11040,12 @@
       <c r="E67" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="17" t="inlineStr">
+      <c r="F67" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G67" s="17" t="inlineStr">
+      <c r="G67" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10320,12 +11078,12 @@
       <c r="E68" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="20" t="inlineStr">
+      <c r="F68" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G68" s="20" t="inlineStr">
+      <c r="G68" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10358,12 +11116,12 @@
       <c r="E69" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F69" s="20" t="inlineStr">
+      <c r="F69" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G69" s="17" t="inlineStr">
+      <c r="G69" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10396,12 +11154,12 @@
       <c r="E70" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F70" s="20" t="inlineStr">
+      <c r="F70" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G70" s="20" t="inlineStr">
+      <c r="G70" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10434,12 +11192,12 @@
       <c r="E71" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F71" s="20" t="inlineStr">
+      <c r="F71" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G71" s="20" t="inlineStr">
+      <c r="G71" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10472,12 +11230,12 @@
       <c r="E72" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F72" s="20" t="inlineStr">
+      <c r="F72" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G72" s="17" t="inlineStr">
+      <c r="G72" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10510,12 +11268,12 @@
       <c r="E73" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F73" s="17" t="inlineStr">
+      <c r="F73" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G73" s="17" t="inlineStr">
+      <c r="G73" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10548,12 +11306,12 @@
       <c r="E74" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="17" t="inlineStr">
+      <c r="F74" s="18" t="inlineStr">
         <is>
           <t>法定</t>
         </is>
       </c>
-      <c r="G74" s="17" t="inlineStr">
+      <c r="G74" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10582,12 +11340,12 @@
       <c r="E75" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="20" t="inlineStr">
+      <c r="F75" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G75" s="17" t="inlineStr">
+      <c r="G75" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10616,12 +11374,12 @@
       <c r="E76" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F76" s="20" t="inlineStr">
+      <c r="F76" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G76" s="20" t="inlineStr">
+      <c r="G76" s="22" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10650,12 +11408,12 @@
       <c r="E77" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F77" s="20" t="inlineStr">
+      <c r="F77" s="22" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G77" s="17" t="inlineStr">
+      <c r="G77" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
@@ -10667,7 +11425,7 @@
       </c>
     </row>
     <row r="79" ht="48" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="A79" s="12" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -10783,7 +11541,7 @@
         </is>
       </c>
       <c r="F6" s="8" t="n"/>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>移した</t>
         </is>
@@ -10816,7 +11574,7 @@
         </is>
       </c>
       <c r="F7" s="8" t="n"/>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>移した</t>
         </is>
@@ -10849,7 +11607,7 @@
         </is>
       </c>
       <c r="F8" s="8" t="n"/>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>移した</t>
         </is>
@@ -10882,7 +11640,7 @@
         </is>
       </c>
       <c r="F9" s="8" t="n"/>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>移した</t>
         </is>
@@ -10915,7 +11673,7 @@
         </is>
       </c>
       <c r="F10" s="8" t="n"/>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>移した</t>
         </is>
@@ -10948,7 +11706,7 @@
         </is>
       </c>
       <c r="F11" s="8" t="n"/>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>移した</t>
         </is>
@@ -10981,7 +11739,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n"/>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>本文に残した（体裁のみ改めた）</t>
         </is>
@@ -11014,18 +11772,18 @@
         </is>
       </c>
       <c r="F13" s="8" t="n"/>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>見出しを改めた</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1024段落152表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1027段落153表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11854,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n"/>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11129,7 +11887,7 @@
         </is>
       </c>
       <c r="F19" s="8" t="n"/>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11162,7 +11920,7 @@
         </is>
       </c>
       <c r="F20" s="8" t="n"/>
-      <c r="G20" s="20" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11195,7 +11953,7 @@
         </is>
       </c>
       <c r="F21" s="8" t="n"/>
-      <c r="G21" s="20" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11228,7 +11986,7 @@
         </is>
       </c>
       <c r="F22" s="8" t="n"/>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11261,7 +12019,7 @@
         </is>
       </c>
       <c r="F23" s="8" t="n"/>
-      <c r="G23" s="20" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11294,7 +12052,7 @@
         </is>
       </c>
       <c r="F24" s="8" t="n"/>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11327,7 +12085,7 @@
         </is>
       </c>
       <c r="F25" s="8" t="n"/>
-      <c r="G25" s="20" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11360,7 +12118,7 @@
         </is>
       </c>
       <c r="F26" s="8" t="n"/>
-      <c r="G26" s="20" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11393,7 +12151,7 @@
         </is>
       </c>
       <c r="F27" s="8" t="n"/>
-      <c r="G27" s="20" t="inlineStr">
+      <c r="G27" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11426,7 +12184,7 @@
         </is>
       </c>
       <c r="F28" s="8" t="n"/>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11459,7 +12217,7 @@
         </is>
       </c>
       <c r="F29" s="8" t="n"/>
-      <c r="G29" s="20" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11492,7 +12250,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n"/>
-      <c r="G30" s="20" t="inlineStr">
+      <c r="G30" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11525,7 +12283,7 @@
         </is>
       </c>
       <c r="F31" s="8" t="n"/>
-      <c r="G31" s="20" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11558,7 +12316,7 @@
         </is>
       </c>
       <c r="F32" s="8" t="n"/>
-      <c r="G32" s="20" t="inlineStr">
+      <c r="G32" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11587,14 +12345,14 @@
         </is>
       </c>
       <c r="F33" s="8" t="n"/>
-      <c r="G33" s="20" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
     </row>
     <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>注1）令和8年9月29日のご指示により、15件は一旦そのまま計画素案に残している。「移す場合の移し先の案」は、後日移すこととなった場合の候補である。
 注2）確認事項No.170として業務工程管理表に登録している。体裁（小見出し【　】の階層ほか）は保留となっており、確認事項No.171による。</t>
@@ -11704,7 +12462,7 @@
           <t>小見出し【　】</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。第9期計画は「１」「（１）」「ア」の階層で小見出しを置いている。</t>
         </is>
@@ -11729,7 +12487,7 @@
           <t>表の体裁</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>第9期計画と同じ。</t>
         </is>
@@ -11754,7 +12512,7 @@
           <t>図の体裁</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>第9期計画と同じ。</t>
         </is>
@@ -11779,7 +12537,7 @@
           <t>注記</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>第9期計画と同じ。</t>
         </is>
@@ -11804,7 +12562,7 @@
           <t>未確定箇所の記号</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>
@@ -11829,7 +12587,7 @@
           <t>感度分析の表（前提を動かした場合の幅）</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>
@@ -11854,7 +12612,7 @@
           <t>対比の表（○○の置き方によるちがい）</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>
@@ -11879,7 +12637,7 @@
           <t>検定の結果</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>
@@ -11904,7 +12662,7 @@
           <t>町別の値</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>第9期計画と同じ。</t>
         </is>
@@ -11929,7 +12687,7 @@
           <t>資料編の構成</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>第9期計画には、意見公募手続の実施状況、策定委員会の委嘱期間・組織・委員名簿・開催の状況、用語解説、区域内の事業所一覧を資料編に掲げる例がある。</t>
         </is>
@@ -11954,7 +12712,7 @@
           <t>他団体の固有名称</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>
@@ -11971,7 +12729,7 @@
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>注）第9期計画の図表レイアウト・フォント・表の体裁を維持することは発注者の指示による。第9期計画にない体裁を用いる場合は、その必要があることを示したうえでお決めいただく。</t>
         </is>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -182,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,6 +234,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -699,7 +705,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -765,7 +771,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -1088,7 +1094,7 @@
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1027段落153表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1031段落153表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -1339,7 +1345,7 @@
           <t>公表版の全章</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>公表版のみ是正</t>
         </is>
@@ -1369,7 +1375,7 @@
           <t>公表版 参考・第6章第2節</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>一部対応</t>
         </is>
@@ -1579,7 +1585,7 @@
           <t>資料編</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>一部対応・協議</t>
         </is>
@@ -1609,7 +1615,7 @@
           <t>計画素案 全体</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>記録した</t>
         </is>
@@ -1639,7 +1645,7 @@
           <t>計画素案 資料7</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="24" t="inlineStr">
         <is>
           <t>変更しない</t>
         </is>
@@ -1870,7 +1876,7 @@
           <t>公表版の作り</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>設計で防いだ</t>
         </is>
@@ -1900,7 +1906,7 @@
           <t>公表版の表紙・自己点検12</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>設計で防いだ</t>
         </is>
@@ -1930,7 +1936,7 @@
           <t>公表版の自己点検3・4・5</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>設計で防いだ</t>
         </is>
@@ -1990,7 +1996,7 @@
           <t>公表版の自己点検16</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>設計で防いだ</t>
         </is>
@@ -2020,7 +2026,7 @@
           <t>公表版の自己点検15</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>設計で防いだ</t>
         </is>
@@ -2374,7 +2380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2491,7 +2497,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表819段落（空段落・目次の行を除く）／実物1027段落（すべて）</t>
+          <t>本表823段落（空段落・目次の行を除く）／実物1031段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -3895,6 +3901,106 @@
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="10" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>原典により確かめた論点のIDがいずれも論点の一覧にあること</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>IDの照合</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>7件</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="10" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>原典と食い違っていたものが計画素案に反映されていること</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>素案の走査</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>要是正 1件／2通りの記載の説明 あり</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="10" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>原典により新たに分かった事項の反映先が素案に現にある章節であること</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>素案の章節との照合</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>存在しない章節 0件</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="10" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉法等改正法の改正事項に生産性向上推進のための協議会が入っていること</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>素案の走査</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>記載あり</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4211,7 +4317,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>8</v>
@@ -4220,7 +4326,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -4270,7 +4376,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
     </row>
@@ -4895,7 +5001,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
     </row>
@@ -4936,7 +5042,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>7</v>
@@ -4945,7 +5051,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -4990,7 +5096,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>14</v>
@@ -4999,7 +5105,7 @@
         <v>11</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -5208,7 +5314,7 @@
       </c>
       <c r="B55" s="16" t="inlineStr"/>
       <c r="C55" s="15" t="n">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="D55" s="15" t="n">
         <v>153</v>
@@ -5217,7 +5323,7 @@
         <v>73</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G55" s="16" t="inlineStr"/>
     </row>
@@ -6778,7 +6884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7394,10 +7500,10 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1">
+    <row r="26" ht="56" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>介護給付費分科会は介護報酬（単位数・算定の要件・運営の基準）を扱う別の審議の場である。課長会議資料及び介護保険部会の対比ではこの場の論点を軸に持っていなかった。本表は当区域に直結するものに絞って掲げる（全31件の対比は別冊「介護給付費分科会の論点整理の受領点検」による）。**資料の原本を確認できていないため、計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない**（確認事項No.182）。</t>
+          <t>介護給付費分科会は介護報酬（単位数・算定の要件・運営の基準）を扱う別の審議の場である。課長会議資料及び介護保険部会の対比ではこの場の論点を軸に持っていなかった。本表は当区域に直結するものに絞って掲げる（全31件の対比は別冊「介護給付費分科会の論点整理の受領点検」による）。令和8年10月14日に資料11件（第268回・第269回・第270回）のご提供を受け、うち7件の論点を原典により確かめた（別冊「介護給付費分科会資料（原典）の受領点検」）。**計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない**（確認事項No.182）。</t>
         </is>
       </c>
     </row>
@@ -7429,6 +7535,11 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
+          <t>原典</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
           <t>本計画における取扱い</t>
         </is>
       </c>
@@ -7459,7 +7570,12 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>第268回 資料1（詳細判明）</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>改定率を据え置き（区分C）とし、1％あたり月額の感度を掲げている。諮問・答申（令和9年1月頃）は当方の第2次概算より後である</t>
         </is>
@@ -7491,7 +7607,12 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>日常生活圏域の設定（No.88）と中長期の見通し（令和17・22年度）を掲げている。圏域別の受入能力・移動時間は把握していない（No.116）</t>
         </is>
@@ -7523,7 +7644,12 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>第268回 資料1（詳細判明）</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>特定地域の判定（基準②の試算）と24時間対応の確保方策の選択肢を掲げている。配置の弾力化・訪問系の包括的な評価は反映していない</t>
         </is>
@@ -7555,7 +7681,12 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>訪問介護の1人1月あたり利用回数が全国の1.87倍であることを把握している。移動負担・依頼辞退は調査していない</t>
         </is>
@@ -7587,7 +7718,12 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>第269回 資料1 p15・p34（要是正）</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>夜間対応型訪問介護の区分を立てている（実績なし）。定期巡回への移行（移行猶予 令和11年3月）は反映していない</t>
         </is>
@@ -7619,7 +7755,12 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>認知症対応型共同生活介護の定員（99人＋［要確認］）と令和11年度 月85.2人を掲げている</t>
         </is>
@@ -7651,7 +7792,12 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>通所介護・地域密着型通所介護・認知症対応型通所介護の見込量を立てている。認知症対応型通所は区域内に事業所がないが給付がある</t>
         </is>
@@ -7683,7 +7829,12 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>第270回 資料4 p14（詳細判明）</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>短期入所生活介護の見込量を立てている。**積雪期の季節利用に係る例外は当区域に直接関わる**</t>
         </is>
@@ -7715,7 +7866,12 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>短期入所療養介護（老健・病院等・介護医療院）の見込量を立てている。総合医学管理加算の限度額外扱いは反映していない</t>
         </is>
@@ -7747,7 +7903,12 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>第270回 資料1 p32・p33（詳細判明）</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>介護老人福祉施設（定員160人）・地域密着型（62人）の定員と見込量の照合を掲げている。実稼働床・休床は把握していない</t>
         </is>
@@ -7779,7 +7940,12 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>介護老人保健施設3施設240人・介護医療院の見込量と、入所の経路（新規入所の57.0％が病院・診療所）を掲げている</t>
         </is>
@@ -7811,7 +7977,12 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>第270回 資料1 p56、第269回 資料1 p20 ほか（詳細判明）</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>介護保険の指定を受けない住まい339人・戸を把握している。**同一建物減算に代わる報酬区分の見直しは単価に及ぶ**</t>
         </is>
@@ -7843,7 +8014,12 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>協力医療機関の要件強化の対象10事業所を掲げている</t>
         </is>
@@ -7875,7 +8051,12 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>地域区分による単価は算定の基礎に含まれる。多床室の室料負担は利用者負担であり給付費とは別に扱う</t>
         </is>
@@ -7907,7 +8088,12 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>国の第10期基本指針（案）別表11事項への対応を資料6で整理し、北海道の第10期支援計画が未策定であることを掲げている</t>
         </is>
@@ -7939,7 +8125,12 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>介護情報基盤の工程（令和10年4月1日 本格運用）を掲げている（No.175）</t>
         </is>
@@ -7971,7 +8162,12 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>未受領</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>第7期給付適正化計画と保険料の算定を掲げている。2割負担の範囲は反映していない（No.33）</t>
         </is>
@@ -8474,7 +8670,7 @@
           <t>第1章第8節、第5章 基本目標3</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>未追加。北海道の計画の改定時期の確認を要する</t>
         </is>
@@ -8504,7 +8700,7 @@
           <t>第6章第4節4</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>決定待ち（確認事項No.88）</t>
         </is>
@@ -8534,7 +8730,7 @@
           <t>第6章第4節1</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>決定待ち（確認事項No.88・No.84）</t>
         </is>
@@ -8564,7 +8760,7 @@
           <t>第3章第4節</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>未受領。提供され次第、評価に加えるかを協議する</t>
         </is>
@@ -8722,7 +8918,7 @@
       <c r="E6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -8798,7 +8994,7 @@
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -8836,7 +9032,7 @@
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -8874,7 +9070,7 @@
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -9021,7 +9217,7 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>2</v>
@@ -9064,7 +9260,7 @@
       <c r="E15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -9102,12 +9298,12 @@
       <c r="E16" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9216,7 +9412,7 @@
       <c r="E19" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -9254,7 +9450,7 @@
       <c r="E20" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -9292,7 +9488,7 @@
       <c r="E21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -9330,7 +9526,7 @@
       <c r="E22" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -9444,12 +9640,12 @@
       <c r="E25" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9482,7 +9678,7 @@
       <c r="E26" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -9520,7 +9716,7 @@
       <c r="E27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -9558,7 +9754,7 @@
       <c r="E28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -9596,12 +9792,12 @@
       <c r="E29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9634,7 +9830,7 @@
       <c r="E30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -9672,7 +9868,7 @@
       <c r="E31" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -9710,12 +9906,12 @@
       <c r="E32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9748,7 +9944,7 @@
       <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="23" t="inlineStr">
+      <c r="F33" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -9786,12 +9982,12 @@
       <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -9824,7 +10020,7 @@
       <c r="E35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="23" t="inlineStr">
+      <c r="F35" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -9862,7 +10058,7 @@
       <c r="E36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -9900,7 +10096,7 @@
       <c r="E37" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -9938,7 +10134,7 @@
       <c r="E38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="22" t="inlineStr">
+      <c r="F38" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -10014,7 +10210,7 @@
       <c r="E40" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="23" t="inlineStr">
+      <c r="F40" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -10052,7 +10248,7 @@
       <c r="E41" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="23" t="inlineStr">
+      <c r="F41" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -10090,12 +10286,12 @@
       <c r="E42" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="22" t="inlineStr">
+      <c r="F42" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G42" s="22" t="inlineStr">
+      <c r="G42" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10166,12 +10362,12 @@
       <c r="E44" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="22" t="inlineStr">
+      <c r="F44" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G44" s="22" t="inlineStr">
+      <c r="G44" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10204,12 +10400,12 @@
       <c r="E45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="22" t="inlineStr">
+      <c r="F45" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G45" s="22" t="inlineStr">
+      <c r="G45" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10356,12 +10552,12 @@
       <c r="E49" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="22" t="inlineStr">
+      <c r="F49" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G49" s="22" t="inlineStr">
+      <c r="G49" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10394,12 +10590,12 @@
       <c r="E50" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="22" t="inlineStr">
+      <c r="F50" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G50" s="22" t="inlineStr">
+      <c r="G50" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10660,7 +10856,7 @@
       <c r="E57" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F57" s="22" t="inlineStr">
+      <c r="F57" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -10698,12 +10894,12 @@
       <c r="E58" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="22" t="inlineStr">
+      <c r="F58" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G58" s="22" t="inlineStr">
+      <c r="G58" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10736,7 +10932,7 @@
       <c r="E59" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="23" t="inlineStr">
+      <c r="F59" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -10850,7 +11046,7 @@
       <c r="E62" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F62" s="22" t="inlineStr">
+      <c r="F62" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -10888,7 +11084,7 @@
       <c r="E63" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="23" t="inlineStr">
+      <c r="F63" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -10926,12 +11122,12 @@
       <c r="E64" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="22" t="inlineStr">
+      <c r="F64" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G64" s="22" t="inlineStr">
+      <c r="G64" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -10964,7 +11160,7 @@
       <c r="E65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="23" t="inlineStr">
+      <c r="F65" s="25" t="inlineStr">
         <is>
           <t>第9期</t>
         </is>
@@ -11078,12 +11274,12 @@
       <c r="E68" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="22" t="inlineStr">
+      <c r="F68" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G68" s="22" t="inlineStr">
+      <c r="G68" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -11116,7 +11312,7 @@
       <c r="E69" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F69" s="22" t="inlineStr">
+      <c r="F69" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -11154,12 +11350,12 @@
       <c r="E70" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F70" s="22" t="inlineStr">
+      <c r="F70" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G70" s="22" t="inlineStr">
+      <c r="G70" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -11192,12 +11388,12 @@
       <c r="E71" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F71" s="22" t="inlineStr">
+      <c r="F71" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G71" s="22" t="inlineStr">
+      <c r="G71" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -11225,12 +11421,12 @@
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F72" s="22" t="inlineStr">
+      <c r="F72" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -11340,7 +11536,7 @@
       <c r="E75" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="22" t="inlineStr">
+      <c r="F75" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -11374,12 +11570,12 @@
       <c r="E76" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F76" s="22" t="inlineStr">
+      <c r="F76" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G76" s="22" t="inlineStr">
+      <c r="G76" s="24" t="inlineStr">
         <is>
           <t>協議</t>
         </is>
@@ -11408,7 +11604,7 @@
       <c r="E77" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F77" s="22" t="inlineStr">
+      <c r="F77" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
@@ -11783,7 +11979,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1027段落153表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1031段落153表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>
@@ -11854,7 +12050,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n"/>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11887,7 +12083,7 @@
         </is>
       </c>
       <c r="F19" s="8" t="n"/>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11920,7 +12116,7 @@
         </is>
       </c>
       <c r="F20" s="8" t="n"/>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11953,7 +12149,7 @@
         </is>
       </c>
       <c r="F21" s="8" t="n"/>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -11986,7 +12182,7 @@
         </is>
       </c>
       <c r="F22" s="8" t="n"/>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12019,7 +12215,7 @@
         </is>
       </c>
       <c r="F23" s="8" t="n"/>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12052,7 +12248,7 @@
         </is>
       </c>
       <c r="F24" s="8" t="n"/>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12085,7 +12281,7 @@
         </is>
       </c>
       <c r="F25" s="8" t="n"/>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12118,7 +12314,7 @@
         </is>
       </c>
       <c r="F26" s="8" t="n"/>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12151,7 +12347,7 @@
         </is>
       </c>
       <c r="F27" s="8" t="n"/>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12184,7 +12380,7 @@
         </is>
       </c>
       <c r="F28" s="8" t="n"/>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12217,7 +12413,7 @@
         </is>
       </c>
       <c r="F29" s="8" t="n"/>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12250,7 +12446,7 @@
         </is>
       </c>
       <c r="F30" s="8" t="n"/>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12283,7 +12479,7 @@
         </is>
       </c>
       <c r="F31" s="8" t="n"/>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12316,7 +12512,7 @@
         </is>
       </c>
       <c r="F32" s="8" t="n"/>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12345,7 +12541,7 @@
         </is>
       </c>
       <c r="F33" s="8" t="n"/>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="24" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
@@ -12462,7 +12658,7 @@
           <t>小見出し【　】</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。第9期計画は「１」「（１）」「ア」の階層で小見出しを置いている。</t>
         </is>
@@ -12562,7 +12758,7 @@
           <t>未確定箇所の記号</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>
@@ -12587,7 +12783,7 @@
           <t>感度分析の表（前提を動かした場合の幅）</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>
@@ -12612,7 +12808,7 @@
           <t>対比の表（○○の置き方によるちがい）</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>
@@ -12637,7 +12833,7 @@
           <t>検定の結果</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>
@@ -12687,7 +12883,7 @@
           <t>資料編の構成</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>第9期計画には、意見公募手続の実施状況、策定委員会の委嘱期間・組織・委員名簿・開催の状況、用語解説、区域内の事業所一覧を資料編に掲げる例がある。</t>
         </is>
@@ -12712,7 +12908,7 @@
           <t>他団体の固有名称</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>第9期計画にない体裁である。</t>
         </is>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="B28" s="15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="15" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1031段落153表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1038段落153表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表823段落（空段落・目次の行を除く）／実物1031段落（すべて）</t>
+          <t>本表829段落（空段落・目次の行を除く）／実物1038段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>73件</t>
+          <t>74件</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>16件（全73件）</t>
+          <t>16件（全74件）</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>11件</t>
         </is>
       </c>
       <c r="E64" s="18" t="inlineStr">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>8</v>
@@ -4326,7 +4326,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -4417,18 +4417,22 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>13</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>【　】の見出しが5件あり、記述の単位が多い。</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -4917,7 +4921,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>7</v>
@@ -4926,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
@@ -5000,10 +5004,14 @@
       <c r="E41" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F41" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G41" s="5" t="inlineStr"/>
+      <c r="F41" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所が集中している。</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -5134,7 +5142,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
     </row>
@@ -5314,16 +5322,16 @@
       </c>
       <c r="B55" s="16" t="inlineStr"/>
       <c r="C55" s="15" t="n">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="D55" s="15" t="n">
         <v>153</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="G55" s="16" t="inlineStr"/>
     </row>
@@ -7503,7 +7511,7 @@
     <row r="26" ht="56" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>介護給付費分科会は介護報酬（単位数・算定の要件・運営の基準）を扱う別の審議の場である。課長会議資料及び介護保険部会の対比ではこの場の論点を軸に持っていなかった。本表は当区域に直結するものに絞って掲げる（全31件の対比は別冊「介護給付費分科会の論点整理の受領点検」による）。令和8年10月14日に資料11件（第268回・第269回・第270回）のご提供を受け、うち7件の論点を原典により確かめた（別冊「介護給付費分科会資料（原典）の受領点検」）。**計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない**（確認事項No.182）。</t>
+          <t>介護給付費分科会は介護報酬（単位数・算定の要件・運営の基準）を扱う別の審議の場である。課長会議資料及び介護保険部会の対比ではこの場の論点を軸に持っていなかった。本表は当区域に直結するものに絞って掲げる（全31件の対比は別冊「介護給付費分科会の論点整理の受領点検」による）。令和8年10月14日に資料25件（第268回・第269回・第270回）のご提供を受け、うち11件の論点を原典により確かめた（別冊「介護給付費分科会資料（原典）の受領点検」）。**計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない**（確認事項No.182）。</t>
         </is>
       </c>
     </row>
@@ -8014,9 +8022,9 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F40" s="21" t="inlineStr">
-        <is>
-          <t>未受領</t>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>第264回 資料2 p70・p72（詳細判明）</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -8051,9 +8059,9 @@
           <t>ある</t>
         </is>
       </c>
-      <c r="F41" s="21" t="inlineStr">
-        <is>
-          <t>未受領</t>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>第262回 資料3、第264回 資料5（詳細判明）</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -8789,7 +8797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9141,7 +9149,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -9635,10 +9643,10 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
@@ -9669,18 +9677,18 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>運営法人の状況</t>
+          <t>指定を受けない住まいと在宅サービスの関係</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr">
@@ -9690,7 +9698,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
+          <t>社会福祉法等の一部を改正する法律により、有料老人ホーム及びサービス付き高齢者向け住宅の入居定員を勘案することが明確化された（法第117条）。指定を受けない住まいの入居者は在宅の受給者として居宅サービスを利用するため、入居定員を勘案することの意味を示すものである。</t>
         </is>
       </c>
     </row>
@@ -9702,20 +9710,20 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>調査の対象者の範囲</t>
+          <t>運営法人の状況</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
           <t>独自</t>
@@ -9728,7 +9736,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
+          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
         </is>
       </c>
     </row>
@@ -9745,18 +9753,18 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>1　主要指標の状況</t>
+          <t>調査の対象者の範囲</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
@@ -9766,7 +9774,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも調査結果の掲載がある。</t>
+          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
         </is>
       </c>
     </row>
@@ -9783,28 +9791,28 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2　年齢構成の影響と町間の差</t>
+          <t>1　主要指標の状況</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G29" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
+          <t>第9期計画にも調査結果の掲載がある。</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9829,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>3　同規模の保険者との比較</t>
+          <t>2　年齢構成の影響と町間の差</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
@@ -9835,14 +9843,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>基本指針が地域間比較を求めている。</t>
+          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -9859,11 +9867,11 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>4　社会参加との関連</t>
+          <t>3　同規模の保険者との比較</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="6" t="n">
         <v>1</v>
@@ -9880,7 +9888,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
+          <t>基本指針が地域間比較を求めている。</t>
         </is>
       </c>
     </row>
@@ -9897,7 +9905,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>5　暮らし向きとの関連</t>
+          <t>4　社会参加との関連</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
@@ -9911,14 +9919,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G32" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
+          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9943,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>6　生活実態の主な値</t>
+          <t>5　暮らし向きとの関連</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
@@ -9944,19 +9952,19 @@
       <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の第2章にも生活実態の記載がある。</t>
+          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
         </is>
       </c>
     </row>
@@ -9973,7 +9981,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>7　地区別の状況</t>
+          <t>6　生活実態の主な値</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
@@ -9982,19 +9990,19 @@
       <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G34" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F34" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
+          <t>第9期計画の第2章にも生活実態の記載がある。</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10019,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>8　前回調査との比較</t>
+          <t>7　地区別の状況</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
@@ -10020,19 +10028,19 @@
       <c r="E35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>経年比較は計画に置く。</t>
+          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
         </is>
       </c>
     </row>
@@ -10044,23 +10052,23 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>重度者の在宅・居住系割合の上昇</t>
+          <t>8　前回調査との比較</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F36" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G36" s="18" t="inlineStr">
@@ -10070,7 +10078,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
+          <t>経年比較は計画に置く。</t>
         </is>
       </c>
     </row>
@@ -10087,11 +10095,11 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>在宅生活の継続に必要な生活支援</t>
+          <t>重度者の在宅・居住系割合の上昇</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>1</v>
@@ -10108,7 +10116,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2・3の根拠となる。</t>
+          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -10120,16 +10128,16 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>第10期分の介護人材実態調査の結果</t>
+          <t>在宅生活の継続に必要な生活支援</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>1</v>
@@ -10146,35 +10154,35 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
+          <t>第5章 基本目標2・3の根拠となる。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の事業費（決算）</t>
+          <t>第10期分の介護人材実態調査の結果</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G39" s="18" t="inlineStr">
@@ -10184,7 +10192,7 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
+          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
         </is>
       </c>
     </row>
@@ -10201,18 +10209,18 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の通いの場の展開状況</t>
+          <t>令和6年度の事業費（決算）</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G40" s="18" t="inlineStr">
@@ -10222,7 +10230,7 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも通いの場の記載がある。</t>
+          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
         </is>
       </c>
     </row>
@@ -10239,11 +10247,11 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>一般介護予防事業の実施状況（令和6年度）</t>
+          <t>令和6年度の通いの場の展開状況</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>1</v>
@@ -10260,7 +10268,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも実施状況の記載がある。</t>
+          <t>第9期計画にも通いの場の記載がある。</t>
         </is>
       </c>
     </row>
@@ -10272,71 +10280,71 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
+          <t>一般介護予防事業の実施状況（令和6年度）</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G42" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
+          <t>第9期計画にも実施状況の記載がある。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>第9期の目標指標との接続</t>
+          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G43" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>4</v>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
+          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
         </is>
       </c>
     </row>
@@ -10353,28 +10361,28 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>H07・H08・H12・H16の振替について</t>
+          <t>第9期の目標指標との接続</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>0</v>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
+          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -10391,14 +10399,14 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>H13・H14の定義変更について</t>
+          <t>H07・H08・H12・H16の振替について</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
@@ -10412,7 +10420,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
         </is>
       </c>
     </row>
@@ -10429,52 +10437,52 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>H15の分母について</t>
+          <t>H13・H14の定義変更について</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G46" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>0</v>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
+          <t>同上。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>基本目標5</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>介護給付費の適正化（第7期給付適正化計画）</t>
+          <t>H15の分母について</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" s="18" t="inlineStr">
         <is>
@@ -10488,31 +10496,31 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
+          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>基本目標5</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>要介護度別の認定者数</t>
+          <t>介護給付費の適正化（第7期給付適正化計画）</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" s="18" t="inlineStr">
         <is>
@@ -10526,7 +10534,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
+          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
         </is>
       </c>
     </row>
@@ -10543,28 +10551,28 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>認定率の置き方によるちがい</t>
+          <t>要介護度別の認定者数</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
+          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
         </is>
       </c>
     </row>
@@ -10581,11 +10589,11 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎による推計のちがい</t>
+          <t>認定率の置き方によるちがい</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>1</v>
@@ -10602,7 +10610,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>同上。案Cを採る理由の説明としては要る。</t>
+          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
         </is>
       </c>
     </row>
@@ -10614,33 +10622,33 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定方法</t>
+          <t>人口の基礎による推計のちがい</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F51" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G51" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>1</v>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>見込量の前提を示すもので、計画に置く。</t>
+          <t>同上。案Cを採る理由の説明としては要る。</t>
         </is>
       </c>
     </row>
@@ -10657,15 +10665,15 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>利用回（日）数</t>
+          <t>見込量の算定方法</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E52" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E52" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F52" s="18" t="inlineStr">
         <is>
           <t>法定</t>
@@ -10678,7 +10686,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号が回数・日数を求めている。</t>
+          <t>見込量の前提を示すもので、計画に置く。</t>
         </is>
       </c>
     </row>
@@ -10690,16 +10698,16 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業の量の見込み</t>
+          <t>利用回（日）数</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>1</v>
@@ -10716,7 +10724,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号。</t>
+          <t>法第117条第2項第1号が回数・日数を求めている。</t>
         </is>
       </c>
     </row>
@@ -10733,11 +10741,11 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業費</t>
+          <t>介護予防・日常生活支援総合事業の量の見込み</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>1</v>
@@ -10754,7 +10762,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号。</t>
+          <t>法第117条第2項第2号。</t>
         </is>
       </c>
     </row>
@@ -10771,14 +10779,14 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実施状況</t>
+          <t>地域支援事業費</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="18" t="inlineStr">
         <is>
@@ -10792,7 +10800,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
+          <t>法第117条第3項第2号。</t>
         </is>
       </c>
     </row>
@@ -10804,20 +10812,20 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>定員と見込量の照合</t>
+          <t>認知症総合支援事業の実施状況</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F56" s="18" t="inlineStr">
         <is>
           <t>法定</t>
@@ -10830,7 +10838,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数の算定の根拠となる。</t>
+          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -10847,18 +10855,18 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
+          <t>定員と見込量の照合</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G57" s="18" t="inlineStr">
@@ -10868,7 +10876,7 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
+          <t>必要利用定員総数の算定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -10885,28 +10893,28 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>供給の担い手の集中</t>
+          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G58" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G58" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
+          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
         </is>
       </c>
     </row>
@@ -10923,28 +10931,28 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>現況（令和8年度）</t>
+          <t>供給の担い手の集中</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G59" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも現況の記載がある。</t>
+          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
         </is>
       </c>
     </row>
@@ -10961,18 +10969,18 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>第10期における必要利用定員総数</t>
+          <t>現況（令和8年度）</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F60" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G60" s="18" t="inlineStr">
@@ -10982,7 +10990,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
+          <t>第9期計画にも現況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -10999,11 +11007,11 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
+          <t>第10期における必要利用定員総数</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E61" s="6" t="n">
         <v>1</v>
@@ -11020,7 +11028,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
+          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
         </is>
       </c>
     </row>
@@ -11032,23 +11040,23 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>入所の経路からみた整備の考え方</t>
+          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G62" s="18" t="inlineStr">
@@ -11058,7 +11066,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
+          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11070,23 +11078,23 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>第9期の状況</t>
+          <t>入所の経路からみた整備の考え方</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F63" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G63" s="18" t="inlineStr">
@@ -11096,7 +11104,7 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも前期の状況の記載がある。</t>
+          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11121,7 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
+          <t>第9期の状況</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
@@ -11122,19 +11130,19 @@
       <c r="E64" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G64" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F64" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+          <t>第9期計画にも前期の状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -11151,28 +11159,28 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の状況</t>
+          <t>期別の必要保険料月額と基準額の対比</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G65" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F65" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>基金の取崩しは保険料の決定に直結する。</t>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -11189,18 +11197,18 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>保険料収納率と所得段階別被保険者数の実績</t>
+          <t>介護給付費準備基金の状況</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F66" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G66" s="18" t="inlineStr">
@@ -11210,7 +11218,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>保険料算定の基礎。</t>
+          <t>基金の取崩しは保険料の決定に直結する。</t>
         </is>
       </c>
     </row>
@@ -11227,11 +11235,11 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>所得段階と乗率の置き方</t>
+          <t>保険料収納率と所得段階別被保険者数の実績</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>1</v>
@@ -11248,7 +11256,7 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
+          <t>保険料算定の基礎。</t>
         </is>
       </c>
     </row>
@@ -11265,28 +11273,28 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>保険料と必要保険料月額との関係</t>
+          <t>所得段階と乗率の置き方</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F68" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G68" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G68" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
+          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11303,28 +11311,28 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>暫定算定</t>
+          <t>保険料と必要保険料月額との関係</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G69" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
         </is>
       </c>
     </row>
@@ -11341,11 +11349,11 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>給付費の置き方によるちがい</t>
+          <t>暫定算定</t>
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E70" s="6" t="n">
         <v>1</v>
@@ -11355,14 +11363,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G70" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
+          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
         </is>
       </c>
     </row>
@@ -11379,11 +11387,11 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映した場合</t>
+          <t>給付費の置き方によるちがい</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E71" s="6" t="n">
         <v>1</v>
@@ -11400,7 +11408,7 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
         </is>
       </c>
     </row>
@@ -11417,28 +11425,28 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>前提を動かした場合の幅</t>
+          <t>サービス別の趨勢を反映した場合</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E72" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F72" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G72" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11455,18 +11463,18 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>所得段階の置き方による保険料の違い</t>
+          <t>前提を動かした場合の幅</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>3</v>
+      </c>
+      <c r="F73" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G73" s="18" t="inlineStr">
@@ -11476,7 +11484,7 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>国は第10期において高所得者の標準乗率の見直し及び課税化に伴う上昇の緩和を含めた標準段階の見直しを検討課題として挙げている（令和8年9月18日社会保障審議会介護保険部会）。段階の置き方により基準額が動くため、3案の比較を掲げる（確認事項No.33）。令和8年10月7日に新設した。</t>
+          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
         </is>
       </c>
     </row>
@@ -11488,16 +11496,16 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>低所得者に係る負担軽減の見直し</t>
+          <t>所得段階の置き方による保険料の違い</t>
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E74" s="6" t="n">
         <v>1</v>
@@ -11514,31 +11522,35 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。令和8年10月7日に、見出しを「第10期に施行される見直し」から改めた。一定以上所得基準は結論を得る段階であり施行が決まっていないため、見出しで施行を断定しない。</t>
+          <t>国は第10期において高所得者の標準乗率の見直し及び課税化に伴う上昇の緩和を含めた標準段階の見直しを検討課題として挙げている（令和8年9月18日社会保障審議会介護保険部会）。段階の置き方により基準額が動くため、3案の比較を掲げる（確認事項No.33）。令和8年10月7日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="44" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>資料5</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>第7節</t>
+        </is>
+      </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの使用データ</t>
+          <t>低所得者に係る負担軽減の見直し</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G75" s="18" t="inlineStr">
@@ -11548,41 +11560,41 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>出典の明示に当たる。</t>
+          <t>令和8年3月課長会議資料により追加した。令和8年10月7日に、見出しを「第10期に施行される見直し」から改めた。一定以上所得基準は結論を得る段階であり施行が決まっていないため、見出しで施行を断定しない。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="44" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>資料7</t>
+          <t>資料5</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr"/>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>採番と表記の規則</t>
+          <t>地域包括ケア「見える化」システムの使用データ</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G76" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
+          <t>出典の明示に当たる。</t>
         </is>
       </c>
     </row>
@@ -11595,33 +11607,67 @@
       <c r="B77" s="5" t="inlineStr"/>
       <c r="C77" s="5" t="inlineStr">
         <is>
+          <t>採番と表記の規則</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="44" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>資料7</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr"/>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
           <t>未確定箇所の表示</t>
         </is>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D78" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E78" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F77" s="24" t="inlineStr">
+      <c r="F78" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G77" s="18" t="inlineStr">
+      <c r="G78" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H78" s="5" t="inlineStr">
         <is>
           <t>［要協議］等の記号の意味を示すものであり、本文を読むために必要な凡例に当たる。記号が0になった時点で落とす。</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="48" customHeight="1">
-      <c r="A79" s="12" t="inlineStr">
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="12" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -11630,7 +11676,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A80:H80"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -11979,7 +12025,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1031段落153表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1038段落153表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>16</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="B28" s="15" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D28" s="15" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1038段落153表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1060段落156表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表153表／実物153表</t>
+          <t>本表156表／実物156表</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表829段落（空段落・目次の行を除く）／実物1038段落（すべて）</t>
+          <t>本表849段落（空段落・目次の行を除く）／実物1060段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>74件</t>
+          <t>79件</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>台帳184件</t>
+          <t>台帳186件</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>16件（全74件）</t>
+          <t>16件（全79件）</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>142／142表</t>
+          <t>145／145表</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>153／153表</t>
+          <t>156／156表</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>第2項（改正後）の行</t>
+          <t>改正後の行</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>5件（第2項第3号（改正後）、第2項第4号（改正後）、第3項第4号・第5号（改正後）、第5項（改正後）、第14項（改正後））</t>
         </is>
       </c>
       <c r="E48" s="18" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>第1章第2節、第1章第8節</t>
+          <t>第1章第2節、第1章第8節、第1章第9節</t>
         </is>
       </c>
       <c r="E52" s="18" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法等改正法の改正事項に生産性向上推進のための協議会が入っていること</t>
+          <t>社会福祉法等改正法の改正事項に法第120条の3の協議会が入っており、市町村が構成員であることを書いていること</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>記載あり</t>
+          <t>第120条の3=あり／構成員として参画=あり</t>
         </is>
       </c>
       <c r="E67" s="18" t="inlineStr">
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
@@ -4151,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
     </row>
@@ -4226,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
     </row>
@@ -4317,20 +4317,20 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>未確定箇所が集中している。</t>
+          <t>未確定箇所が集中している。【　】の見出しが7件あり、記述の単位が多い。</t>
         </is>
       </c>
     </row>
@@ -4417,20 +4417,20 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>13</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>【　】の見出しが5件あり、記述の単位が多い。</t>
+          <t>【　】の見出しが6件あり、記述の単位が多い。</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>1</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
     </row>
@@ -4825,10 +4825,14 @@
       <c r="E34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G34" s="5" t="inlineStr"/>
+      <c r="F34" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所が集中している。</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
@@ -4896,7 +4900,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>3</v>
@@ -4904,10 +4908,14 @@
       <c r="E37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G37" s="5" t="inlineStr"/>
+      <c r="F37" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所が集中している。</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -4921,7 +4929,7 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>7</v>
@@ -4930,7 +4938,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
@@ -5005,7 +5013,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
@@ -5025,16 +5033,16 @@
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E42" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
     </row>
@@ -5079,7 +5087,7 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>1</v>
@@ -5322,16 +5330,16 @@
       </c>
       <c r="B55" s="16" t="inlineStr"/>
       <c r="C55" s="15" t="n">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="G55" s="16" t="inlineStr"/>
     </row>
@@ -5358,7 +5366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5578,7 +5586,7 @@
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>第2項（改正後）①</t>
+          <t>第2項第3号（改正後）</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -5588,12 +5596,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>中長期的なサービスの見通し（令和22年度を含む）を定めること。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。</t>
+          <t>介護給付等対象サービスの種類ごとの量及び地域支援事業の量に関する中長期的な推計。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。号は法律案要綱 第2の14（1）による。</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>第6章第1節（認定者数）、第6章第2節（見込量）、第6章第3節3（総給付費 令和17・22年度）</t>
+          <t>第2章第8節（中長期推計）、第6章第1節（認定者数）、第6章第2節（見込量）、第6章第3節3（総給付費 令和17・22年度）、第6章第3節2（地域支援事業の量の中長期的な推計）</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
@@ -5603,14 +5611,14 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月16日に見込量・給付費まで広げた。見える化システムが求める令和12・27・32年度は算定の側に置いている。</t>
+          <t>令和8年9月16日に見込量・給付費まで広げた。令和8年10月14日に、要綱により地域支援事業の量も対象であることを確かめ、令和17年度・令和22年度の量を算定して第6章第3節2に加えた。見える化システムが求める令和12・27・32年度は算定の側に置いている。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>第2項（改正後）②</t>
+          <t>第2項第4号（改正後）</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -5620,7 +5628,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>中長期的なサービスの見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めること。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。</t>
+          <t>介護給付等対象サービスを提供する体制の確保及び地域支援事業の実施に関し、中長期的な観点から市町村が取り組むべき施策に関する事項。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。号は法律案要綱 第2の14（1）による。</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -5635,7 +5643,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>①の推計の表を加えたことでは充足しない要件である。令和22年度の水準を踏まえた整備の考え方は、日常生活圏域ごとの必要利用定員総数の決定と併せて定める［要協議］。条文を受領していないため定めるべき事項の範囲は［要確認］（確認事項No.181）。</t>
+          <t>第3号の推計の表を加えたことでは充足しない要件である。令和22年度の水準を踏まえた整備の考え方は、日常生活圏域ごとの必要利用定員総数の決定と併せて定める［要協議］。要綱により号は確定したが、条文を受領していないため定めるべき事項の範囲は［要確認］（確認事項No.181）。</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5906,7 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>第3項［号 要確認］</t>
+          <t>第3項第4号・第5号（改正後）</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -5908,22 +5916,22 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>介護給付等対象サービスに従事する者の確保及び資質の向上並びにその業務の効率化及び質の向上に資する事業に関する事項。</t>
+          <t>①介護給付等対象サービスの提供における業務の効率化、質の向上その他の生産性の向上、介護支援専門員その他の当該業務に従事する者の確保及び資質の向上その他の質の高い介護給付等対象サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組に資する都道府県と連携した取組に関する事項　②介護支援専門員その他の地域支援事業に従事する者の確保及び資質の向上に資する都道府県と連携した取組に関する事項　③地域支援事業の実施における業務の効率化、質の向上その他の生産性の向上に資する都道府県と連携した取組に関する事項。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。号は法律案要綱 第2の14（2）による。</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>第2章第6節（介護人材の状況）、第5章 基本目標4（介護人材）</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>対応済</t>
+          <t>第2章第6節（介護人材の状況）、第5章 基本目標4（介護人材）、第5章 基本目標2（地域支援事業の実施）</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>介護人材の確保・定着、生産性向上、外国人職員の受入れを掲げている。第3項の号の番号は条文の受領前のものであり、本号の位置は［要確認］（確認事項No.181）。</t>
+          <t>介護人材の確保・定着、生産性向上、外国人職員の受入れを掲げている。令和8年10月14日に、要綱により3項目であること及びいずれも「都道府県と連携した取組」であることを確かめた。北海道が置く協議会（法第120条の3）への参画を第5章 基本目標4に加えたが、②地域支援事業に従事する者の確保及び③地域支援事業の実施における生産性の向上について、北海道と連携した取組を掲げていない［要協議］。</t>
         </is>
       </c>
     </row>
@@ -6151,130 +6159,130 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="56" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>第5項（改正後）</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>作成の基準</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>第2項第1号及び第2号並びに第3号の中長期的な推計を定めるに当たっては、①当該市町村が定める区域ごとの有料老人ホーム（老人福祉法第29条第1項の届出が行われているもの）及び登録有料老人ホーム並びに高齢者の居住の安定確保に関する法律に規定する登録住宅のそれぞれの入居定員総数　②当該市町村が属する都道府県が定める区域ごとの医療に関する専門的知識を有する者と介護サービス事業者、居宅における医療を提供する医療機関その他の関係者との連携の状況　を勘案しなければならない。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。項は法律案要綱 第2の14（3）による。</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節【区域ごとの入居定員総数（法第117条第5項による勘案）】、第2章第3節（高齢者向け住まいの状況）、第1章第8節（医療と介護の連携）、第6章第5節</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月14日に要綱により新設を確かめ、①について勘案したことを第2章第3節に明記した。入居定員総数は14施設445人（戸）であり、町別の内訳は第2章第3節第1項の表のとおりである。日常生活圏域が確定していないため区域ごとの整理は［要協議］（確認事項No.88）。②の都道府県が定める区域ごとの連携の状況は、上川中部医療圏の単位で把握できていない［要確認］。登録有料老人ホームに係る部分の施行は公布の日から起算して2年を超えない範囲内において政令で定める日である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>第14項（改正後）</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>策定の手続</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>第2項第3号の中長期的な推計を定め、又は変更しようとするときは、あらかじめ都道府県の意見を聴かなければならない。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。項は法律案要綱 第2の14（4）による。</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>第1章第5節【法令が定める手続】</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月14日に要綱により新設を確かめ、第1章第5節の手続の表に加えた。計画案についての意見の聴取と併せて行うか別に行うかは北海道に確認する［要確認］。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>注1）介護保険法は第215条までであり、広域連合の根拠は地方自治法第284条である。保険給付・保険料・施策は保険者（広域連合）を単位として定める。
 注2）条文を受領していないため、第1項・第2項・第3項以外の項は「第117条［項 要確認］」と記し項番号を書いていない（確認事項No.181）。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行っている。
-注3）第3項の号の番号は条文の受領前のものである。介護人材に係る事項は号の位置を確かめられないため「第3項［号 要確認］」と記している。
+注3）令和8年10月14日に社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。改正に係らない号の番号は条文の受領前のものである。
 注4）第117条は記載事項（第2項・第3項）のほかに、計画の性格、作成の基準、他計画との関係及び策定の手続を定めている。記載事項の号の対比だけでは、医療計画との整合性の確保、市町村老人福祉計画と一体のものとして作成すること、都道府県知事への提出が点検の外に出る。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>【介護保険法以外の関係法令との対比】</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>計画の記載事項は介護保険法第117条に限られない。市町村を名宛人とする法令については、本広域連合が地方自治法第284条により設けられ介護保険法上の保険者としての事務を共同処理するものであることから、市町村認知症施策推進計画と同じ整理により構成3町が定めるものと本計画に定めるものを分ける。</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>法令</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>名宛人</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>定めの内容</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>計画素案の反映先</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>原典の受領と残る課題</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="52" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>老人福祉法第20条の8</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>市町村</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>市町村老人福祉計画を定めるものとされ、老人福祉事業の量の目標を定める。同計画は市町村介護保険事業計画と一体のものとして作成する。</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>第1章第2節、第1章第8節</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>一部対応</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>未受領。令和8年10月14日に法令名及び一体作成の定めを加えた。構成3町の高齢者福祉計画が同計画に当たることの確認、一体作成の方法及び老人福祉事業の量の目標との関係は［要協議］（確認事項No.178）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="52" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>成年後見制度の利用の促進に関する法律第14条</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>市町村</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>国の基本計画を勘案して、成年後見制度の利用の促進に関する施策についての基本的な計画を定めるよう努めるものとされる。</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>第1章第2節、第5章 基本目標1（権利擁護・中核機関）</t>
-        </is>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>一部対応</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>未受領。令和8年10月14日に第1章第2節へ位置づけを加えた。構成3町における策定の状況及び中核機関の整備の状況は［要確認］（確認事項No.179）。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>高齢者虐待の防止、高齢者の養護者に対する支援等に関する法律</t>
+          <t>老人福祉法第20条の8</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -6284,44 +6292,44 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>通報の受理、高齢者の安全の確認、措置及び養護者の支援を市町村の事務とする。計画の記載を直接義務づけるものではない。</t>
+          <t>市町村老人福祉計画を定めるものとされ、老人福祉事業の量の目標を定める。同計画は市町村介護保険事業計画と一体のものとして作成する。</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>第1章第2節、第5章 基本目標1（3）（4）（5）</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>対応済</t>
+          <t>第1章第2節、第1章第8節</t>
+        </is>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>未受領。施策・主な事業・達成目標（虐待通報への48時間以内の安全確認率100％）を定めている。令和8年10月14日に第1章第2節へ法令名を加えた。</t>
+          <t>未受領。令和8年10月14日に法令名及び一体作成の定めを加えた。構成3町の高齢者福祉計画が同計画に当たることの確認、一体作成の方法及び老人福祉事業の量の目標との関係は［要協議］（確認事項No.178）。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="52" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法第3条</t>
+          <t>成年後見制度の利用の促進に関する法律第14条</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>―（基本理念）</t>
+          <t>市町村</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>認知症施策の基本理念を定める。</t>
+          <t>国の基本計画を勘案して、成年後見制度の利用の促進に関する施策についての基本的な計画を定めるよう努めるものとされる。</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>第1章第2節、第4章（基本理念）、第5章 基本目標2（3）</t>
+          <t>第1章第2節、第5章 基本目標1（権利擁護・中核機関）</t>
         </is>
       </c>
       <c r="E37" s="17" t="inlineStr">
@@ -6331,14 +6339,14 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>未受領。令和8年10月14日に基本理念に沿って施策を定める旨を加えた。各号の内容は［要確認］（確認事項No.149・No.181）。</t>
+          <t>未受領。令和8年10月14日に第1章第2節へ位置づけを加えた。構成3町における策定の状況及び中核機関の整備の状況は［要確認］（確認事項No.179）。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="52" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>同法第13条</t>
+          <t>高齢者虐待の防止、高齢者の養護者に対する支援等に関する法律</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -6348,12 +6356,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画を定めるよう努めるものとされる。</t>
+          <t>通報の受理、高齢者の安全の確認、措置及び養護者の支援を市町村の事務とする。計画の記載を直接義務づけるものではない。</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>第1章第2節、第1章第8節、第5章 基本目標2（3）、資料2</t>
+          <t>第1章第2節、第5章 基本目標1（3）（4）（5）</t>
         </is>
       </c>
       <c r="E38" s="18" t="inlineStr">
@@ -6363,29 +6371,29 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>未受領。構成3町がそれぞれ策定し、本計画は介護保険法第117条第3項による事項として認知症施策を掲げる（案B。令和8年9月16日 ご了承）。</t>
+          <t>未受領。施策・主な事業・達成目標（虐待通報への48時間以内の安全確認率100％）を定めている。令和8年10月14日に第1章第2節へ法令名を加えた。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="52" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>水防法／土砂災害警戒区域等における土砂災害防止対策の推進に関する法律</t>
+          <t>共生社会の実現を推進するための認知症基本法第3条</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の所有者又は管理者</t>
+          <t>―（基本理念）</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>市町村地域防災計画に定められた要配慮者利用施設について、避難確保計画の作成及び避難訓練の実施を求める。</t>
+          <t>認知症施策の基本理念を定める。</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>第1章第8節、第5章 基本目標5（3）（4）</t>
+          <t>第1章第2節、第4章（基本理念）、第5章 基本目標2（3）</t>
         </is>
       </c>
       <c r="E39" s="17" t="inlineStr">
@@ -6395,61 +6403,61 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>未受領。令和8年10月14日に施策及び主な事業へ加えた。対象施設及び作成の状況は構成3町の地域防災計画によるため［要確認］（確認事項No.180）。達成目標には数値を掲げていない。</t>
+          <t>未受領。令和8年10月14日に基本理念に沿って施策を定める旨を加えた。各号の内容は［要確認］（確認事項No.149・No.181）。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="52" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第78条の4</t>
+          <t>同法第13条</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>広域連合（条例）</t>
+          <t>市町村</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>地域密着型サービスの人員・設備・運営の基準を市町村（広域連合）の条例で定める。省令はその条例を定めるに当たっての基準である。</t>
+          <t>市町村認知症施策推進計画を定めるよう努めるものとされる。</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>第1章第9節1、第6章第4節</t>
-        </is>
-      </c>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>一部対応</t>
+          <t>第1章第2節、第1章第8節、第5章 基本目標2（3）、資料2</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>対応済</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>未受領。当該条例を受領していないため、令和6年改正後の省令に対応しているかを確認できない（確認事項No.95）。</t>
+          <t>未受領。構成3町がそれぞれ策定し、本計画は介護保険法第117条第3項による事項として認知症施策を掲げる（案B。令和8年9月16日 ご了承）。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="52" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）</t>
+          <t>水防法／土砂災害警戒区域等における土砂災害防止対策の推進に関する法律</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>―（改正法）</t>
+          <t>要配慮者利用施設の所有者又は管理者</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第117条の記載事項の追加（中長期的なサービスの見通し及びこれを踏まえた提供体制の確保等のための施策）、令和9年4月新設の3区分、特定地域の特例等。</t>
+          <t>市町村地域防災計画に定められた要配慮者利用施設について、避難確保計画の作成及び避難訓練の実施を求める。</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>第1章第9節2、第6章第1節〜第3節、第6章第5節</t>
+          <t>第1章第8節、第5章 基本目標5（3）（4）</t>
         </is>
       </c>
       <c r="E41" s="17" t="inlineStr">
@@ -6459,44 +6467,108 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>未受領。7件を整理済み（第1章第9節2）。改正後の条文の構成を確認できていないため、記載事項の点検は条文の番号ではなく内容を単位として行っている（確認事項No.89・No.181）。</t>
+          <t>未受領。令和8年10月14日に施策及び主な事業へ加えた。対象施設及び作成の状況は構成3町の地域防災計画によるため［要確認］（確認事項No.180）。達成目標には数値を掲げていない。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="52" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
+          <t>介護保険法第78条の4</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>広域連合（条例）</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービスの人員・設備・運営の基準を市町村（広域連合）の条例で定める。省令はその条例を定めるに当たっての基準である。</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節1、第6章第4節</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>未受領。当該条例を受領していないため、令和6年改正後の省令に対応しているかを確認できない（確認事項No.95）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="52" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>―（改正法）</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法第117条の記載事項の追加（中長期的なサービスの見通し及びこれを踏まえた提供体制の確保等のための施策）、令和9年4月新設の3区分、特定地域の特例等。</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節2、第6章第1節〜第3節、第6章第5節</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>未受領。7件を整理済み（第1章第9節2）。改正後の条文の構成を確認できていないため、記載事項の点検は条文の番号ではなく内容を単位として行っている（確認事項No.89・No.181）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="52" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>地方自治法第284条</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>―（広域連合の根拠）</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>広域連合は特別地方公共団体として設けられ、介護保険法上の保険者としての事務を共同処理する。</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>第1章第2節</t>
         </is>
       </c>
-      <c r="E42" s="18" t="inlineStr">
+      <c r="E44" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>未受領。介護保険法は第215条までであり第284条は存在しない。広域連合の根拠は地方自治法である。</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>注）本表の法令はいずれも条文を受領していない。「対応」は計画素案に当該の記述があるかの判定であり、条文との逐語の照合ではない。条文のご提供を確認事項No.181によりお願いしている。</t>
         </is>
@@ -6505,11 +6577,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8797,7 +8869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9187,10 +9259,10 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
@@ -9221,14 +9293,14 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>引き続き検討することとされた事項</t>
+          <t>施行の日</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
@@ -9242,35 +9314,35 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月18日社会保障審議会介護保険部会の資料により追加した。給付と負担の在り方として引き続き検討することとされた7事項を、本計画への影響が及び得る箇所と対にして掲げる。いずれも算定には織り込んでいない。令和8年10月7日に新設した。</t>
+          <t>社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）による。施行は原則として令和9年4月1日であるが4区分の例外があり、いずれも第10期計画の期間中に施行される。令和8年10月14日に要綱により新設した。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>第2章</t>
+          <t>第1章</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第9節</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>第10期の人口の基礎</t>
+          <t>介護保険法の改正（要綱 第2）</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G15" s="18" t="inlineStr">
@@ -9280,69 +9352,69 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>推計の基礎を示すもので、見込量の前提として要る。</t>
+          <t>改正事項ごとに内容・施行の日・本計画における取扱いを対にしたもの。従前は介護保険法と他の法律の改正を1つの表にまとめていた。令和8年10月14日に要綱により分けた。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>第2章</t>
+          <t>第1章</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第9節</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>第9期計画及び社人研推計との関係</t>
+          <t>社会福祉法その他の法律の改正（要綱 第1・第6から第8まで）</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>3</v>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
+          <t>社会福祉法・老人福祉法・社会福祉士及び介護福祉士法の改正のうち本計画に関わるもの。令和8年10月14日に要綱により新設した。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>第2章</t>
+          <t>第1章</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第9節</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>認知症高齢者の状況</t>
+          <t>引き続き検討することとされた事項</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="18" t="inlineStr">
         <is>
@@ -9356,7 +9428,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>国の第10期基本指針が主要テーマとする事項である。法第117条第3項第6号（認知症である被保険者の支援）の前提となる。令和8年9月29日に新設した。</t>
+          <t>令和8年9月18日社会保障審議会介護保険部会の資料により追加した。給付と負担の在り方として引き続き検討することとされた7事項を、本計画への影響が及び得る箇所と対にして掲げる。いずれも算定には織り込んでいない。令和8年10月7日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9373,18 +9445,18 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>認定に要する期間</t>
+          <t>第10期の人口の基礎</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G18" s="18" t="inlineStr">
@@ -9394,7 +9466,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第27条第11項が申請から30日以内の処分を定めており、認定事務の状況は第5章 基本目標5の要介護認定の適正化の前提となる（確認事項No.43）。令和8年10月5日に新設した。</t>
+          <t>推計の基礎を示すもので、見込量の前提として要る。</t>
         </is>
       </c>
     </row>
@@ -9406,33 +9478,33 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>上川管内における位置</t>
+          <t>第9期計画及び社人研推計との関係</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>5</v>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも管内比較がある。</t>
+          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
         </is>
       </c>
     </row>
@@ -9444,23 +9516,23 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の利用強度</t>
+          <t>認知症高齢者の状況</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G20" s="18" t="inlineStr">
@@ -9470,7 +9542,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
+          <t>国の第10期基本指針が主要テーマとする事項である。法第117条第3項第6号（認知症である被保険者の支援）の前提となる。令和8年9月29日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9482,23 +9554,23 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>町別の要介護認定者数</t>
+          <t>認定に要する期間</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>2</v>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G21" s="18" t="inlineStr">
@@ -9508,7 +9580,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>実績は町別に掲げる方針による。</t>
+          <t>介護保険法第27条第11項が申請から30日以内の処分を定めており、認定事務の状況は第5章 基本目標5の要介護認定の適正化の前提となる（確認事項No.43）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9525,14 +9597,14 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>町別の給付費の実績</t>
+          <t>上川管内における位置</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
@@ -9546,7 +9618,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>実績は町別に掲げる方針による。</t>
+          <t>第9期計画にも管内比較がある。</t>
         </is>
       </c>
     </row>
@@ -9558,23 +9630,23 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>事業所数と定員・給付の突合</t>
+          <t>訪問介護の利用強度</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>3</v>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G23" s="18" t="inlineStr">
@@ -9584,7 +9656,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
+          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -9596,23 +9668,23 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>職種別の状況（介護老人福祉施設）</t>
+          <t>町別の要介護認定者数</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
@@ -9622,7 +9694,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（従事者数）に対応する。</t>
+          <t>実績は町別に掲げる方針による。</t>
         </is>
       </c>
     </row>
@@ -9634,33 +9706,33 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>リハビリテーション専門職の配置</t>
+          <t>町別の給付費の実績</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
+          <t>実績は町別に掲げる方針による。</t>
         </is>
       </c>
     </row>
@@ -9677,14 +9749,14 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>指定を受けない住まいと在宅サービスの関係</t>
+          <t>事業所数と定員・給付の突合</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
@@ -9698,7 +9770,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律により、有料老人ホーム及びサービス付き高齢者向け住宅の入居定員を勘案することが明確化された（法第117条）。指定を受けない住まいの入居者は在宅の受給者として居宅サービスを利用するため、入居定員を勘案することの意味を示すものである。</t>
+          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -9715,18 +9787,18 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>運営法人の状況</t>
+          <t>職種別の状況（介護老人福祉施設）</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G27" s="18" t="inlineStr">
@@ -9736,7 +9808,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
+          <t>基本指針別表 七（従事者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -9748,33 +9820,33 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>調査の対象者の範囲</t>
+          <t>リハビリテーション専門職の配置</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
+          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
         </is>
       </c>
     </row>
@@ -9786,23 +9858,23 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>1　主要指標の状況</t>
+          <t>指定を受けない住まいと在宅サービスの関係</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G29" s="18" t="inlineStr">
@@ -9812,7 +9884,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも調査結果の掲載がある。</t>
+          <t>社会福祉法等の一部を改正する法律により、有料老人ホーム及びサービス付き高齢者向け住宅の入居定員を勘案することが明確化された（法第117条）。指定を受けない住まいの入居者は在宅の受給者として居宅サービスを利用するため、入居定員を勘案することの意味を示すものである。</t>
         </is>
       </c>
     </row>
@@ -9824,33 +9896,33 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>2　年齢構成の影響と町間の差</t>
+          <t>区域ごとの入居定員総数（法第117条第5項による勘案）</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E30" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G30" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
+          <t>社会福祉法等の一部を改正する法律案要綱 第2の14（3）により、法第117条第5項の勘案事項として、区域ごとの有料老人ホーム及び登録有料老人ホーム並びに登録住宅の入居定員総数が定められた。勘案したことを示す必要があるため計画に置く。令和8年10月14日に要綱により新設した。</t>
         </is>
       </c>
     </row>
@@ -9862,20 +9934,20 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>3　同規模の保険者との比較</t>
+          <t>運営法人の状況</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E31" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
           <t>独自</t>
@@ -9888,7 +9960,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>基本指針が地域間比較を求めている。</t>
+          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
         </is>
       </c>
     </row>
@@ -9905,14 +9977,14 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>4　社会参加との関連</t>
+          <t>調査の対象者の範囲</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
@@ -9926,7 +9998,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
+          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
         </is>
       </c>
     </row>
@@ -9943,7 +10015,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>5　暮らし向きとの関連</t>
+          <t>1　主要指標の状況</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
@@ -9952,19 +10024,19 @@
       <c r="E33" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G33" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F33" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
+          <t>第9期計画にも調査結果の掲載がある。</t>
         </is>
       </c>
     </row>
@@ -9981,28 +10053,28 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>6　生活実態の主な値</t>
+          <t>2　年齢構成の影響と町間の差</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の第2章にも生活実態の記載がある。</t>
+          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -10019,11 +10091,11 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>7　地区別の状況</t>
+          <t>3　同規模の保険者との比較</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>1</v>
@@ -10033,14 +10105,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G35" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
+          <t>基本指針が地域間比較を求めている。</t>
         </is>
       </c>
     </row>
@@ -10057,7 +10129,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>8　前回調査との比較</t>
+          <t>4　社会参加との関連</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
@@ -10066,9 +10138,9 @@
       <c r="E36" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G36" s="18" t="inlineStr">
@@ -10078,7 +10150,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>経年比較は計画に置く。</t>
+          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -10090,16 +10162,16 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>重度者の在宅・居住系割合の上昇</t>
+          <t>5　暮らし向きとの関連</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>1</v>
@@ -10109,14 +10181,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
+          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
         </is>
       </c>
     </row>
@@ -10128,23 +10200,23 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>在宅生活の継続に必要な生活支援</t>
+          <t>6　生活実態の主な値</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F38" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G38" s="18" t="inlineStr">
@@ -10154,7 +10226,7 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2・3の根拠となる。</t>
+          <t>第9期計画の第2章にも生活実態の記載がある。</t>
         </is>
       </c>
     </row>
@@ -10166,16 +10238,16 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>第10期分の介護人材実態調査の結果</t>
+          <t>7　地区別の状況</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E39" s="6" t="n">
         <v>1</v>
@@ -10185,42 +10257,42 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
+          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の事業費（決算）</t>
+          <t>8　前回調査との比較</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F40" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G40" s="18" t="inlineStr">
@@ -10230,35 +10302,35 @@
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
+          <t>経年比較は計画に置く。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の通いの場の展開状況</t>
+          <t>重度者の在宅・居住系割合の上昇</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G41" s="18" t="inlineStr">
@@ -10268,35 +10340,35 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも通いの場の記載がある。</t>
+          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>一般介護予防事業の実施状況（令和6年度）</t>
+          <t>在宅生活の継続に必要な生活支援</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G42" s="18" t="inlineStr">
@@ -10306,70 +10378,70 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも実施状況の記載がある。</t>
+          <t>第5章 基本目標2・3の根拠となる。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
+          <t>第10期分の介護人材実態調査の結果</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
+          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>第9期の目標指標との接続</t>
+          <t>令和6年度の事業費（決算）</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="F44" s="18" t="inlineStr">
         <is>
           <t>法定</t>
@@ -10382,145 +10454,145 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
+          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>H07・H08・H12・H16の振替について</t>
+          <t>令和6年度の通いの場の展開状況</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G45" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F45" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
+          <t>第9期計画にも通いの場の記載がある。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>H13・H14の定義変更について</t>
+          <t>一般介護予防事業の実施状況（令和6年度）</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G46" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F46" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>第9期計画にも実施状況の記載がある。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>H15の分母について</t>
+          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E47" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G47" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
+          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>基本目標5</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>介護給付費の適正化（第7期給付適正化計画）</t>
+          <t>第9期の目標指標との接続</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F48" s="18" t="inlineStr">
         <is>
@@ -10534,69 +10606,69 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
+          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>要介護度別の認定者数</t>
+          <t>H07・H08・H12・H16の振替について</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G49" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
+          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
         </is>
       </c>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>認定率の置き方によるちがい</t>
+          <t>H13・H14の定義変更について</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
@@ -10610,69 +10682,69 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
+          <t>同上。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎による推計のちがい</t>
+          <t>H15の分母について</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>同上。案Cを採る理由の説明としては要る。</t>
+          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>基本目標5</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定方法</t>
+          <t>介護給付費の適正化（第7期給付適正化計画）</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F52" s="18" t="inlineStr">
         <is>
@@ -10686,7 +10758,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>見込量の前提を示すもので、計画に置く。</t>
+          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
         </is>
       </c>
     </row>
@@ -10698,16 +10770,16 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>利用回（日）数</t>
+          <t>要介護度別の認定者数</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>1</v>
@@ -10724,7 +10796,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号が回数・日数を求めている。</t>
+          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
         </is>
       </c>
     </row>
@@ -10736,12 +10808,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業の量の見込み</t>
+          <t>認定率の置き方によるちがい</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
@@ -10750,19 +10822,19 @@
       <c r="E54" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G54" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号。</t>
+          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
         </is>
       </c>
     </row>
@@ -10774,33 +10846,33 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業費</t>
+          <t>人口の基礎による推計のちがい</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G55" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号。</t>
+          <t>同上。案Cを採る理由の説明としては要る。</t>
         </is>
       </c>
     </row>
@@ -10812,19 +10884,19 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実施状況</t>
+          <t>見込量の算定方法</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F56" s="18" t="inlineStr">
         <is>
@@ -10838,7 +10910,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
+          <t>見込量の前提を示すもので、計画に置く。</t>
         </is>
       </c>
     </row>
@@ -10850,16 +10922,16 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>定員と見込量の照合</t>
+          <t>利用回（日）数</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E57" s="6" t="n">
         <v>1</v>
@@ -10876,7 +10948,7 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数の算定の根拠となる。</t>
+          <t>法第117条第2項第1号が回数・日数を求めている。</t>
         </is>
       </c>
     </row>
@@ -10888,23 +10960,23 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
+          <t>介護予防・日常生活支援総合事業の量の見込み</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G58" s="18" t="inlineStr">
@@ -10914,7 +10986,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
+          <t>法第117条第2項第2号。</t>
         </is>
       </c>
     </row>
@@ -10926,33 +10998,33 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>供給の担い手の集中</t>
+          <t>地域支援事業の量の中長期的な推計</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G59" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G59" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
+          <t>法第117条第2項第3号。社会福祉法等の一部を改正する法律案要綱 第2の14（1）イにより、サービスの種類ごとの量と併せて地域支援事業の量の中長期的な推計が基本的記載事項となった。令和8年10月14日に要綱により新設した。</t>
         </is>
       </c>
     </row>
@@ -10964,23 +11036,23 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>現況（令和8年度）</t>
+          <t>地域支援事業費</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G60" s="18" t="inlineStr">
@@ -10990,7 +11062,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも現況の記載がある。</t>
+          <t>法第117条第3項第2号。</t>
         </is>
       </c>
     </row>
@@ -11002,20 +11074,20 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>第10期における必要利用定員総数</t>
+          <t>認知症総合支援事業の実施状況</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E61" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F61" s="18" t="inlineStr">
         <is>
           <t>法定</t>
@@ -11028,7 +11100,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
+          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11045,11 +11117,11 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
+          <t>定員と見込量の照合</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>1</v>
@@ -11066,7 +11138,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
+          <t>必要利用定員総数の算定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -11078,12 +11150,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>入所の経路からみた整備の考え方</t>
+          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
@@ -11104,7 +11176,7 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
+          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
         </is>
       </c>
     </row>
@@ -11116,33 +11188,33 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>第9期の状況</t>
+          <t>供給の担い手の集中</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G64" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F64" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G64" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも前期の状況の記載がある。</t>
+          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
         </is>
       </c>
     </row>
@@ -11154,33 +11226,33 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
+          <t>現況（令和8年度）</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G65" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F65" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+          <t>第9期計画にも現況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -11192,23 +11264,23 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の状況</t>
+          <t>第10期における必要利用定員総数</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G66" s="18" t="inlineStr">
@@ -11218,7 +11290,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>基金の取崩しは保険料の決定に直結する。</t>
+          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
         </is>
       </c>
     </row>
@@ -11230,16 +11302,16 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>保険料収納率と所得段階別被保険者数の実績</t>
+          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>1</v>
@@ -11256,7 +11328,7 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>保険料算定の基礎。</t>
+          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11268,23 +11340,23 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>所得段階と乗率の置き方</t>
+          <t>入所の経路からみた整備の考え方</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>0</v>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G68" s="18" t="inlineStr">
@@ -11294,7 +11366,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
+          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -11311,28 +11383,28 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>保険料と必要保険料月額との関係</t>
+          <t>第9期の状況</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F69" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G69" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F69" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
+          <t>第9期計画にも前期の状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -11349,11 +11421,11 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>暫定算定</t>
+          <t>期別の必要保険料月額と基準額の対比</t>
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E70" s="6" t="n">
         <v>1</v>
@@ -11363,14 +11435,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G70" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G70" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -11387,28 +11459,28 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>給付費の置き方によるちがい</t>
+          <t>介護給付費準備基金の状況</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F71" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G71" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F71" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
+          <t>基金の取崩しは保険料の決定に直結する。</t>
         </is>
       </c>
     </row>
@@ -11425,28 +11497,28 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映した場合</t>
+          <t>保険料収納率と所得段階別被保険者数の実績</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E72" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F72" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G72" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
+          <t>保険料算定の基礎。</t>
         </is>
       </c>
     </row>
@@ -11463,18 +11535,18 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>前提を動かした場合の幅</t>
+          <t>所得段階と乗率の置き方</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F73" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G73" s="18" t="inlineStr">
@@ -11484,7 +11556,7 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11501,28 +11573,28 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>所得段階の置き方による保険料の違い</t>
+          <t>保険料と必要保険料月額との関係</t>
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G74" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>2</v>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G74" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>国は第10期において高所得者の標準乗率の見直し及び課税化に伴う上昇の緩和を含めた標準段階の見直しを検討課題として挙げている（令和8年9月18日社会保障審議会介護保険部会）。段階の置き方により基準額が動くため、3案の比較を掲げる（確認事項No.33）。令和8年10月7日に新設した。</t>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
         </is>
       </c>
     </row>
@@ -11534,23 +11606,23 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>低所得者に係る負担軽減の見直し</t>
+          <t>暫定算定</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E75" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G75" s="18" t="inlineStr">
@@ -11560,24 +11632,28 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。令和8年10月7日に、見出しを「第10期に施行される見直し」から改めた。一定以上所得基準は結論を得る段階であり施行が決まっていないため、見出しで施行を断定しない。</t>
+          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="44" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>資料5</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの使用データ</t>
+          <t>給付費の置き方によるちがい</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" s="6" t="n">
         <v>1</v>
@@ -11587,34 +11663,38 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G76" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>出典の明示に当たる。</t>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="44" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>資料7</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>採番と表記の規則</t>
+          <t>サービス別の趨勢を反映した場合</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="24" t="inlineStr">
         <is>
@@ -11628,46 +11708,228 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
+          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="44" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>前提を動かした場合の幅</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="44" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>所得段階の置き方による保険料の違い</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>国は第10期において高所得者の標準乗率の見直し及び課税化に伴う上昇の緩和を含めた標準段階の見直しを検討課題として挙げている（令和8年9月18日社会保障審議会介護保険部会）。段階の置き方により基準額が動くため、3案の比較を掲げる（確認事項No.33）。令和8年10月7日に新設した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="44" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>第7節</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>低所得者に係る負担軽減の見直し</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>令和8年3月課長会議資料により追加した。令和8年10月7日に、見出しを「第10期に施行される見直し」から改めた。一定以上所得基準は結論を得る段階であり施行が決まっていないため、見出しで施行を断定しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="44" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>資料5</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr"/>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>地域包括ケア「見える化」システムの使用データ</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>出典の明示に当たる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="44" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
           <t>資料7</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr"/>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr"/>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>採番と表記の規則</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="44" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>資料7</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr"/>
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>未確定箇所の表示</t>
         </is>
       </c>
-      <c r="D78" s="6" t="n">
+      <c r="D83" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E83" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="24" t="inlineStr">
+      <c r="F83" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G78" s="18" t="inlineStr">
+      <c r="G83" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>［要協議］等の記号の意味を示すものであり、本文を読むために必要な凡例に当たる。記号が0になった時点で落とす。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="48" customHeight="1">
-      <c r="A80" s="12" t="inlineStr">
+    <row r="85" ht="48" customHeight="1">
+      <c r="A85" s="12" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -11676,7 +11938,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A85:H85"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -12025,7 +12287,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1038段落153表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1060段落156表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1060段落156表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1059段落156表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表849段落（空段落・目次の行を除く）／実物1060段落（すべて）</t>
+          <t>本表848段落（空段落・目次の行を除く）／実物1059段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -4301,7 +4301,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
     </row>
@@ -4326,7 +4326,7 @@
         <v>7</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>1</v>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B55" s="16" t="inlineStr"/>
       <c r="C55" s="15" t="n">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D55" s="15" t="n">
         <v>156</v>
@@ -7583,7 +7583,7 @@
     <row r="26" ht="56" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>介護給付費分科会は介護報酬（単位数・算定の要件・運営の基準）を扱う別の審議の場である。課長会議資料及び介護保険部会の対比ではこの場の論点を軸に持っていなかった。本表は当区域に直結するものに絞って掲げる（全31件の対比は別冊「介護給付費分科会の論点整理の受領点検」による）。令和8年10月14日に資料25件（第268回・第269回・第270回）のご提供を受け、うち11件の論点を原典により確かめた（別冊「介護給付費分科会資料（原典）の受領点検」）。**計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない**（確認事項No.182）。</t>
+          <t>介護給付費分科会は介護報酬（単位数・算定の要件・運営の基準）を扱う別の審議の場である。課長会議資料及び介護保険部会の対比ではこの場の論点を軸に持っていなかった。本表は当区域に直結するものに絞って掲げる（全31件の対比は別冊「介護給付費分科会の論点整理の受領点検」による）。令和8年10月14日に資料25件（第268回・第269回・第270回）のご提供を受け、うち11件の論点を原典により確かめた（別冊「介護給付費分科会資料（原典）の受領点検」）。計画素案には検討されている事項があることまでを記載し、単位数・要件・施行時期を書いていない（確認事項No.182）。</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>短期入所生活介護の見込量を立てている。**積雪期の季節利用に係る例外は当区域に直接関わる**</t>
+          <t>短期入所生活介護の見込量を立てている。積雪期の季節利用に係る例外は当区域に直接関わる</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>介護保険の指定を受けない住まい339人・戸を把握している。**同一建物減算に代わる報酬区分の見直しは単価に及ぶ**</t>
+          <t>介護保険の指定を受けない住まい339人・戸を把握している。同一建物減算に代わる報酬区分の見直しは単価に及ぶ</t>
         </is>
       </c>
     </row>
@@ -12287,7 +12287,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1060段落156表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1059段落156表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>16</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1059段落156表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1062段落156表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2380,7 +2380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表848段落（空段落・目次の行を除く）／実物1059段落（すべて）</t>
+          <t>本表851段落（空段落・目次の行を除く）／実物1062段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>台帳186件</t>
+          <t>台帳189件</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>13／17件</t>
+          <t>14／17件</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>「医療計画との整合性」が計画素案にあること</t>
+          <t>「地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項」が計画素案にあること</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -3783,21 +3783,21 @@
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="10" t="n">
-        <v>43</v>
+        <v>41.8</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>介護給付費分科会の論点を31件読めていること</t>
+          <t>「第118条第10項」が計画素案にあること</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>len(KB.RONTEN)</t>
+          <t>現れる章節</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>31件</t>
+          <t>第1章第8節</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr">
@@ -3808,21 +3808,21 @@
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="10" t="n">
-        <v>44</v>
+        <v>41.9</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>論点の全件に当方の反映先の判定があること</t>
+          <t>「第115条の45第4項」が計画素案にあること</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>BUNKA_TOUHOU</t>
+          <t>現れる章節</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>31／31件</t>
+          <t>第6章第3節</t>
         </is>
       </c>
       <c r="E60" s="18" t="inlineStr">
@@ -3833,21 +3833,21 @@
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>当区域に直結する論点が計画素案で扱われていること</t>
+          <t>「第94条第6項」が計画素案にあること</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>語による判定</t>
+          <t>現れる章節</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>未対応 0件</t>
+          <t>第6章第5節</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr">
@@ -3858,21 +3858,21 @@
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節に介護給付費分科会の項があること</t>
+          <t>介護給付費分科会の論点を31件読めていること</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>in_draft</t>
+          <t>len(KB.RONTEN)</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>記載あり</t>
+          <t>31件</t>
         </is>
       </c>
       <c r="E62" s="18" t="inlineStr">
@@ -3883,21 +3883,21 @@
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="10" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>計画素案に単位数の値を書いていないこと</t>
+          <t>論点の全件に当方の反映先の判定があること</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>数値を伴う「○○単位」の走査</t>
+          <t>BUNKA_TOUHOU</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>現れない</t>
+          <t>31／31件</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr">
@@ -3908,21 +3908,21 @@
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="10" t="n">
-        <v>47.1</v>
+        <v>45</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>原典により確かめた論点のIDがいずれも論点の一覧にあること</t>
+          <t>当区域に直結する論点が計画素案で扱われていること</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>IDの照合</t>
+          <t>語による判定</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>11件</t>
+          <t>未対応 0件</t>
         </is>
       </c>
       <c r="E64" s="18" t="inlineStr">
@@ -3933,21 +3933,21 @@
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="10" t="n">
-        <v>47.2</v>
+        <v>46</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>原典と食い違っていたものが計画素案に反映されていること</t>
+          <t>計画素案 第1章第9節に介護給付費分科会の項があること</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>素案の走査</t>
+          <t>in_draft</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>要是正 1件／2通りの記載の説明 あり</t>
+          <t>記載あり</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr">
@@ -3958,21 +3958,21 @@
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="10" t="n">
-        <v>47.3</v>
+        <v>47</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>原典により新たに分かった事項の反映先が素案に現にある章節であること</t>
+          <t>計画素案に単位数の値を書いていないこと</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>素案の章節との照合</t>
+          <t>数値を伴う「○○単位」の走査</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>存在しない章節 0件</t>
+          <t>現れない</t>
         </is>
       </c>
       <c r="E66" s="18" t="inlineStr">
@@ -3983,24 +3983,99 @@
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="10" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>原典により確かめた論点のIDがいずれも論点の一覧にあること</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>IDの照合</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>11件</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="10" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>原典と食い違っていたものが計画素案に反映されていること</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>素案の走査</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>要是正 1件／2通りの記載の説明 あり</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="10" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>原典により新たに分かった事項の反映先が素案に現にある章節であること</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>素案の章節との照合</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>存在しない章節 0件</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="10" t="n">
         <v>47.4</v>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>社会福祉法等改正法の改正事項に法第120条の3の協議会が入っており、市町村が構成員であることを書いていること</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>素案の走査</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>第120条の3=あり／構成員として参画=あり</t>
         </is>
       </c>
-      <c r="E67" s="18" t="inlineStr">
+      <c r="E70" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -4242,7 +4317,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2</v>
@@ -4301,7 +4376,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
     </row>
@@ -4417,7 +4492,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>13</v>
@@ -5042,7 +5117,7 @@
         <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
     </row>
@@ -5087,7 +5162,7 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>1</v>
@@ -5330,7 +5405,7 @@
       </c>
       <c r="B55" s="16" t="inlineStr"/>
       <c r="C55" s="15" t="n">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="D55" s="15" t="n">
         <v>156</v>
@@ -5339,7 +5414,7 @@
         <v>79</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G55" s="16" t="inlineStr"/>
     </row>
@@ -5366,7 +5441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5884,29 +5959,29 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>高齢者居住安定確保計画その他の住民の居住に係る施策との連携に関する事項。</t>
+          <t>認知症である被保険者の地域における自立した日常生活の支援に関する事項、関連施策との有機的な連携その他の認知症に関する施策の総合的な推進。</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>第2章第3節（高齢者向け住まい）、第5章 基本目標3</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>一部対応</t>
+          <t>第5章 基本目標2、第1章第2節（市町村認知症施策推進計画）</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>対応済</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>介護保険の指定を受けない住まい339人・戸を把握しているが、北海道の高齢者居住安定確保計画との連携の記述がない。</t>
+          <t>令和8年10月15日に参照条文により号が確定した。従前は本号を「高齢者居住安定確保計画その他の居住に係る施策との連携」としていたが誤りであった。居住に係る施策との連携は第3項第10号であり、市町村高齢者居住安定確保計画との関係は第11項の調和の義務である。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>第3項第4号・第5号（改正後）</t>
+          <t>第3項第10号</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -5916,12 +5991,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>①介護給付等対象サービスの提供における業務の効率化、質の向上その他の生産性の向上、介護支援専門員その他の当該業務に従事する者の確保及び資質の向上その他の質の高い介護給付等対象サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組に資する都道府県と連携した取組に関する事項　②介護支援専門員その他の地域支援事業に従事する者の確保及び資質の向上に資する都道府県と連携した取組に関する事項　③地域支援事業の実施における業務の効率化、質の向上その他の生産性の向上に資する都道府県と連携した取組に関する事項。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。号は法律案要綱 第2の14（2）による。</t>
+          <t>地域支援事業と高齢者保健事業及び国民健康保険保健事業の一体的な実施、医療との連携、高齢者の居住に係る施策との連携その他の被保険者の地域における自立した日常生活の支援のため必要な事項。</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>第2章第6節（介護人材の状況）、第5章 基本目標4（介護人材）、第5章 基本目標2（地域支援事業の実施）</t>
+          <t>第2章第3節（高齢者向け住まい）、第5章 基本目標3</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
@@ -5931,61 +6006,61 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>介護人材の確保・定着、生産性向上、外国人職員の受入れを掲げている。令和8年10月14日に、要綱により3項目であること及びいずれも「都道府県と連携した取組」であることを確かめた。北海道が置く協議会（法第120条の3）への参画を第5章 基本目標4に加えたが、②地域支援事業に従事する者の確保及び③地域支援事業の実施における生産性の向上について、北海道と連携した取組を掲げていない［要協議］。</t>
+          <t>令和8年10月15日に参照条文により号が確定した。介護保険の指定を受けない住まい339人・戸を把握している。高齢者保健事業及び国民健康保険保健事業との一体的な実施の記述がない［要確認］。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>第3項第9号</t>
+          <t>第11項</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>任意記載事項</t>
+          <t>他計画との関係</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>その他介護給付等対象サービス及び地域支援事業の円滑な提供を図るために市町村が必要と認める事項。</t>
+          <t>市町村地域福祉計画（社会福祉法第107条第1項）、市町村高齢者居住安定確保計画（高齢者の居住の安定確保に関する法律第4条の2第1項）その他の要介護者等の保健、医療、福祉又は居住に関する事項を定める計画と調和が保たれたものでなければならない。</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>第1章第6節（進行管理）、第5章 基本目標5（保険運営）</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>対応済</t>
+          <t>第1章第8節（関係計画等との関係）</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>令和8年10月15日に参照条文により項が確定し、調和の義務であることを第1章第8節に加えた。任意記載事項ではなく義務である。構成3町における策定の状況は［要確認］。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>第117条［項 要確認］</t>
+          <t>第3項第4号・第5号（改正後）</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>作成の基準</t>
+          <t>任意記載事項</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>市町村介護保険事業計画は、日常生活圏域ごとの人口、要介護者等の人数等を勘案して作成されなければならない。</t>
+          <t>①介護給付等対象サービスの提供における業務の効率化、質の向上その他の生産性の向上、介護支援専門員その他の当該業務に従事する者の確保及び資質の向上その他の質の高い介護給付等対象サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組に資する都道府県と連携した取組に関する事項　②介護支援専門員その他の地域支援事業に従事する者の確保及び資質の向上に資する都道府県と連携した取組に関する事項　③地域支援事業の実施における業務の効率化、質の向上その他の生産性の向上に資する都道府県と連携した取組に関する事項。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。号は法律案要綱 第2の14（2）による。</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>第1章第7節（日常生活圏域の設定）、第6章第4節4（必要利用定員総数）</t>
+          <t>第2章第6節（介護人材の状況）、第5章 基本目標4（介護人材）、第5章 基本目標2（地域支援事業の実施）</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
@@ -5995,29 +6070,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>第9期の6圏域をそのまま掲げている。基盤整備の単位としての圏域（3町3圏域の案）は［要協議］のまま（確認事項No.88）。圏域ごとの人口は第9期計画による令和5年10月1日現在の値である。</t>
+          <t>介護人材の確保・定着、生産性向上、外国人職員の受入れを掲げている。令和8年10月14日に、要綱により3項目であること及びいずれも「都道府県と連携した取組」であることを確かめた。北海道が置く協議会（法第120条の3）への参画を第5章 基本目標4に加えたが、②地域支援事業に従事する者の確保及び③地域支援事業の実施における生産性の向上について、北海道と連携した取組を掲げていない［要協議］。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>第117条［項 要確認］</t>
+          <t>第3項第9号</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>他計画との関係</t>
+          <t>任意記載事項</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>市町村介護保険事業計画は、医療計画との整合性の確保が図られたものでなければならない。</t>
+          <t>その他介護給付等対象サービス及び地域支援事業の円滑な提供を図るために市町村が必要と認める事項。</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>第1章第8節（関係計画等との関係）</t>
+          <t>第1章第6節（進行管理）、第5章 基本目標5（保険運営）</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
@@ -6027,7 +6102,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月14日に、法が整合性の確保を定めていること及び整合を図る箇所（在宅医療・介護連携、協力医療機関、施設の整備）を加えた。北海道の第10期支援計画は未策定（確認事項No.111）。</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -6039,17 +6114,17 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>他計画との関係</t>
+          <t>作成の基準</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>市町村介護保険事業計画は、市町村老人福祉計画と一体のものとして作成されなければならない（老人福祉法第20条の8と対をなす規定）。</t>
+          <t>市町村介護保険事業計画は、当該市町村の区域における人口構造の変化の見通し、要介護者等の人数及び要介護者等の介護給付等対象サービスの利用に関する意向その他の事情を勘案して作成されなければならない（第4項）。</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>第1章第2節（計画の位置付け）、第1章第8節</t>
+          <t>第1章第7節（日常生活圏域の設定）、第6章第4節4（必要利用定員総数）</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
@@ -6059,39 +6134,39 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月14日に、構成3町の高齢者福祉計画が市町村老人福祉計画に当たること及び一体作成の定めを加えた。広域連合は老人福祉法上の市町村ではないため同計画は3町が策定する（市町村認知症施策推進計画と同じ構造）。一体のものとして作成する方法は［要協議］（確認事項No.178）。</t>
+          <t>第9期の6圏域をそのまま掲げている。基盤整備の単位としての圏域（3町3圏域の案）は［要協議］のまま（確認事項No.88）。圏域ごとの人口は第9期計画による令和5年10月1日現在の値である。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>第117条［項 要確認］</t>
+          <t>第10項</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>策定の手続</t>
+          <t>他計画との関係</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>計画を定め、又は変更しようとするときは、あらかじめ被保険者の意見を反映させるために必要な措置を講ずる。</t>
+          <t>市町村介護保険事業計画は、地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項に規定する市町村計画との整合性の確保が図られたものでなければならない。</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>第1章第5節【法令が定める手続】</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>対応済</t>
+          <t>第1章第8節（関係計画等との関係）</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>意見公募手続を令和9年1月にウェブサイトにより2週間行い、概要版を併せて示すこととしている。方法及び時期は［要協議］。</t>
+          <t>令和8年10月15日に参照条文により項が確定した。従前は「医療計画との整合性の確保」としていたが誤りであった。医療計画及び地域医療構想との整合性の確保は第118条第10項により都道府県介護保険事業支援計画について定められているものである。同法第5条第1項の市町村計画（いわゆる市町村計画）の策定の状況は［要確認］。北海道の第10期支援計画は未策定（確認事項No.111）。</t>
         </is>
       </c>
     </row>
@@ -6103,27 +6178,27 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>策定の手続</t>
+          <t>他計画との関係</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>計画を定め、又は変更しようとするときは、あらかじめ都道府県の意見を聴く。</t>
+          <t>市町村介護保険事業計画は、市町村老人福祉計画と一体のものとして作成されなければならない（老人福祉法第20条の8と対をなす規定）。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>第1章第5節【法令が定める手続】</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>対応済</t>
+          <t>第1章第2節（計画の位置付け）、第1章第8節</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>令和8年10月14日に、構成3町の高齢者福祉計画が市町村老人福祉計画に当たること及び一体作成の定めを加えた。広域連合は老人福祉法上の市町村ではないため同計画は3町が策定する（市町村認知症施策推進計画と同じ構造）。一体のものとして作成する方法は［要協議］（確認事項No.178）。</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6215,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>計画を定め、又は変更したときは、遅滞なくこれを都道府県知事に提出する。</t>
+          <t>計画を定め、又は変更しようとするときは、あらかじめ被保険者の意見を反映させるために必要な措置を講ずる。</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -6155,76 +6230,140 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月14日に加えた。従前は素案に記載がなかった。</t>
+          <t>意見公募手続を令和9年1月にウェブサイトにより2週間行い、概要版を併せて示すこととしている。方法及び時期は［要協議］。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="52" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>第5項（改正後）</t>
+          <t>第117条［項 要確認］</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>作成の基準</t>
+          <t>策定の手続</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>第2項第1号及び第2号並びに第3号の中長期的な推計を定めるに当たっては、①当該市町村が定める区域ごとの有料老人ホーム（老人福祉法第29条第1項の届出が行われているもの）及び登録有料老人ホーム並びに高齢者の居住の安定確保に関する法律に規定する登録住宅のそれぞれの入居定員総数　②当該市町村が属する都道府県が定める区域ごとの医療に関する専門的知識を有する者と介護サービス事業者、居宅における医療を提供する医療機関その他の関係者との連携の状況　を勘案しなければならない。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。項は法律案要綱 第2の14（3）による。</t>
+          <t>計画を定め、又は変更しようとするときは、あらかじめ都道府県の意見を聴く。</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>第2章第3節【区域ごとの入居定員総数（法第117条第5項による勘案）】、第2章第3節（高齢者向け住まいの状況）、第1章第8節（医療と介護の連携）、第6章第5節</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>一部対応</t>
+          <t>第1章第5節【法令が定める手続】</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>対応済</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>令和8年10月14日に要綱により新設を確かめ、①について勘案したことを第2章第3節に明記した。入居定員総数は14施設445人（戸）であり、町別の内訳は第2章第3節第1項の表のとおりである。日常生活圏域が確定していないため区域ごとの整理は［要協議］（確認事項No.88）。②の都道府県が定める区域ごとの連携の状況は、上川中部医療圏の単位で把握できていない［要確認］。登録有料老人ホームに係る部分の施行は公布の日から起算して2年を超えない範囲内において政令で定める日である。</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
         <is>
+          <t>第117条［項 要確認］</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>策定の手続</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>計画を定め、又は変更したときは、遅滞なくこれを都道府県知事に提出する。</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>第1章第5節【法令が定める手続】</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>対応済</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月14日に加えた。従前は素案に記載がなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>第5項（改正後）</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>作成の基準</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>第2項第1号及び第2号並びに第3号の中長期的な推計を定めるに当たっては、①当該市町村が定める区域ごとの有料老人ホーム（老人福祉法第29条第1項の届出が行われているもの）及び登録有料老人ホーム並びに高齢者の居住の安定確保に関する法律に規定する登録住宅のそれぞれの入居定員総数　②当該市町村が属する都道府県が定める区域ごとの医療に関する専門的知識を有する者と介護サービス事業者、居宅における医療を提供する医療機関その他の関係者との連携の状況　を勘案しなければならない。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。項は法律案要綱 第2の14（3）による。</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節【区域ごとの入居定員総数（法第117条第5項による勘案）】、第2章第3節（高齢者向け住まいの状況）、第1章第8節（医療と介護の連携）、第6章第5節</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月14日に要綱により新設を確かめ、①について勘案したことを第2章第3節に明記した。入居定員総数は14施設445人（戸）であり、町別の内訳は第2章第3節第1項の表のとおりである。日常生活圏域が確定していないため区域ごとの整理は［要協議］（確認事項No.88）。②の都道府県が定める区域ごとの連携の状況は、上川中部医療圏の単位で把握できていない［要確認］。登録有料老人ホームに係る部分の施行は公布の日から起算して2年を超えない範囲内において政令で定める日である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
           <t>第14項（改正後）</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>策定の手続</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>第2項第3号の中長期的な推計を定め、又は変更しようとするときは、あらかじめ都道府県の意見を聴かなければならない。社会福祉法等の一部を改正する法律（令和8年法律第51号）による追加。項は法律案要綱 第2の14（4）による。</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>第1章第5節【法令が定める手続】</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>令和8年10月14日に要綱により新設を確かめ、第1章第5節の手続の表に加えた。計画案についての意見の聴取と併せて行うか別に行うかは北海道に確認する［要確認］。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="56" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>注1）介護保険法は第215条までであり、広域連合の根拠は地方自治法第284条である。保険給付・保険料・施策は保険者（広域連合）を単位として定める。
 注2）条文を受領していないため、第1項・第2項・第3項以外の項は「第117条［項 要確認］」と記し項番号を書いていない（確認事項No.181）。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行っている。
@@ -6233,120 +6372,56 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>【介護保険法以外の関係法令との対比】</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>計画の記載事項は介護保険法第117条に限られない。市町村を名宛人とする法令については、本広域連合が地方自治法第284条により設けられ介護保険法上の保険者としての事務を共同処理するものであることから、市町村認知症施策推進計画と同じ整理により構成3町が定めるものと本計画に定めるものを分ける。</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>法令</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>名宛人</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>定めの内容</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>計画素案の反映先</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>原典の受領と残る課題</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="52" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>老人福祉法第20条の8</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>市町村</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>市町村老人福祉計画を定めるものとされ、老人福祉事業の量の目標を定める。同計画は市町村介護保険事業計画と一体のものとして作成する。</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>第1章第2節、第1章第8節</t>
-        </is>
-      </c>
-      <c r="E36" s="17" t="inlineStr">
-        <is>
-          <t>一部対応</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>未受領。令和8年10月14日に法令名及び一体作成の定めを加えた。構成3町の高齢者福祉計画が同計画に当たることの確認、一体作成の方法及び老人福祉事業の量の目標との関係は［要協議］（確認事項No.178）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="52" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>成年後見制度の利用の促進に関する法律第14条</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>市町村</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>国の基本計画を勘案して、成年後見制度の利用の促進に関する施策についての基本的な計画を定めるよう努めるものとされる。</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>第1章第2節、第5章 基本目標1（権利擁護・中核機関）</t>
-        </is>
-      </c>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>一部対応</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>未受領。令和8年10月14日に第1章第2節へ位置づけを加えた。構成3町における策定の状況及び中核機関の整備の状況は［要確認］（確認事項No.179）。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="52" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>高齢者虐待の防止、高齢者の養護者に対する支援等に関する法律</t>
+          <t>老人福祉法第20条の8</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -6356,44 +6431,44 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>通報の受理、高齢者の安全の確認、措置及び養護者の支援を市町村の事務とする。計画の記載を直接義務づけるものではない。</t>
+          <t>市町村老人福祉計画を定めるものとされ、老人福祉事業の量の目標を定める。同計画は市町村介護保険事業計画と一体のものとして作成する。</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>第1章第2節、第5章 基本目標1（3）（4）（5）</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>対応済</t>
+          <t>第1章第2節、第1章第8節</t>
+        </is>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>未受領。施策・主な事業・達成目標（虐待通報への48時間以内の安全確認率100％）を定めている。令和8年10月14日に第1章第2節へ法令名を加えた。</t>
+          <t>未受領。令和8年10月14日に法令名及び一体作成の定めを加えた。構成3町の高齢者福祉計画が同計画に当たることの確認、一体作成の方法及び老人福祉事業の量の目標との関係は［要協議］（確認事項No.178）。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="52" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>共生社会の実現を推進するための認知症基本法第3条</t>
+          <t>成年後見制度の利用の促進に関する法律第14条</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
         <is>
-          <t>―（基本理念）</t>
+          <t>市町村</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>認知症施策の基本理念を定める。</t>
+          <t>国の基本計画を勘案して、成年後見制度の利用の促進に関する施策についての基本的な計画を定めるよう努めるものとされる。</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>第1章第2節、第4章（基本理念）、第5章 基本目標2（3）</t>
+          <t>第1章第2節、第5章 基本目標1（権利擁護・中核機関）</t>
         </is>
       </c>
       <c r="E39" s="17" t="inlineStr">
@@ -6403,14 +6478,14 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>未受領。令和8年10月14日に基本理念に沿って施策を定める旨を加えた。各号の内容は［要確認］（確認事項No.149・No.181）。</t>
+          <t>未受領。令和8年10月14日に第1章第2節へ位置づけを加えた。構成3町における策定の状況及び中核機関の整備の状況は［要確認］（確認事項No.179）。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="52" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>同法第13条</t>
+          <t>高齢者虐待の防止、高齢者の養護者に対する支援等に関する法律</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -6420,12 +6495,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画を定めるよう努めるものとされる。</t>
+          <t>通報の受理、高齢者の安全の確認、措置及び養護者の支援を市町村の事務とする。計画の記載を直接義務づけるものではない。</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>第1章第2節、第1章第8節、第5章 基本目標2（3）、資料2</t>
+          <t>第1章第2節、第5章 基本目標1（3）（4）（5）</t>
         </is>
       </c>
       <c r="E40" s="18" t="inlineStr">
@@ -6435,29 +6510,29 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>未受領。構成3町がそれぞれ策定し、本計画は介護保険法第117条第3項による事項として認知症施策を掲げる（案B。令和8年9月16日 ご了承）。</t>
+          <t>未受領。施策・主な事業・達成目標（虐待通報への48時間以内の安全確認率100％）を定めている。令和8年10月14日に第1章第2節へ法令名を加えた。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="52" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>水防法／土砂災害警戒区域等における土砂災害防止対策の推進に関する法律</t>
+          <t>共生社会の実現を推進するための認知症基本法第3条</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の所有者又は管理者</t>
+          <t>―（基本理念）</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>市町村地域防災計画に定められた要配慮者利用施設について、避難確保計画の作成及び避難訓練の実施を求める。</t>
+          <t>認知症施策の基本理念を定める。</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>第1章第8節、第5章 基本目標5（3）（4）</t>
+          <t>第1章第2節、第4章（基本理念）、第5章 基本目標2（3）</t>
         </is>
       </c>
       <c r="E41" s="17" t="inlineStr">
@@ -6467,61 +6542,61 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>未受領。令和8年10月14日に施策及び主な事業へ加えた。対象施設及び作成の状況は構成3町の地域防災計画によるため［要確認］（確認事項No.180）。達成目標には数値を掲げていない。</t>
+          <t>未受領。令和8年10月14日に基本理念に沿って施策を定める旨を加えた。各号の内容は［要確認］（確認事項No.149・No.181）。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="52" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第78条の4</t>
+          <t>同法第13条</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>広域連合（条例）</t>
+          <t>市町村</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>地域密着型サービスの人員・設備・運営の基準を市町村（広域連合）の条例で定める。省令はその条例を定めるに当たっての基準である。</t>
+          <t>市町村認知症施策推進計画を定めるよう努めるものとされる。</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>第1章第9節1、第6章第4節</t>
-        </is>
-      </c>
-      <c r="E42" s="17" t="inlineStr">
-        <is>
-          <t>一部対応</t>
+          <t>第1章第2節、第1章第8節、第5章 基本目標2（3）、資料2</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>対応済</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>未受領。当該条例を受領していないため、令和6年改正後の省令に対応しているかを確認できない（確認事項No.95）。</t>
+          <t>未受領。構成3町がそれぞれ策定し、本計画は介護保険法第117条第3項による事項として認知症施策を掲げる（案B。令和8年9月16日 ご了承）。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="52" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）</t>
+          <t>水防法／土砂災害警戒区域等における土砂災害防止対策の推進に関する法律</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>―（改正法）</t>
+          <t>要配慮者利用施設の所有者又は管理者</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第117条の記載事項の追加（中長期的なサービスの見通し及びこれを踏まえた提供体制の確保等のための施策）、令和9年4月新設の3区分、特定地域の特例等。</t>
+          <t>市町村地域防災計画に定められた要配慮者利用施設について、避難確保計画の作成及び避難訓練の実施を求める。</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>第1章第9節2、第6章第1節〜第3節、第6章第5節</t>
+          <t>第1章第8節、第5章 基本目標5（3）（4）</t>
         </is>
       </c>
       <c r="E43" s="17" t="inlineStr">
@@ -6531,44 +6606,108 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>未受領。7件を整理済み（第1章第9節2）。改正後の条文の構成を確認できていないため、記載事項の点検は条文の番号ではなく内容を単位として行っている（確認事項No.89・No.181）。</t>
+          <t>未受領。令和8年10月14日に施策及び主な事業へ加えた。対象施設及び作成の状況は構成3町の地域防災計画によるため［要確認］（確認事項No.180）。達成目標には数値を掲げていない。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="52" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
+          <t>介護保険法第78条の4</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>広域連合（条例）</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービスの人員・設備・運営の基準を市町村（広域連合）の条例で定める。省令はその条例を定めるに当たっての基準である。</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節1、第6章第4節</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>未受領。当該条例を受領していないため、令和6年改正後の省令に対応しているかを確認できない（確認事項No.95）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="52" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>―（改正法）</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>介護保険法第117条の記載事項の追加（中長期的なサービスの見通し及びこれを踏まえた提供体制の確保等のための施策）、令和9年4月新設の3区分、特定地域の特例等。</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節2、第6章第1節〜第3節、第6章第5節</t>
+        </is>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>一部対応</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>未受領。7件を整理済み（第1章第9節2）。改正後の条文の構成を確認できていないため、記載事項の点検は条文の番号ではなく内容を単位として行っている（確認事項No.89・No.181）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="52" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>地方自治法第284条</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>―（広域連合の根拠）</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>広域連合は特別地方公共団体として設けられ、介護保険法上の保険者としての事務を共同処理する。</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>第1章第2節</t>
         </is>
       </c>
-      <c r="E44" s="18" t="inlineStr">
+      <c r="E46" s="18" t="inlineStr">
         <is>
           <t>対応済</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>未受領。介護保険法は第215条までであり第284条は存在しない。広域連合の根拠は地方自治法である。</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>注）本表の法令はいずれも条文を受領していない。「対応」は計画素案に当該の記述があるかの判定であり、条文との逐語の照合ではない。条文のご提供を確認事項No.181によりお願いしている。</t>
         </is>
@@ -6577,11 +6716,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A48:F48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8737,12 +8876,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>高齢者居住安定確保計画との連携（第3項第8号）</t>
+          <t>市町村高齢者居住安定確保計画との調和（第11項）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>北海道の高齢者居住安定確保計画との連携に関する記述がない。介護保険の指定を受けない住まいの状況は把握できている。</t>
+          <t>令和8年10月15日に参照条文により、高齢者居住安定確保計画との関係は第11項の調和の義務であり第3項第8号の任意記載事項ではないことが分かった。同項の相手は市町村地域福祉計画及び市町村高齢者居住安定確保計画であり、いずれも構成3町が定めるものである。</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -8750,9 +8889,9 @@
           <t>第1章第8節、第5章 基本目標3</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>未追加。北海道の計画の改定時期の確認を要する</t>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>追加済み（令和8年10月15日）。3町における策定の状況は［要確認］</t>
         </is>
       </c>
     </row>
@@ -8993,7 +9132,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>1</v>
@@ -9829,7 +9968,7 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>2</v>
@@ -11307,7 +11446,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>混合型特定施設入居者生活介護に係る必要利用定員総数</t>
+          <t>特定施設入居者生活介護に係る必要利用定員総数</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
@@ -11328,7 +11467,7 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項が勘案事項として挙げるもの。第9期計画及び従前の素案に記載がなかった（確認事項No.113）。定めないこととする旨を記載している。令和8年10月1日に新設した。</t>
+          <t>法第117条第2項第1号により本計画が定める必要利用定員総数の範囲を示すもの（確認事項No.113）。令和8年10月15日に参照条文により、介護専用型及び混合型の必要利用定員総数はいずれも都道府県介護保険事業支援計画の事項（法第118条第2項第1号・第4項）であり本計画の記載事項でないことが分かったため、見出し及び記述を是正した。</t>
         </is>
       </c>
     </row>
@@ -12287,7 +12426,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1059段落156表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1062段落156表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1062段落156表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1063段落156表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表851段落（空段落・目次の行を除く）／実物1062段落（すべて）</t>
+          <t>本表852段落（空段落・目次の行を除く）／実物1063段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>台帳189件</t>
+          <t>台帳190件</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>6</v>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="B55" s="16" t="inlineStr"/>
       <c r="C55" s="15" t="n">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D55" s="15" t="n">
         <v>156</v>
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>4</v>
@@ -12426,7 +12426,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1062段落156表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1063段落156表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="B28" s="15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D28" s="15" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1063段落156表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1074段落158表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表156表／実物156表</t>
+          <t>本表158表／実物158表</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表852段落（空段落・目次の行を除く）／実物1063段落（すべて）</t>
+          <t>本表860段落（空段落・目次の行を除く）／実物1074段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>79件</t>
+          <t>81件</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>第1章第9節、第6章第4節</t>
+          <t>第1章第9節、第6章第4節、第6章第5節</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>16件（全79件）</t>
+          <t>16件（全81件）</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>145／145表</t>
+          <t>147／147表</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>156／156表</t>
+          <t>158／158表</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
@@ -4367,16 +4367,16 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
     </row>
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>13</v>
@@ -4500,12 +4500,12 @@
       <c r="E18" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>9</v>
+      <c r="F18" s="9" t="n">
+        <v>10</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>【　】の見出しが6件あり、記述の単位が多い。</t>
+          <t>未確定箇所が集中している。【　】の見出しが6件あり、記述の単位が多い。</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>6</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -5162,16 +5162,16 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
     </row>
@@ -5405,16 +5405,16 @@
       </c>
       <c r="B55" s="16" t="inlineStr"/>
       <c r="C55" s="15" t="n">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="G55" s="16" t="inlineStr"/>
     </row>
@@ -9008,7 +9008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9242,18 +9242,18 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>北海道第9期計画の基本目標との対応</t>
+          <t>北海道第10期計画の骨子（案）との対応</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>都道府県計画との調和は法第117条第9項による。</t>
+          <t>都道府県計画との調和による。令和8年8月27日の北海道高齢者保健福祉施策検討協議会に示された第10期計画の骨子（案）の基本目標8件との対応である。令和8年10月20日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>「市町村数」を単位とする指標の読替え</t>
+          <t>北海道第9期計画の基本目標との対応</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
@@ -9289,9 +9289,9 @@
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>北海道計画の指標が市町村数を単位とするため、広域連合として読み替える必要がある。分量は3行にとどまる。</t>
+          <t>都道府県計画との調和は法第117条第9項による。北海道の第10期の評価指標が示されていないため、評価指標による対応は引き続き第9期による。</t>
         </is>
       </c>
     </row>
@@ -9313,23 +9313,23 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>第9節</t>
+          <t>第8節</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2040年を見据えた地域類型の考え方</t>
+          <t>「市町村数」を単位とする指標の読替え</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。</t>
+          <t>北海道計画の指標が市町村数を単位とするため、広域連合として読み替える必要がある。分量は3行にとどまる。</t>
         </is>
       </c>
     </row>
@@ -9356,11 +9356,11 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>医療と介護の協議の場の再編成</t>
+          <t>2040年を見据えた地域類型の考え方</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -9394,14 +9394,14 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）に係る特例の創設</t>
+          <t>医療と介護の協議の場の再編成</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>令和9年4月施行。第10期の初年度から適用される。</t>
+          <t>令和8年3月課長会議資料により追加した。</t>
         </is>
       </c>
     </row>
@@ -9432,14 +9432,14 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>施行の日</t>
+          <t>中山間・人口減少地域（特定地域）に係る特例の創設</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）による。施行は原則として令和9年4月1日であるが4区分の例外があり、いずれも第10期計画の期間中に施行される。令和8年10月14日に要綱により新設した。</t>
+          <t>令和9年4月施行。第10期の初年度から適用される。</t>
         </is>
       </c>
     </row>
@@ -9470,11 +9470,11 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>介護保険法の改正（要綱 第2）</t>
+          <t>施行の日</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>1</v>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>改正事項ごとに内容・施行の日・本計画における取扱いを対にしたもの。従前は介護保険法と他の法律の改正を1つの表にまとめていた。令和8年10月14日に要綱により分けた。</t>
+          <t>社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）による。施行は原則として令和9年4月1日であるが4区分の例外があり、いずれも第10期計画の期間中に施行される。令和8年10月14日に要綱により新設した。</t>
         </is>
       </c>
     </row>
@@ -9508,14 +9508,14 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法その他の法律の改正（要綱 第1・第6から第8まで）</t>
+          <t>介護保険法の改正（要綱 第2）</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" s="18" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法・老人福祉法・社会福祉士及び介護福祉士法の改正のうち本計画に関わるもの。令和8年10月14日に要綱により新設した。</t>
+          <t>改正事項ごとに内容・施行の日・本計画における取扱いを対にしたもの。従前は介護保険法と他の法律の改正を1つの表にまとめていた。令和8年10月14日に要綱により分けた。</t>
         </is>
       </c>
     </row>
@@ -9546,14 +9546,14 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>引き続き検討することとされた事項</t>
+          <t>社会福祉法その他の法律の改正（要綱 第1・第6から第8まで）</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="18" t="inlineStr">
         <is>
@@ -9567,35 +9567,35 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月18日社会保障審議会介護保険部会の資料により追加した。給付と負担の在り方として引き続き検討することとされた7事項を、本計画への影響が及び得る箇所と対にして掲げる。いずれも算定には織り込んでいない。令和8年10月7日に新設した。</t>
+          <t>社会福祉法・老人福祉法・社会福祉士及び介護福祉士法の改正のうち本計画に関わるもの。令和8年10月14日に要綱により新設した。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>第2章</t>
+          <t>第1章</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>第9節</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>第10期の人口の基礎</t>
+          <t>引き続き検討することとされた事項</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>2</v>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G18" s="18" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>推計の基礎を示すもので、見込量の前提として要る。</t>
+          <t>令和8年9月18日社会保障審議会介護保険部会の資料により追加した。給付と負担の在り方として引き続き検討することとされた7事項を、本計画への影響が及び得る箇所と対にして掲げる。いずれも算定には織り込んでいない。令和8年10月7日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9622,28 +9622,28 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>第9期計画及び社人研推計との関係</t>
+          <t>第10期の人口の基礎</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G19" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
+          <t>推計の基礎を示すもので、見込量の前提として要る。</t>
         </is>
       </c>
     </row>
@@ -9660,28 +9660,28 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>認知症高齢者の状況</t>
+          <t>第9期計画及び社人研推計との関係</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E20" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>国の第10期基本指針が主要テーマとする事項である。法第117条第3項第6号（認知症である被保険者の支援）の前提となる。令和8年9月29日に新設した。</t>
+          <t>推計の対比であり、計画の本文に置くか資料編に移すかを協議する。第9期計画には同種の対比がない。</t>
         </is>
       </c>
     </row>
@@ -9698,14 +9698,14 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>認定に要する期間</t>
+          <t>認知症高齢者の状況</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="18" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>介護保険法第27条第11項が申請から30日以内の処分を定めており、認定事務の状況は第5章 基本目標5の要介護認定の適正化の前提となる（確認事項No.43）。令和8年10月5日に新設した。</t>
+          <t>国の第10期基本指針が主要テーマとする事項である。法第117条第3項第6号（認知症である被保険者の支援）の前提となる。令和8年9月29日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9731,23 +9731,23 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>上川管内における位置</t>
+          <t>認定に要する期間</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>2</v>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G22" s="18" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも管内比較がある。</t>
+          <t>介護保険法第27条第11項が申請から30日以内の処分を定めており、認定事務の状況は第5章 基本目標5の要介護認定の適正化の前提となる（確認事項No.43）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -9774,18 +9774,18 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の利用強度</t>
+          <t>上川管内における位置</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E23" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G23" s="18" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
+          <t>第9期計画にも管内比較がある。</t>
         </is>
       </c>
     </row>
@@ -9812,18 +9812,18 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>町別の要介護認定者数</t>
+          <t>訪問介護の利用強度</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>3</v>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>実績は町別に掲げる方針による。</t>
+          <t>基本指針別表 五（1人当たり算定回数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>町別の給付費の実績</t>
+          <t>町別の要介護認定者数</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
@@ -9883,23 +9883,23 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>事業所数と定員・給付の突合</t>
+          <t>町別の給付費の実績</t>
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>1</v>
+      </c>
+      <c r="F26" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
+          <t>実績は町別に掲げる方針による。</t>
         </is>
       </c>
     </row>
@@ -9926,14 +9926,14 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>職種別の状況（介護老人福祉施設）</t>
+          <t>事業所数と定員・給付の突合</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F27" s="18" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>基本指針別表 七（従事者数）に対応する。</t>
+          <t>基本指針別表 七（施設・事業所数、利用者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -9964,28 +9964,28 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>リハビリテーション専門職の配置</t>
+          <t>職種別の状況（介護老人福祉施設）</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G28" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
+          <t>基本指針別表 七（従事者数）に対応する。</t>
         </is>
       </c>
     </row>
@@ -10002,28 +10002,28 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>指定を受けない住まいと在宅サービスの関係</t>
+          <t>リハビリテーション専門職の配置</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>2</v>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律により、有料老人ホーム及びサービス付き高齢者向け住宅の入居定員を勘案することが明確化された（法第117条）。指定を受けない住まいの入居者は在宅の受給者として居宅サービスを利用するため、入居定員を勘案することの意味を示すものである。</t>
+          <t>地域ケア会議への専門職の派遣の前提となる情報だが、第9期計画にはない。第5章 基本目標2との接続を示せば計画に置ける。</t>
         </is>
       </c>
     </row>
@@ -10040,14 +10040,14 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>区域ごとの入居定員総数（法第117条第5項による勘案）</t>
+          <t>指定を受けない住まいと在宅サービスの関係</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律案要綱 第2の14（3）により、法第117条第5項の勘案事項として、区域ごとの有料老人ホーム及び登録有料老人ホーム並びに登録住宅の入居定員総数が定められた。勘案したことを示す必要があるため計画に置く。令和8年10月14日に要綱により新設した。</t>
+          <t>社会福祉法等の一部を改正する法律により、有料老人ホーム及びサービス付き高齢者向け住宅の入居定員を勘案することが明確化された（法第117条）。指定を受けない住まいの入居者は在宅の受給者として居宅サービスを利用するため、入居定員を勘案することの意味を示すものである。</t>
         </is>
       </c>
     </row>
@@ -10078,18 +10078,18 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>運営法人の状況</t>
+          <t>区域ごとの入居定員総数（法第117条第5項による勘案）</t>
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G31" s="18" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
+          <t>社会福祉法等の一部を改正する法律案要綱 第2の14（3）により、法第117条第5項の勘案事項として、区域ごとの有料老人ホーム及び登録有料老人ホーム並びに登録住宅の入居定員総数が定められた。勘案したことを示す必要があるため計画に置く。令和8年10月14日に要綱により新設した。</t>
         </is>
       </c>
     </row>
@@ -10111,20 +10111,20 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>調査の対象者の範囲</t>
+          <t>運営法人の状況</t>
         </is>
       </c>
       <c r="D32" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E32" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
           <t>独自</t>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
+          <t>法第117条第3項第5号（事業所相互間の連携）に接続する。上位6法人が過半を占めるという供給の集中は整備方針の前提となる。</t>
         </is>
       </c>
     </row>
@@ -10154,18 +10154,18 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>1　主要指標の状況</t>
+          <t>調査の対象者の範囲</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G33" s="18" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも調査結果の掲載がある。</t>
+          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
         </is>
       </c>
     </row>
@@ -10192,28 +10192,28 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2　年齢構成の影響と町間の差</t>
+          <t>1　主要指標の状況</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G34" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F34" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
+          <t>第9期計画にも調査結果の掲載がある。</t>
         </is>
       </c>
     </row>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>3　同規模の保険者との比較</t>
+          <t>2　年齢構成の影響と町間の差</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
@@ -10244,14 +10244,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>基本指針が地域間比較を求めている。</t>
+          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -10268,11 +10268,11 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>4　社会参加との関連</t>
+          <t>3　同規模の保険者との比較</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>1</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
+          <t>基本指針が地域間比較を求めている。</t>
         </is>
       </c>
     </row>
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>5　暮らし向きとの関連</t>
+          <t>4　社会参加との関連</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
@@ -10320,14 +10320,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G37" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
+          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>6　生活実態の主な値</t>
+          <t>5　暮らし向きとの関連</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
@@ -10353,19 +10353,19 @@
       <c r="E38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の第2章にも生活実態の記載がある。</t>
+          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>7　地区別の状況</t>
+          <t>6　生活実態の主な値</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
@@ -10391,19 +10391,19 @@
       <c r="E39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F39" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
+          <t>第9期計画の第2章にも生活実態の記載がある。</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>8　前回調査との比較</t>
+          <t>7　地区別の状況</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
@@ -10429,19 +10429,19 @@
       <c r="E40" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>経年比較は計画に置く。</t>
+          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
         </is>
       </c>
     </row>
@@ -10453,23 +10453,23 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>重度者の在宅・居住系割合の上昇</t>
+          <t>8　前回調査との比較</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F41" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G41" s="18" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
+          <t>経年比較は計画に置く。</t>
         </is>
       </c>
     </row>
@@ -10496,11 +10496,11 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>在宅生活の継続に必要な生活支援</t>
+          <t>重度者の在宅・居住系割合の上昇</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>1</v>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2・3の根拠となる。</t>
+          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -10529,16 +10529,16 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>第10期分の介護人材実態調査の結果</t>
+          <t>在宅生活の継続に必要な生活支援</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>1</v>
@@ -10555,35 +10555,35 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
+          <t>第5章 基本目標2・3の根拠となる。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の事業費（決算）</t>
+          <t>第10期分の介護人材実態調査の結果</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G44" s="18" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
+          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
         </is>
       </c>
     </row>
@@ -10610,18 +10610,18 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の通いの場の展開状況</t>
+          <t>令和6年度の事業費（決算）</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G45" s="18" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも通いの場の記載がある。</t>
+          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
         </is>
       </c>
     </row>
@@ -10648,11 +10648,11 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>一般介護予防事業の実施状況（令和6年度）</t>
+          <t>令和6年度の通いの場の展開状況</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>1</v>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも実施状況の記載がある。</t>
+          <t>第9期計画にも通いの場の記載がある。</t>
         </is>
       </c>
     </row>
@@ -10681,71 +10681,71 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
+          <t>一般介護予防事業の実施状況（令和6年度）</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G47" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F47" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
+          <t>第9期計画にも実施状況の記載がある。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>第9期の目標指標との接続</t>
+          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G48" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>4</v>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
+          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
         </is>
       </c>
     </row>
@@ -10762,28 +10762,28 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>H07・H08・H12・H16の振替について</t>
+          <t>第9期の目標指標との接続</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>0</v>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
+          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -10800,14 +10800,14 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>H13・H14の定義変更について</t>
+          <t>H07・H08・H12・H16の振替について</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
         </is>
       </c>
     </row>
@@ -10838,52 +10838,52 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>H15の分母について</t>
+          <t>H13・H14の定義変更について</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G51" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>0</v>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
+          <t>同上。</t>
         </is>
       </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>基本目標5</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>介護給付費の適正化（第7期給付適正化計画）</t>
+          <t>H15の分母について</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="18" t="inlineStr">
         <is>
@@ -10897,31 +10897,31 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
+          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>基本目標5</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>要介護度別の認定者数</t>
+          <t>介護給付費の適正化（第7期給付適正化計画）</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" s="18" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
+          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
         </is>
       </c>
     </row>
@@ -10952,28 +10952,28 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>認定率の置き方によるちがい</t>
+          <t>要介護度別の認定者数</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G54" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
+          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
         </is>
       </c>
     </row>
@@ -10990,11 +10990,11 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎による推計のちがい</t>
+          <t>認定率の置き方によるちがい</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>1</v>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>同上。案Cを採る理由の説明としては要る。</t>
+          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
         </is>
       </c>
     </row>
@@ -11023,33 +11023,33 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定方法</t>
+          <t>人口の基礎による推計のちがい</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F56" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G56" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>1</v>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>見込量の前提を示すもので、計画に置く。</t>
+          <t>同上。案Cを採る理由の説明としては要る。</t>
         </is>
       </c>
     </row>
@@ -11066,15 +11066,15 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>利用回（日）数</t>
+          <t>見込量の算定方法</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E57" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E57" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F57" s="18" t="inlineStr">
         <is>
           <t>法定</t>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号が回数・日数を求めている。</t>
+          <t>見込量の前提を示すもので、計画に置く。</t>
         </is>
       </c>
     </row>
@@ -11099,16 +11099,16 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業の量の見込み</t>
+          <t>利用回（日）数</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E58" s="6" t="n">
         <v>1</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号。</t>
+          <t>法第117条第2項第1号が回数・日数を求めている。</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業の量の中長期的な推計</t>
+          <t>介護予防・日常生活支援総合事業の量の見込み</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第3号。社会福祉法等の一部を改正する法律案要綱 第2の14（1）イにより、サービスの種類ごとの量と併せて地域支援事業の量の中長期的な推計が基本的記載事項となった。令和8年10月14日に要綱により新設した。</t>
+          <t>法第117条第2項第2号。</t>
         </is>
       </c>
     </row>
@@ -11180,11 +11180,11 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業費</t>
+          <t>地域支援事業の量の中長期的な推計</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" s="6" t="n">
         <v>1</v>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号。</t>
+          <t>法第117条第2項第3号。社会福祉法等の一部を改正する法律案要綱 第2の14（1）イにより、サービスの種類ごとの量と併せて地域支援事業の量の中長期的な推計が基本的記載事項となった。令和8年10月14日に要綱により新設した。</t>
         </is>
       </c>
     </row>
@@ -11218,14 +11218,14 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実施状況</t>
+          <t>地域支援事業費</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="18" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
+          <t>法第117条第3項第2号。</t>
         </is>
       </c>
     </row>
@@ -11251,20 +11251,20 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>定員と見込量の照合</t>
+          <t>認知症総合支援事業の実施状況</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E62" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F62" s="18" t="inlineStr">
         <is>
           <t>法定</t>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数の算定の根拠となる。</t>
+          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11294,18 +11294,18 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
+          <t>定員と見込量の照合</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G63" s="18" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
+          <t>必要利用定員総数の算定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -11332,28 +11332,28 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>供給の担い手の集中</t>
+          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G64" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
+          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
         </is>
       </c>
     </row>
@@ -11370,28 +11370,28 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>現況（令和8年度）</t>
+          <t>供給の担い手の集中</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E65" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G65" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F65" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも現況の記載がある。</t>
+          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
         </is>
       </c>
     </row>
@@ -11408,18 +11408,18 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>第10期における必要利用定員総数</t>
+          <t>現況（令和8年度）</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F66" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G66" s="18" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
+          <t>第9期計画にも現況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -11446,11 +11446,11 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>特定施設入居者生活介護に係る必要利用定員総数</t>
+          <t>第10期における必要利用定員総数</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>1</v>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号により本計画が定める必要利用定員総数の範囲を示すもの（確認事項No.113）。令和8年10月15日に参照条文により、介護専用型及び混合型の必要利用定員総数はいずれも都道府県介護保険事業支援計画の事項（法第118条第2項第1号・第4項）であり本計画の記載事項でないことが分かったため、見出し及び記述を是正した。</t>
+          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
         </is>
       </c>
     </row>
@@ -11479,23 +11479,23 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>入所の経路からみた整備の考え方</t>
+          <t>特定施設入居者生活介護に係る必要利用定員総数</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G68" s="18" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
+          <t>法第117条第2項第1号により本計画が定める必要利用定員総数の範囲を示すもの（確認事項No.113）。令和8年10月15日に参照条文により、介護専用型及び混合型の必要利用定員総数はいずれも都道府県介護保険事業支援計画の事項（法第118条第2項第1号・第4項）であり本計画の記載事項でないことが分かったため、見出し及び記述を是正した。</t>
         </is>
       </c>
     </row>
@@ -11517,23 +11517,23 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>第9期の状況</t>
+          <t>入所の経路からみた整備の考え方</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G69" s="18" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも前期の状況の記載がある。</t>
+          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
+          <t>北海道の道作成指針（案）が示す整備の考え方</t>
         </is>
       </c>
       <c r="D70" s="6" t="n">
@@ -11569,19 +11569,19 @@
       <c r="E70" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F70" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G70" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+          <t>北海道の第10期計画の策定に係る道作成指針（案）が市町村介護保険事業計画の基本的記載事項として示す事項と本計画における扱いの対照である。令和8年10月20日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11598,11 +11598,11 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の状況</t>
+          <t>第9期の状況</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71" s="6" t="n">
         <v>1</v>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>基金の取崩しは保険料の決定に直結する。</t>
+          <t>第9期計画にも前期の状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>保険料収納率と所得段階別被保険者数の実績</t>
+          <t>期別の必要保険料月額と基準額の対比</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
@@ -11645,19 +11645,19 @@
       <c r="E72" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F72" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G72" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F72" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>保険料算定の基礎。</t>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -11674,18 +11674,18 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>所得段階と乗率の置き方</t>
+          <t>介護給付費準備基金の状況</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E73" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F73" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F73" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G73" s="18" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
+          <t>基金の取崩しは保険料の決定に直結する。</t>
         </is>
       </c>
     </row>
@@ -11712,28 +11712,28 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>保険料と必要保険料月額との関係</t>
+          <t>保険料収納率と所得段階別被保険者数の実績</t>
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F74" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G74" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
+          <t>保険料算定の基礎。</t>
         </is>
       </c>
     </row>
@@ -11750,18 +11750,18 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>暫定算定</t>
+          <t>所得段階と乗率の置き方</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E75" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G75" s="18" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
+          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11788,14 +11788,14 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>給付費の置き方によるちがい</t>
+          <t>保険料と必要保険料月額との関係</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
         </is>
       </c>
     </row>
@@ -11826,11 +11826,11 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映した場合</t>
+          <t>暫定算定</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E77" s="6" t="n">
         <v>1</v>
@@ -11840,14 +11840,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G77" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G77" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
+          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
         </is>
       </c>
     </row>
@@ -11864,28 +11864,28 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>前提を動かした場合の幅</t>
+          <t>給付費の置き方によるちがい</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F78" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G78" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G78" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
         </is>
       </c>
     </row>
@@ -11902,28 +11902,28 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>所得段階の置き方による保険料の違い</t>
+          <t>サービス別の趨勢を反映した場合</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E79" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F79" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G79" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F79" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>国は第10期において高所得者の標準乗率の見直し及び課税化に伴う上昇の緩和を含めた標準段階の見直しを検討課題として挙げている（令和8年9月18日社会保障審議会介護保険部会）。段階の置き方により基準額が動くため、3案の比較を掲げる（確認事項No.33）。令和8年10月7日に新設した。</t>
+          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11935,23 +11935,23 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>低所得者に係る負担軽減の見直し</t>
+          <t>前提を動かした場合の幅</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>3</v>
+      </c>
+      <c r="F80" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G80" s="18" t="inlineStr">
@@ -11961,31 +11961,35 @@
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。令和8年10月7日に、見出しを「第10期に施行される見直し」から改めた。一定以上所得基準は結論を得る段階であり施行が決まっていないため、見出しで施行を断定しない。</t>
+          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="44" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>資料5</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>第6節</t>
+        </is>
+      </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの使用データ</t>
+          <t>所得段階の置き方による保険料の違い</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E81" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G81" s="18" t="inlineStr">
@@ -11995,54 +11999,58 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>出典の明示に当たる。</t>
+          <t>国は第10期において高所得者の標準乗率の見直し及び課税化に伴う上昇の緩和を含めた標準段階の見直しを検討課題として挙げている（令和8年9月18日社会保障審議会介護保険部会）。段階の置き方により基準額が動くため、3案の比較を掲げる（確認事項No.33）。令和8年10月7日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="44" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>資料7</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>第7節</t>
+        </is>
+      </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>採番と表記の規則</t>
+          <t>低所得者に係る負担軽減の見直し</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G82" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G82" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
+          <t>令和8年3月課長会議資料により追加した。令和8年10月7日に、見出しを「第10期に施行される見直し」から改めた。一定以上所得基準は結論を得る段階であり施行が決まっていないため、見出しで施行を断定しない。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="44" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>資料7</t>
+          <t>資料5</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr"/>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>未確定箇所の表示</t>
+          <t>地域包括ケア「見える化」システムの使用データ</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
@@ -12063,12 +12071,80 @@
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
+          <t>出典の明示に当たる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="44" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>資料7</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr"/>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>採番と表記の規則</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="44" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>資料7</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr"/>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所の表示</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
           <t>［要協議］等の記号の意味を示すものであり、本文を読むために必要な凡例に当たる。記号が0になった時点で落とす。</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="48" customHeight="1">
-      <c r="A85" s="12" t="inlineStr">
+    <row r="87" ht="48" customHeight="1">
+      <c r="A87" s="12" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -12077,7 +12153,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A87:H87"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -12426,7 +12502,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1063段落156表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1074段落158表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>台帳190件</t>
+          <t>台帳192件</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>0</v>
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="B28" s="15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D28" s="15" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1074段落158表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1083段落160表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表158表／実物158表</t>
+          <t>本表160表／実物160表</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表860段落（空段落・目次の行を除く）／実物1074段落（すべて）</t>
+          <t>本表868段落（空段落・目次の行を除く）／実物1083段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>81件</t>
+          <t>82件</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>台帳192件</t>
+          <t>台帳193件</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>16件（全81件）</t>
+          <t>16件（全82件）</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>158／158表</t>
+          <t>160／160表</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
@@ -4492,20 +4492,20 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>未確定箇所が集中している。【　】の見出しが6件あり、記述の単位が多い。</t>
+          <t>未確定箇所が集中している。【　】の見出しが7件あり、記述の単位が多い。</t>
         </is>
       </c>
     </row>
@@ -5116,10 +5116,14 @@
       <c r="E42" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G42" s="5" t="inlineStr"/>
+      <c r="F42" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>未確定箇所が集中している。</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -5405,16 +5409,16 @@
       </c>
       <c r="B55" s="16" t="inlineStr"/>
       <c r="C55" s="15" t="n">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G55" s="16" t="inlineStr"/>
     </row>
@@ -9008,7 +9012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10120,10 +10124,10 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
@@ -10149,19 +10153,19 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>調査の対象者の範囲</t>
+          <t>事業所ごとの定員と従事者の5か年の推移</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
@@ -10175,7 +10179,7 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
+          <t>国が提供する事業所分析データにより、区域内の事業所ごとの定員・利用者数・従事者数の5か年の推移を確かめたものである。介護給付等対象サービスの量を定める際に勘案する「計画期間中に見込まれる介護サービス施設・事業所の開設・廃止等による影響」及び供給の制約の判断材料となる。</t>
         </is>
       </c>
     </row>
@@ -10192,18 +10196,18 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>1　主要指標の状況</t>
+          <t>調査の対象者の範囲</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+        <v>0</v>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
@@ -10213,7 +10217,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも調査結果の掲載がある。</t>
+          <t>他の調査と合算できないことを示す注記に当たる。分量を1段落に抑える。</t>
         </is>
       </c>
     </row>
@@ -10230,28 +10234,28 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2　年齢構成の影響と町間の差</t>
+          <t>1　主要指標の状況</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G35" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F35" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G35" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
+          <t>第9期計画にも調査結果の掲載がある。</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10272,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>3　同規模の保険者との比較</t>
+          <t>2　年齢構成の影響と町間の差</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
@@ -10282,14 +10286,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>基本指針が地域間比較を求めている。</t>
+          <t>年齢調整と町間の差の検定は第9期計画にない。結果のみを本文に置き、検定の方法は資料編又は調査報告書に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -10306,11 +10310,11 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>4　社会参加との関連</t>
+          <t>3　同規模の保険者との比較</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>1</v>
@@ -10327,7 +10331,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
+          <t>基本指針が地域間比較を求めている。</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10348,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>5　暮らし向きとの関連</t>
+          <t>4　社会参加との関連</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
@@ -10358,14 +10362,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G38" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
+          <t>第5章 基本目標2（通いの場）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -10382,7 +10386,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>6　生活実態の主な値</t>
+          <t>5　暮らし向きとの関連</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
@@ -10391,19 +10395,19 @@
       <c r="E39" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の第2章にも生活実態の記載がある。</t>
+          <t>フレイルと暮らし向きの関連は施策に直接つながらない。低所得者支援（第6章第7節）に接続するなら残す。</t>
         </is>
       </c>
     </row>
@@ -10420,7 +10424,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>7　地区別の状況</t>
+          <t>6　生活実態の主な値</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
@@ -10429,19 +10433,19 @@
       <c r="E40" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F40" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G40" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F40" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
+          <t>第9期計画の第2章にも生活実態の記載がある。</t>
         </is>
       </c>
     </row>
@@ -10458,7 +10462,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>8　前回調査との比較</t>
+          <t>7　地区別の状況</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
@@ -10467,19 +10471,19 @@
       <c r="E41" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>経年比較は計画に置く。</t>
+          <t>地区の定義が［要確認］のまま（確認事項No.9）。定義が決まらない場合は町別に集約するか移すかを協議する。</t>
         </is>
       </c>
     </row>
@@ -10491,23 +10495,23 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>重度者の在宅・居住系割合の上昇</t>
+          <t>8　前回調査との比較</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F42" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G42" s="18" t="inlineStr">
@@ -10517,7 +10521,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
+          <t>経年比較は計画に置く。</t>
         </is>
       </c>
     </row>
@@ -10534,11 +10538,11 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>在宅生活の継続に必要な生活支援</t>
+          <t>重度者の在宅・居住系割合の上昇</t>
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>1</v>
@@ -10555,7 +10559,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>第5章 基本目標2・3の根拠となる。</t>
+          <t>施設整備の方針（第6章第5節）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -10567,16 +10571,16 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>第10期分の介護人材実態調査の結果</t>
+          <t>在宅生活の継続に必要な生活支援</t>
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>1</v>
@@ -10593,35 +10597,35 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
+          <t>第5章 基本目標2・3の根拠となる。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>第3章</t>
+          <t>第2章</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の事業費（決算）</t>
+          <t>第10期分の介護人材実態調査の結果</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G45" s="18" t="inlineStr">
@@ -10631,7 +10635,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
+          <t>基本指針が介護人材の確保を主要テーマとしている。</t>
         </is>
       </c>
     </row>
@@ -10648,18 +10652,18 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の通いの場の展開状況</t>
+          <t>令和6年度の事業費（決算）</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F46" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G46" s="18" t="inlineStr">
@@ -10669,7 +10673,7 @@
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも通いの場の記載がある。</t>
+          <t>法第117条第3項第2号（地域支援事業に要する費用の額）。</t>
         </is>
       </c>
     </row>
@@ -10686,11 +10690,11 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>一般介護予防事業の実施状況（令和6年度）</t>
+          <t>令和6年度の通いの場の展開状況</t>
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>1</v>
@@ -10707,7 +10711,7 @@
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも実施状況の記載がある。</t>
+          <t>第9期計画にも通いの場の記載がある。</t>
         </is>
       </c>
     </row>
@@ -10719,71 +10723,71 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
+          <t>一般介護予防事業の実施状況（令和6年度）</t>
         </is>
       </c>
       <c r="D48" s="6" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F48" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F48" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
+          <t>第9期計画にも実施状況の記載がある。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>第4章</t>
+          <t>第3章</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>第9期の目標指標との接続</t>
+          <t>調査に所見があるが、対応する施策を確認できない5領域</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G49" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>4</v>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
+          <t>第9期の施策の不足を指摘するもの。第10期の施策の根拠として本文に置く案と、評価表に移して本文は結論のみとする案がある。</t>
         </is>
       </c>
     </row>
@@ -10800,28 +10804,28 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>H07・H08・H12・H16の振替について</t>
+          <t>第9期の目標指標との接続</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>0</v>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
+          <t>第9期計画の目標指標を引き継いだことと、改称により系列が接続しないことを示すものである（確認事項No.39）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -10838,14 +10842,14 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>H13・H14の定義変更について</t>
+          <t>H07・H08・H12・H16の振替について</t>
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
@@ -10859,7 +10863,7 @@
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>同上。</t>
+          <t>当初の定義では算定できなかったことの説明。第9期からの系列が接続しないことは計画に書く必要があるが、振替の経緯は資料1に集約できる。</t>
         </is>
       </c>
     </row>
@@ -10876,52 +10880,52 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>H15の分母について</t>
+          <t>H13・H14の定義変更について</t>
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G52" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>0</v>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
+          <t>同上。</t>
         </is>
       </c>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>第5章</t>
+          <t>第4章</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>基本目標5</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>介護給付費の適正化（第7期給付適正化計画）</t>
+          <t>H15の分母について</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E53" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F53" s="18" t="inlineStr">
         <is>
@@ -10935,31 +10939,31 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
+          <t>給付費の計画乖離率の分母を標準給付費見込額とすることを示すものである。保険料の算定の基礎と範囲をそろえる必要がある（確認事項No.45）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>第6章</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>第1節</t>
+          <t>基本目標5</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>要介護度別の認定者数</t>
+          <t>介護給付費の適正化（第7期給付適正化計画）</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E54" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" s="18" t="inlineStr">
         <is>
@@ -10973,7 +10977,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
+          <t>法第117条第2項第3号・第4号の記載事項に当たる。</t>
         </is>
       </c>
     </row>
@@ -10990,28 +10994,28 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>認定率の置き方によるちがい</t>
+          <t>要介護度別の認定者数</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G55" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
+          <t>見込量の算定の基礎であり、基本指針別表 四に対応する。</t>
         </is>
       </c>
     </row>
@@ -11028,11 +11032,11 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎による推計のちがい</t>
+          <t>認定率の置き方によるちがい</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>1</v>
@@ -11049,7 +11053,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>同上。案Cを採る理由の説明としては要る。</t>
+          <t>推計の感度分析。計画に置くか見込量算定の成果品に委ねるかを協議する。</t>
         </is>
       </c>
     </row>
@@ -11061,33 +11065,33 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>第2節</t>
+          <t>第1節</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>見込量の算定方法</t>
+          <t>人口の基礎による推計のちがい</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F57" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
-        </is>
-      </c>
-      <c r="G57" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+        <v>1</v>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>見込量の前提を示すもので、計画に置く。</t>
+          <t>同上。案Cを採る理由の説明としては要る。</t>
         </is>
       </c>
     </row>
@@ -11104,15 +11108,15 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>利用回（日）数</t>
+          <t>見込量の算定方法</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E58" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E58" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F58" s="18" t="inlineStr">
         <is>
           <t>法定</t>
@@ -11125,7 +11129,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号が回数・日数を求めている。</t>
+          <t>見込量の前提を示すもので、計画に置く。</t>
         </is>
       </c>
     </row>
@@ -11137,16 +11141,16 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>第3節</t>
+          <t>第2節</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>介護予防・日常生活支援総合事業の量の見込み</t>
+          <t>利用回（日）数</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>1</v>
@@ -11163,7 +11167,7 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号。</t>
+          <t>法第117条第2項第1号が回数・日数を求めている。</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11184,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業の量の中長期的な推計</t>
+          <t>介護予防・日常生活支援総合事業の量の見込み</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
@@ -11201,7 +11205,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第3号。社会福祉法等の一部を改正する法律案要綱 第2の14（1）イにより、サービスの種類ごとの量と併せて地域支援事業の量の中長期的な推計が基本的記載事項となった。令和8年10月14日に要綱により新設した。</t>
+          <t>法第117条第2項第2号。</t>
         </is>
       </c>
     </row>
@@ -11218,11 +11222,11 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>地域支援事業費</t>
+          <t>地域支援事業の量の中長期的な推計</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" s="6" t="n">
         <v>1</v>
@@ -11239,7 +11243,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>法第117条第3項第2号。</t>
+          <t>法第117条第2項第3号。社会福祉法等の一部を改正する法律案要綱 第2の14（1）イにより、サービスの種類ごとの量と併せて地域支援事業の量の中長期的な推計が基本的記載事項となった。令和8年10月14日に要綱により新設した。</t>
         </is>
       </c>
     </row>
@@ -11256,14 +11260,14 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実施状況</t>
+          <t>地域支援事業費</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="18" t="inlineStr">
         <is>
@@ -11277,7 +11281,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
+          <t>法第117条第3項第2号。</t>
         </is>
       </c>
     </row>
@@ -11289,20 +11293,20 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>第4節</t>
+          <t>第3節</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>定員と見込量の照合</t>
+          <t>認知症総合支援事業の実施状況</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E63" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F63" s="18" t="inlineStr">
         <is>
           <t>法定</t>
@@ -11315,7 +11319,7 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>必要利用定員総数の算定の根拠となる。</t>
+          <t>法第117条第2項第2号の地域支援事業の量の見込みに係るものである。量を立てられないため、構成3町の実施状況を掲げている（確認事項No.150）。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11332,18 +11336,18 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
+          <t>定員と見込量の照合</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G64" s="18" t="inlineStr">
@@ -11353,7 +11357,7 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
+          <t>必要利用定員総数の算定の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -11370,28 +11374,28 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>供給の担い手の集中</t>
+          <t>区域内の入居状況と当広域連合の被保険者の受給者数</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G65" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
+          <t>区域内の定員が上限ではないことを示すもので、必要利用定員総数を誤読させないために要る。</t>
         </is>
       </c>
     </row>
@@ -11408,28 +11412,28 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>現況（令和8年度）</t>
+          <t>供給の担い手の集中</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E66" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F66" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G66" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F66" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G66" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも現況の記載がある。</t>
+          <t>運営法人の集中（第2章第3節）と重複する。第6章では整備方針への接続だけを残す案がある。</t>
         </is>
       </c>
     </row>
@@ -11446,18 +11450,18 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>第10期における必要利用定員総数</t>
+          <t>現況（令和8年度）</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F67" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F67" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G67" s="18" t="inlineStr">
@@ -11467,7 +11471,7 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
+          <t>第9期計画にも現況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -11484,11 +11488,11 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>特定施設入居者生活介護に係る必要利用定員総数</t>
+          <t>第10期における必要利用定員総数</t>
         </is>
       </c>
       <c r="D68" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E68" s="6" t="n">
         <v>1</v>
@@ -11505,7 +11509,7 @@
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>法第117条第2項第1号により本計画が定める必要利用定員総数の範囲を示すもの（確認事項No.113）。令和8年10月15日に参照条文により、介護専用型及び混合型の必要利用定員総数はいずれも都道府県介護保険事業支援計画の事項（法第118条第2項第1号・第4項）であり本計画の記載事項でないことが分かったため、見出し及び記述を是正した。</t>
+          <t>法第117条第2項第1号。［要協議］のまま残している。</t>
         </is>
       </c>
     </row>
@@ -11517,23 +11521,23 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>第5節</t>
+          <t>第4節</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>入所の経路からみた整備の考え方</t>
+          <t>特定施設入居者生活介護に係る必要利用定員総数</t>
         </is>
       </c>
       <c r="D69" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+        <v>1</v>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G69" s="18" t="inlineStr">
@@ -11543,7 +11547,7 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
+          <t>法第117条第2項第1号により本計画が定める必要利用定員総数の範囲を示すもの（確認事項No.113）。令和8年10月15日に参照条文により、介護専用型及び混合型の必要利用定員総数はいずれも都道府県介護保険事業支援計画の事項（法第118条第2項第1号・第4項）であり本計画の記載事項でないことが分かったため、見出し及び記述を是正した。</t>
         </is>
       </c>
     </row>
@@ -11560,18 +11564,18 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>北海道の道作成指針（案）が示す整備の考え方</t>
+          <t>入所の経路からみた整備の考え方</t>
         </is>
       </c>
       <c r="D70" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>0</v>
+      </c>
+      <c r="F70" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G70" s="18" t="inlineStr">
@@ -11581,7 +11585,7 @@
       </c>
       <c r="H70" s="5" t="inlineStr">
         <is>
-          <t>北海道の第10期計画の策定に係る道作成指針（案）が市町村介護保険事業計画の基本的記載事項として示す事項と本計画における扱いの対照である。令和8年10月20日に新設した。</t>
+          <t>整備方針（法第117条第3項第3号）の根拠となる。</t>
         </is>
       </c>
     </row>
@@ -11593,12 +11597,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>第6節</t>
+          <t>第5節</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>第9期の状況</t>
+          <t>北海道の道作成指針（案）が示す整備の考え方</t>
         </is>
       </c>
       <c r="D71" s="6" t="n">
@@ -11607,9 +11611,9 @@
       <c r="E71" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F71" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G71" s="18" t="inlineStr">
@@ -11619,7 +11623,7 @@
       </c>
       <c r="H71" s="5" t="inlineStr">
         <is>
-          <t>第9期計画にも前期の状況の記載がある。</t>
+          <t>北海道の第10期計画の策定に係る道作成指針（案）が市町村介護保険事業計画の基本的記載事項として示す事項と本計画における扱いの対照である。令和8年10月20日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11640,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>期別の必要保険料月額と基準額の対比</t>
+          <t>第9期の状況</t>
         </is>
       </c>
       <c r="D72" s="6" t="n">
@@ -11645,19 +11649,19 @@
       <c r="E72" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F72" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G72" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="F72" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
+        </is>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H72" s="5" t="inlineStr">
         <is>
-          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
+          <t>第9期計画にも前期の状況の記載がある。</t>
         </is>
       </c>
     </row>
@@ -11674,28 +11678,28 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金の状況</t>
+          <t>期別の必要保険料月額と基準額の対比</t>
         </is>
       </c>
       <c r="D73" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E73" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F73" s="25" t="inlineStr">
-        <is>
-          <t>第9期</t>
-        </is>
-      </c>
-      <c r="G73" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="F73" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G73" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>基金の取崩しは保険料の決定に直結する。</t>
+          <t>第5期からの対比。保険料の説明としては有用だが第9期計画にはない。資料編に移す案がある。</t>
         </is>
       </c>
     </row>
@@ -11712,18 +11716,18 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>保険料収納率と所得段階別被保険者数の実績</t>
+          <t>介護給付費準備基金の状況</t>
         </is>
       </c>
       <c r="D74" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E74" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+      <c r="F74" s="25" t="inlineStr">
+        <is>
+          <t>第9期</t>
         </is>
       </c>
       <c r="G74" s="18" t="inlineStr">
@@ -11733,7 +11737,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>保険料算定の基礎。</t>
+          <t>基金の取崩しは保険料の決定に直結する。</t>
         </is>
       </c>
     </row>
@@ -11750,11 +11754,11 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>所得段階と乗率の置き方</t>
+          <t>保険料収納率と所得段階別被保険者数の実績</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E75" s="6" t="n">
         <v>1</v>
@@ -11771,7 +11775,7 @@
       </c>
       <c r="H75" s="5" t="inlineStr">
         <is>
-          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
+          <t>保険料算定の基礎。</t>
         </is>
       </c>
     </row>
@@ -11788,28 +11792,28 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>保険料と必要保険料月額との関係</t>
+          <t>所得段階と乗率の置き方</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F76" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
-        </is>
-      </c>
-      <c r="G76" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+        <v>1</v>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
+        </is>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
-          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
+          <t>所得段階及び乗率は政令を踏まえて条例で定めるもので、保険料の算定の前提である。政令の公布後に再算定することを記載している（確認事項No.33）。令和8年10月5日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11826,28 +11830,28 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>暫定算定</t>
+          <t>保険料と必要保険料月額との関係</t>
         </is>
       </c>
       <c r="D77" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E77" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G77" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
+          <t>剰余・不足の見方の説明。基金の取崩しの判断に要る。</t>
         </is>
       </c>
     </row>
@@ -11864,11 +11868,11 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>給付費の置き方によるちがい</t>
+          <t>暫定算定</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E78" s="6" t="n">
         <v>1</v>
@@ -11878,14 +11882,14 @@
           <t>独自</t>
         </is>
       </c>
-      <c r="G78" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
+          <t>令和8年9月29日のご指示により、見出しを「受託者による暫定算定」から改めた。計画は広域連合が定めるものであり、本文に受託者を主語とする見出しを置かない。</t>
         </is>
       </c>
     </row>
@@ -11902,11 +11906,11 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映した場合</t>
+          <t>給付費の置き方によるちがい</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E79" s="6" t="n">
         <v>1</v>
@@ -11923,7 +11927,7 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
+          <t>3つの置き方の対比。採用案が決まれば1つに絞れる。</t>
         </is>
       </c>
     </row>
@@ -11940,28 +11944,28 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>前提を動かした場合の幅</t>
+          <t>サービス別の趨勢を反映した場合</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E80" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F80" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G80" s="18" t="inlineStr">
-        <is>
-          <t>残す</t>
+      <c r="G80" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
+          <t>対計画比の偏りを補正した場合の対比（確認事項No.106）。補正を行うかどうかのご判断を待つ間に置くもので、ご判断の後は落とす。令和8年10月1日に新設した。</t>
         </is>
       </c>
     </row>
@@ -11978,18 +11982,18 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>所得段階の置き方による保険料の違い</t>
+          <t>前提を動かした場合の幅</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E81" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="18" t="inlineStr">
-        <is>
-          <t>法定</t>
+        <v>3</v>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
         </is>
       </c>
       <c r="G81" s="18" t="inlineStr">
@@ -11999,7 +12003,7 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>国は第10期において高所得者の標準乗率の見直し及び課税化に伴う上昇の緩和を含めた標準段階の見直しを検討課題として挙げている（令和8年9月18日社会保障審議会介護保険部会）。段階の置き方により基準額が動くため、3案の比較を掲げる（確認事項No.33）。令和8年10月7日に新設した。</t>
+          <t>保険料の決定に当たり幅を示すことは計画の説明として要る。採用案が決まった後も残す。</t>
         </is>
       </c>
     </row>
@@ -12011,16 +12015,16 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>第7節</t>
+          <t>第6節</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>低所得者に係る負担軽減の見直し</t>
+          <t>所得段階の置き方による保険料の違い</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E82" s="6" t="n">
         <v>1</v>
@@ -12037,31 +12041,35 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>令和8年3月課長会議資料により追加した。令和8年10月7日に、見出しを「第10期に施行される見直し」から改めた。一定以上所得基準は結論を得る段階であり施行が決まっていないため、見出しで施行を断定しない。</t>
+          <t>国は第10期において高所得者の標準乗率の見直し及び課税化に伴う上昇の緩和を含めた標準段階の見直しを検討課題として挙げている（令和8年9月18日社会保障審議会介護保険部会）。段階の置き方により基準額が動くため、3案の比較を掲げる（確認事項No.33）。令和8年10月7日に新設した。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="44" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>資料5</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr"/>
+          <t>第6章</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>第7節</t>
+        </is>
+      </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>地域包括ケア「見える化」システムの使用データ</t>
+          <t>低所得者に係る負担軽減の見直し</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E83" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="24" t="inlineStr">
-        <is>
-          <t>独自</t>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>法定</t>
         </is>
       </c>
       <c r="G83" s="18" t="inlineStr">
@@ -12071,41 +12079,41 @@
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>出典の明示に当たる。</t>
+          <t>令和8年3月課長会議資料により追加した。令和8年10月7日に、見出しを「第10期に施行される見直し」から改めた。一定以上所得基準は結論を得る段階であり施行が決まっていないため、見出しで施行を断定しない。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="44" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>資料7</t>
+          <t>資料5</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr"/>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>採番と表記の規則</t>
+          <t>地域包括ケア「見える化」システムの使用データ</t>
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G84" s="24" t="inlineStr">
-        <is>
-          <t>協議</t>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>残す</t>
         </is>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
+          <t>出典の明示に当たる。</t>
         </is>
       </c>
     </row>
@@ -12118,33 +12126,67 @@
       <c r="B85" s="5" t="inlineStr"/>
       <c r="C85" s="5" t="inlineStr">
         <is>
+          <t>採番と表記の規則</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>独自</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>協議</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>図表の採番の規則であり、成果品の仕様に近い。資料7の冒頭1段落に圧縮する案がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="44" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>資料7</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr"/>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
           <t>未確定箇所の表示</t>
         </is>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D86" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="E86" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F85" s="24" t="inlineStr">
+      <c r="F86" s="24" t="inlineStr">
         <is>
           <t>独自</t>
         </is>
       </c>
-      <c r="G85" s="18" t="inlineStr">
+      <c r="G86" s="18" t="inlineStr">
         <is>
           <t>残す</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H86" s="5" t="inlineStr">
         <is>
           <t>［要協議］等の記号の意味を示すものであり、本文を読むために必要な凡例に当たる。記号が0になった時点で落とす。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="48" customHeight="1">
-      <c r="A87" s="12" t="inlineStr">
+    <row r="88" ht="48" customHeight="1">
+      <c r="A88" s="12" t="inlineStr">
         <is>
           <t>注1）区分「法定」は法令又は基本指針が求める事項の説明、「第9期」は第9期計画にも同種の記載がある事項、「独自」は第9期計画になく法令も直接には求めていない当方の分析である。
 注2）判定「残す」は計画に置く、「移す」は打合せ協議用の資料へ移す、「協議」はいずれとするかをお決めいただくものである。「移す」も削るという意味ではなく、本文には結論のみを残す。</t>
@@ -12153,8 +12195,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A87:H87"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A88:H88"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12502,7 +12544,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1074段落158表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1083段落160表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>147／147表</t>
+          <t>149／149表</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">

--- a/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
+++ b/output/第10期計画_計画素案の記載内容の洗い出しと対比.xlsx
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
     <row r="31" ht="56" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1083段落160表36図となった（表6点の減）。
+          <t>ご指示「移すは8件とも移してよい。協議は一旦そのまま。小見出しは保留」により、8件を計画素案から移した（07シート）。移した内容は本文から消えるのではなく、結論のみを本文に残している。移し先はいずれも既にある成果品であり、新たな成果品は起こしていない。これにより計画素案は943段落147表から1090段落161表36図となった（表6点の減）。
 「協議」と判定した16件は、ご指示により一旦そのまま素案に残している。小見出しの体裁（確認事項No.171）は保留である。</t>
         </is>
       </c>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>本表160表／実物160表</t>
+          <t>本表161表／実物161表</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>本表868段落（空段落・目次の行を除く）／実物1083段落（すべて）</t>
+          <t>本表875段落（空段落・目次の行を除く）／実物1090段落（すべて）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>149／149表</t>
+          <t>150／150表</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>160／160表</t>
+          <t>161／161表</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
@@ -4217,16 +4217,16 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
     </row>
@@ -4376,7 +4376,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>3</v>
@@ -4930,7 +4930,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>4</v>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>14</v>
@@ -5200,7 +5200,7 @@
         <v>11</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
@@ -5409,16 +5409,16 @@
       </c>
       <c r="B55" s="16" t="inlineStr"/>
       <c r="C55" s="15" t="n">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E55" s="15" t="n">
         <v>82</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G55" s="16" t="inlineStr"/>
     </row>
@@ -11036,7 +11036,7 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>1</v>
@@ -11986,7 +11986,7 @@
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E81" s="6" t="n">
         <v>3</v>
@@ -12544,7 +12544,7 @@
         <is>
           <t>注1）移し先は、いずれも既にある成果品である。当初の案では「進行管理の実施要領（新規）」「協議用の保険料算定資料（新規）」としていたが、同じ内容を扱う成果品が既にあるため、新たな成果品を起こさずそちらへ移した。
 注2）移した先の成果品名は計画素案の本文に書いていない（計画の読み手に向けた記述ではないため）。
-注3）この移行により、計画素案は943段落147表から1083段落160表36図（表6点の減）となった。</t>
+注3）この移行により、計画素案は943段落147表から1090段落161表36図（表6点の減）となった。</t>
         </is>
       </c>
     </row>
